--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Checks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Findings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Licences" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Data freshness" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licences" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data freshness" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$F$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$F$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checks'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$138</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Findings'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Licences'!$A$1:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Licences'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Data freshness'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 4 Oct 2026, 21:07 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 9 Oct 2026, 16:42 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>31% on 6 Sep 2026</t>
+          <t>31% on 11 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>45.3% on 6 Sep 2026</t>
+          <t>45.3% on 11 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>4 on 6 Sep 2026</t>
+          <t>4 on 11 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>52 on 6 Sep 2026</t>
+          <t>52 on 11 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="7" t="n"/>
     </row>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2408,8 +2408,35 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>No accounts are at risk in Entra ID Protection</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Risky users need Entra ID P2</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Check each account with the person. If they don't recognise recent sign-ins, reset the password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised or dismiss the risk in Entra ID Protection. Add a Conditional Access policy that asks for a secure password change on high user risk. The Risky users report lists each account.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F54"/>
+  <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -4269,7 +4296,7 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Set domain authentication by mallory.quinn@fabrikam.example on 2 Oct 2026</t>
+          <t>Set domain authentication by mallory.quinn@fabrikam.example on 7 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4362,7 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 15 Apr 2026</t>
+          <t>Licensed member, last signed in 20 Apr 2026</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4384,7 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 27 Feb 2026</t>
+          <t>Licensed member, last signed in 4 Mar 2026</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4406,7 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 27 May 2026</t>
+          <t>Licensed member, last signed in 1 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4428,7 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 30 Jan 2026</t>
+          <t>Licensed member, last signed in 4 Feb 2026</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4450,7 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 28 May 2026</t>
+          <t>Licensed member, last signed in 2 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4472,7 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 1 Jul 2026</t>
+          <t>Licensed member, last signed in 6 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -5757,7 +5784,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5772,7 +5799,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5787,7 +5814,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5802,7 +5829,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5817,7 +5844,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5832,7 +5859,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5847,7 +5874,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5862,7 +5889,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5877,7 +5904,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5892,7 +5919,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5907,7 +5934,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -5922,7 +5949,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -5937,7 +5964,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5948,11 +5975,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mailboxes</t>
+          <t>Deleted users and groups</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5963,11 +5990,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Inbox rules</t>
+          <t>Mailboxes</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>46299.8794212963</v>
+        <v>46304.69524305555</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -5978,11 +6005,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mailbox size</t>
+          <t>Inbox rules</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>46299.87943287037</v>
+        <v>46304.69525462963</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -5993,11 +6020,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Legacy sign-ins</t>
+          <t>Mailbox size</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>46299.87943287037</v>
+        <v>46304.69525462963</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6008,11 +6035,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sign-in activity</t>
+          <t>Legacy sign-ins</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>46299.87943287037</v>
+        <v>46304.69525462963</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6023,11 +6050,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Email domains</t>
+          <t>Sign-in activity</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>46299.87943287037</v>
+        <v>46304.69525462963</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6038,11 +6065,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Risky users</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>46299.87943287037</v>
+        <v>46304.69525462963</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6053,11 +6080,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Directory sync</t>
+          <t>Email domains</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>46299.87943287037</v>
+        <v>46304.69525462963</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6068,11 +6095,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SharePoint and OneDrive usage</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>46299.87943287037</v>
+        <v>46304.69525462963</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6083,11 +6110,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shared files</t>
+          <t>Directory sync</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>46299.87943287037</v>
+        <v>46304.69525462963</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6098,11 +6125,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SharePoint storage</t>
+          <t>SharePoint and OneDrive usage</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>46299.87943287037</v>
+        <v>46304.69525462963</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6113,20 +6140,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Shared files</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>46304.69525462963</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SharePoint storage</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>46304.69525462963</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Microsoft 365 usage</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
-        <v>46299.87943287037</v>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B28" s="12" t="n">
+        <v>46304.69525462963</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Up to date</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C26"/>
+  <autoFilter ref="A1:C28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licences" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data freshness" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Checks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Findings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Licences" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Data freshness" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 9 Oct 2026, 16:42 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 9 Oct 2026, 23:19 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>All 3 shared mailbox(es) block sign-in</t>
+          <t>All 3 shared mailboxes block sign-in</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.9 GB older versions</t>
+          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>483.2 GB, of which 46.0 GB in the recycle bin and 36.8 GB older versions</t>
+          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>65.3 GB, of which 1.0 GB in the recycle bin and 5.0 GB older versions</t>
+          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>352.6 GB, of which 12.0 GB in the recycle bin and 26.2 GB older versions</t>
+          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.6 GB older versions</t>
+          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97091435185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>46304.69524305555</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6020,11 +6020,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mailbox size</t>
+          <t>Sign-in activity</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6035,11 +6035,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Legacy sign-ins</t>
+          <t>Mailbox size</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6050,11 +6050,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sign-in activity</t>
+          <t>Legacy sign-ins</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>46304.69525462963</v>
+        <v>46304.97092592593</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 9 Oct 2026, 23:19 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 9 Oct 2026, 23:28 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>46304.97091435185</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>46304.97092592593</v>
+        <v>46304.97725694445</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 9 Oct 2026, 23:28 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 9 Oct 2026, 23:46 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>46304.97725694445</v>
+        <v>46304.99011574074</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 9 Oct 2026, 23:46 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 9 Oct 2026, 23:53 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99449074074</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99450231482</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99450231482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99450231482</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99450231482</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99450231482</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99450231482</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99450231482</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99450231482</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>46304.99011574074</v>
+        <v>46304.99450231482</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -17,11 +17,11 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$F$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checks'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$139</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Findings'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Licences'!$A$1:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Licences'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Data freshness'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 9 Oct 2026, 23:53 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 10 Oct 2026, 20:56 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>31% on 11 Sep 2026</t>
+          <t>33% on 12 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>45.3% on 11 Sep 2026</t>
+          <t>46.9% on 12 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>4 on 11 Sep 2026</t>
+          <t>4 on 12 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>52 on 11 Sep 2026</t>
+          <t>52 on 12 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -630,11 +630,11 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>1 critical, 25 high, 53 medium, 58 low findings</t>
+          <t>1 critical, 26 high, 53 medium, 58 low findings</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="7" t="n"/>
     </row>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -943,12 +943,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>No guest holds a privileged role</t>
+          <t>1 guest admin assignment</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2456,7 +2461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2567,17 +2572,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>1 app with access to mail, files or the directory</t>
+          <t>1 guest admin assignment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mail Sync Pro</t>
+          <t>g#EXT#@fabrikam.example</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Mail.Read (application permission; unverified publisher)</t>
+          <t>Guest holding Exchange Administrator</t>
         </is>
       </c>
     </row>
@@ -2589,17 +2594,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>6 of 54 computers not encrypted</t>
+          <t>1 app with access to mail, files or the directory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
+          <t>Mail Sync Pro</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Windows disk isn't encrypted</t>
+          <t>Mail.Read (application permission; unverified publisher)</t>
         </is>
       </c>
     </row>
@@ -2616,17 +2621,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Windows disk isn't encrypted</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Windows disk isn't encrypted</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2670,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2687,7 +2692,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
+          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2709,7 +2714,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
+          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2726,17 +2731,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
+          <t>6 of 54 computers not encrypted</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LAPTOP-HARRIS31 (noah.harris@fabrikam.example)</t>
+          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Windows 10 stopped getting security updates on 14 Oct 2025. Extended Security Updates or LTSC can cover it; otherwise upgrade.</t>
+          <t>Windows disk isn't encrypted</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2758,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAPTOP-JACKSON49 (chloe.jackson@fabrikam.example)</t>
+          <t>LAPTOP-HARRIS31 (noah.harris@fabrikam.example)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2775,7 +2780,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>LAPTOP-JACKSON49 (chloe.jackson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -2797,7 +2802,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LAPTOP-SMITH13 (owen.smith@fabrikam.example)</t>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2819,7 +2824,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LAPTOP-WALKER04 (rhys.walker@fabrikam.example)</t>
+          <t>LAPTOP-SMITH13 (owen.smith@fabrikam.example)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -2841,7 +2846,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
+          <t>LAPTOP-WALKER04 (rhys.walker@fabrikam.example)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2863,7 +2868,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LAPTOP-WOOD22 (william.wood@fabrikam.example)</t>
+          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -2875,7 +2880,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -2885,12 +2890,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DESK-ALLEN09 (thomas.allen@fabrikam.example)</t>
+          <t>LAPTOP-WOOD22 (william.wood@fabrikam.example)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 10 stopped getting security updates on 14 Oct 2025. Extended Security Updates or LTSC can cover it; otherwise upgrade.</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2912,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DESK-CLARK06 (ruby.clark@fabrikam.example)</t>
+          <t>DESK-ALLEN09 (thomas.allen@fabrikam.example)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -2929,7 +2934,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DESK-HARRISON21 (leo.harrison@fabrikam.example)</t>
+          <t>DESK-CLARK06 (ruby.clark@fabrikam.example)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2951,7 +2956,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DESK-KHAN30 (owen.khan@fabrikam.example)</t>
+          <t>DESK-HARRISON21 (leo.harrison@fabrikam.example)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -2973,7 +2978,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DESK-KING24 (megan.king@fabrikam.example)</t>
+          <t>DESK-KHAN30 (owen.khan@fabrikam.example)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -2995,7 +3000,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
+          <t>DESK-KING24 (megan.king@fabrikam.example)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -3017,7 +3022,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DESK-ROBERTS45 (jack.roberts@fabrikam.example)</t>
+          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -3039,17 +3044,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>DESK-ROBERTS45 (jack.roberts@fabrikam.example)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DESK-WHITE42 (lily.white@fabrikam.example)</t>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3093,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DESK-WILLIAMS27 (arthur.williams@fabrikam.example)</t>
+          <t>DESK-WHITE42 (lily.white@fabrikam.example)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -3110,7 +3115,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DESK-WOOD39 (ruby.wood@fabrikam.example)</t>
+          <t>DESK-WILLIAMS27 (arthur.williams@fabrikam.example)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -3132,7 +3137,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LAPTOP-BROWN01 (aisha.brown@fabrikam.example)</t>
+          <t>DESK-WOOD39 (ruby.wood@fabrikam.example)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -3154,7 +3159,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+          <t>LAPTOP-BROWN01 (aisha.brown@fabrikam.example)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -3176,7 +3181,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LAPTOP-GREEN32 (megan.green@fabrikam.example)</t>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -3198,7 +3203,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LAPTOP-JOHNSON47 (thomas.johnson@fabrikam.example)</t>
+          <t>LAPTOP-GREEN32 (megan.green@fabrikam.example)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -3220,7 +3225,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LAPTOP-JONES34 (ethan.jones@fabrikam.example)</t>
+          <t>LAPTOP-JOHNSON47 (thomas.johnson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -3242,7 +3247,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LAPTOP-KHAN35 (lily.khan@fabrikam.example)</t>
+          <t>LAPTOP-JONES34 (ethan.jones@fabrikam.example)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -3264,7 +3269,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LAPTOP-LEE02 (jack.lee@fabrikam.example)</t>
+          <t>LAPTOP-KHAN35 (lily.khan@fabrikam.example)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -3286,7 +3291,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+          <t>LAPTOP-LEE02 (jack.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -3308,7 +3313,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LAPTOP-ROBERTS41 (henry.roberts@fabrikam.example)</t>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -3330,7 +3335,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LAPTOP-SCOTT17 (owen.scott@fabrikam.example)</t>
+          <t>LAPTOP-ROBERTS41 (henry.roberts@fabrikam.example)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -3352,7 +3357,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LAPTOP-SCOTT19 (isla.scott@fabrikam.example)</t>
+          <t>LAPTOP-SCOTT17 (owen.scott@fabrikam.example)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -3374,17 +3379,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LAPTOP-SMITH50 (oscar.smith@fabrikam.example)</t>
+          <t>LAPTOP-SCOTT19 (isla.scott@fabrikam.example)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LAPTOP-TAYLOR43 (olivia.taylor@fabrikam.example)</t>
+          <t>LAPTOP-SMITH50 (oscar.smith@fabrikam.example)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
           <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3428,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LAPTOP-THOMAS08 (ava.thomas@fabrikam.example)</t>
+          <t>LAPTOP-TAYLOR43 (olivia.taylor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -3445,7 +3450,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LAPTOP-TURNER37 (callum.turner@fabrikam.example)</t>
+          <t>LAPTOP-THOMAS08 (ava.thomas@fabrikam.example)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -3467,7 +3472,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LAPTOP-WALKER10 (george.walker@fabrikam.example)</t>
+          <t>LAPTOP-TURNER37 (callum.turner@fabrikam.example)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -3489,7 +3494,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
+          <t>LAPTOP-WALKER10 (george.walker@fabrikam.example)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -3511,7 +3516,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LAPTOP-WILLIAMS20 (priya.williams@fabrikam.example)</t>
+          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -3523,22 +3528,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>1 suspicious inbox rule</t>
+          <t>7 of 54 Windows computers past end of support</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>LAPTOP-WILLIAMS20 (priya.williams@fabrikam.example)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>".": Moves to RSS Feeds mail mentioning invoice, payment; Rule name '.' looks deliberately blank</t>
+          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3555,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>5 external forwards</t>
+          <t>1 suspicious inbox rule</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3560,7 +3565,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Mailbox forwarding to anna.kowalski@homemail.example (keeps a copy)</t>
+          <t>".": Moves to RSS Feeds mail mentioning invoice, payment; Rule name '.' looks deliberately blank</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3587,7 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Inbox rule "Copy to home" forwards to anna.kowalski.home@homemail.example</t>
+          <t>Mailbox forwarding to anna.kowalski@homemail.example (keeps a copy)</t>
         </is>
       </c>
     </row>
@@ -3599,17 +3604,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>rhys.hall@fabrikam.example</t>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Mailbox forwarding to rhys.hall@homemail.example (doesn't keep a copy)</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Inbox rule "Copy to home" forwards to anna.kowalski.home@homemail.example</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>rhys.walker@fabrikam.example</t>
+          <t>rhys.hall@fabrikam.example</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Mailbox forwarding to rhys.walker@homemail.example (doesn't keep a copy)</t>
+          <t>Mailbox forwarding to rhys.hall@homemail.example (doesn't keep a copy)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3653,12 +3653,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>thomas.robinson@fabrikam.example</t>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Inbox rule "Invoices to bookkeeper" forwards to bookkeeping@ledgerline.example</t>
+          <t>Mailbox forwarding to rhys.walker@homemail.example (doesn't keep a copy)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3670,24 +3675,24 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>5 external forwards</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>thomas.robinson@fabrikam.example</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>No MFA method registered</t>
+          <t>Inbox rule "Invoices to bookkeeper" forwards to bookkeeping@ledgerline.example</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -3697,7 +3702,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>aaron.smith@fabrikam.example</t>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -3719,7 +3724,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>aisha.brown@fabrikam.example</t>
+          <t>aaron.smith@fabrikam.example</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -3741,7 +3746,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>amelia.khan@fabrikam.example</t>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -3763,7 +3768,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>arthur.williams@fabrikam.example</t>
+          <t>amelia.khan@fabrikam.example</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -3785,7 +3790,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ava.jackson@fabrikam.example</t>
+          <t>arthur.williams@fabrikam.example</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -3807,7 +3812,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ava.moore@fabrikam.example</t>
+          <t>ava.jackson@fabrikam.example</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -3829,7 +3834,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ava.thomas@fabrikam.example</t>
+          <t>ava.moore@fabrikam.example</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -3851,7 +3856,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>carl.svensson@fabrikam.example</t>
+          <t>ava.thomas@fabrikam.example</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -3873,7 +3878,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>chloe.jackson@fabrikam.example</t>
+          <t>carl.svensson@fabrikam.example</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3895,7 +3900,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>george.williams@fabrikam.example</t>
+          <t>chloe.jackson@fabrikam.example</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -3917,7 +3922,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>henry.roberts@fabrikam.example</t>
+          <t>george.williams@fabrikam.example</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3939,7 +3944,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>isla.scott@fabrikam.example</t>
+          <t>henry.roberts@fabrikam.example</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3961,7 +3966,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>jack.lee@fabrikam.example</t>
+          <t>isla.scott@fabrikam.example</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -3983,7 +3988,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jack.roberts@fabrikam.example</t>
+          <t>jack.lee@fabrikam.example</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -4005,7 +4010,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>lily.khan@fabrikam.example</t>
+          <t>jack.roberts@fabrikam.example</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -4027,7 +4032,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>lily.watson@fabrikam.example</t>
+          <t>lily.khan@fabrikam.example</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -4049,7 +4054,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>lily.white@fabrikam.example</t>
+          <t>lily.watson@fabrikam.example</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -4071,7 +4076,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>megan.king@fabrikam.example</t>
+          <t>lily.white@fabrikam.example</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -4093,7 +4098,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>noah.wood@fabrikam.example</t>
+          <t>megan.king@fabrikam.example</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -4115,7 +4120,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>olivia.taylor@fabrikam.example</t>
+          <t>noah.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -4137,7 +4142,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>owen.scott@fabrikam.example</t>
+          <t>olivia.taylor@fabrikam.example</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -4159,7 +4164,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>rhys.walker@fabrikam.example</t>
+          <t>owen.scott@fabrikam.example</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -4181,7 +4186,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ruby.davies@fabrikam.example</t>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -4203,7 +4208,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ruby.wood@fabrikam.example</t>
+          <t>ruby.davies@fabrikam.example</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -4225,7 +4230,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>thomas.johnson@fabrikam.example</t>
+          <t>ruby.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4247,7 +4252,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>zara.edwards@fabrikam.example</t>
+          <t>thomas.johnson@fabrikam.example</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -4259,22 +4264,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Legacy authentication is allowed</t>
+          <t>27 users without MFA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>zara.edwards@fabrikam.example</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>No enabled policy blocks legacy authentication for all users</t>
+          <t>No MFA method registered</t>
         </is>
       </c>
     </row>
@@ -4286,17 +4291,17 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>1 domain had sign-in settings changed in the last 30 days</t>
+          <t>Legacy authentication is allowed</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Set domain authentication by mallory.quinn@fabrikam.example on 7 Oct 2026</t>
+          <t>No enabled policy blocks legacy authentication for all users</t>
         </is>
       </c>
     </row>
@@ -4308,24 +4313,24 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
+          <t>1 domain had sign-in settings changed in the last 30 days</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Clients (Finance / Documents)</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Anyone can edit, link never expires</t>
+          <t>Set domain authentication by mallory.quinn@fabrikam.example on 8 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -4335,12 +4340,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>holiday.jpg (OneDrive of anna.kowalski@fabrikam.example)</t>
+          <t>Clients (Finance / Documents)</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Anyone can view</t>
+          <t>Anyone can edit, link never expires</t>
         </is>
       </c>
     </row>
@@ -4352,17 +4357,17 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>2 files and folders shared with anyone</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>aaron.smith@fabrikam.example</t>
+          <t>holiday.jpg (OneDrive of anna.kowalski@fabrikam.example)</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 20 Apr 2026</t>
+          <t>Anyone can view</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4384,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>aisha.brown@fabrikam.example</t>
+          <t>aaron.smith@fabrikam.example</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 4 Mar 2026</t>
+          <t>Licensed member, last signed in 21 Apr 2026</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4406,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>jack.lee@fabrikam.example</t>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 1 Jun 2026</t>
+          <t>Licensed member, last signed in 5 Mar 2026</t>
         </is>
       </c>
     </row>
@@ -4423,12 +4428,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>noah.wood@fabrikam.example</t>
+          <t>jack.lee@fabrikam.example</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 4 Feb 2026</t>
+          <t>Licensed member, last signed in 2 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -4445,12 +4450,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>rhys.walker@fabrikam.example</t>
+          <t>noah.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 2 Jun 2026</t>
+          <t>Licensed member, last signed in 5 Feb 2026</t>
         </is>
       </c>
     </row>
@@ -4467,19 +4472,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>zara.edwards@fabrikam.example</t>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 6 Jul 2026</t>
+          <t>Licensed member, last signed in 3 Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -4489,34 +4494,34 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>g#EXT#@fabrikam.example</t>
+          <t>zara.edwards@fabrikam.example</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Member, never signed in, created ?</t>
+          <t>Licensed member, last signed in 7 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
+          <t>7 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>g#EXT#@fabrikam.example</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator; signs in with Authenticator app</t>
+          <t>Guest, never signed in, created ?</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4538,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator; signs in with no MFA method at all</t>
+          <t>Global Administrator; signs in with Authenticator app</t>
         </is>
       </c>
     </row>
@@ -4550,17 +4555,17 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>1 app with privileged roles</t>
+          <t>2 admins without a phishing-resistant method</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Some app</t>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>App holding Exchange Administrator</t>
+          <t>Global Administrator; signs in with no MFA method at all</t>
         </is>
       </c>
     </row>
@@ -4572,17 +4577,17 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Users can consent to any app</t>
+          <t>1 app with privileged roles</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>Some app</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Any user can grant any app access to their mail and files</t>
+          <t>App holding Exchange Administrator</t>
         </is>
       </c>
     </row>
@@ -4594,17 +4599,17 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>Users can consent to any app</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
+          <t>Any user can grant any app access to their mail and files</t>
         </is>
       </c>
     </row>
@@ -4621,7 +4626,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
+          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -4643,17 +4648,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
           <t>Not compliant</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4670,12 +4670,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
           <t>Not compliant</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4697,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -4714,7 +4719,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -4736,7 +4741,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -4758,7 +4763,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
+          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -4780,7 +4785,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
+          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -4797,17 +4802,17 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>1 mail domain without DKIM</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 DKIM isn't set up (selector2 CNAME missing)</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
@@ -4819,7 +4824,7 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
+          <t>1 mail domain without DKIM</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4829,14 +4834,14 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>DMARC is monitor-only (p=none); spoofed mail is still delivered</t>
+          <t>Microsoft 365 DKIM isn't set up (selector2 CNAME missing)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -4846,41 +4851,41 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>parked.example</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Doesn't receive mail but has no DMARC p=reject record</t>
+          <t>DMARC is monitor-only (p=none); spoofed mail is still delivered</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>3 teams and groups without an owner</t>
+          <t>2 domains without DMARC enforcement</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Project Phoenix</t>
+          <t>parked.example</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>Team, only owner is disabled (Ben Okafor)</t>
+          <t>Doesn't receive mail but has no DMARC p=reject record</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -4890,12 +4895,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Project Phoenix</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, no owner</t>
+          <t>Team, only owner is disabled (Ben Okafor)</t>
         </is>
       </c>
     </row>
@@ -4912,34 +4917,34 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Provisioned</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, owned only by an app (Provisioning app)</t>
+          <t>Microsoft 365 group, no owner</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Enforced by Require MFA for all users, with 1 exclusion to review</t>
+          <t>3 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>Provisioned</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Excluded from "Require MFA for all users"</t>
+          <t>Microsoft 365 group, owned only by an app (Provisioning app)</t>
         </is>
       </c>
     </row>
@@ -4951,17 +4956,17 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>1 disabled account still licensed</t>
+          <t>Enforced by Require MFA for all users, with 1 exclusion to review</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ben.okafor@fabrikam.example</t>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Disabled, holding 1 licence</t>
+          <t>Excluded from "Require MFA for all users"</t>
         </is>
       </c>
     </row>
@@ -4973,17 +4978,17 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including anonymous links</t>
+          <t>1 disabled account still licensed</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SharePoint and OneDrive</t>
+          <t>ben.okafor@fabrikam.example</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Anyone links are allowed</t>
+          <t>Disabled, holding 1 licence</t>
         </is>
       </c>
     </row>
@@ -4995,29 +5000,24 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>Anyone, including anonymous links</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tenant SharePoint storage</t>
+          <t>SharePoint and OneDrive</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Anyone links are allowed</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/finance</t>
+          <t>Tenant SharePoint storage</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/imaging</t>
+          <t>https://fabrikam.sharepoint.com/sites/finance</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
+          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/marketing</t>
+          <t>https://fabrikam.sharepoint.com/sites/imaging</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
+          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/patient-records</t>
+          <t>https://fabrikam.sharepoint.com/sites/marketing</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
+          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/practice</t>
+          <t>https://fabrikam.sharepoint.com/sites/patient-records</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
+          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5157,17 +5157,22 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>1 app registration with expiring or expired credentials</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Old connector</t>
+          <t>https://fabrikam.sharepoint.com/sites/practice</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>The 1 credential expired, last on 1 Jan 2025</t>
+          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5179,17 +5184,17 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>1 of 55 joined computers not in Intune</t>
+          <t>1 app registration with expiring or expired credentials</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DESK-RECEPTION</t>
+          <t>Old connector</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Hybrid joined, not managed by Intune</t>
+          <t>The 1 credential expired, last on 1 Jan 2025</t>
         </is>
       </c>
     </row>
@@ -5201,17 +5206,17 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>1 of 55 joined computers not in Intune</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
+          <t>DESK-RECEPTION</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>Hybrid joined, not managed by Intune</t>
         </is>
       </c>
     </row>
@@ -5228,17 +5233,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
           <t>Last check-in 38 days ago</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5255,12 +5255,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
           <t>Last check-in 38 days ago</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5282,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
@@ -5299,12 +5304,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 45 days ago</t>
+          <t>Last check-in 38 days ago</t>
         </is>
       </c>
     </row>
@@ -5316,17 +5321,17 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>1 of 57 device records unused for 90+ days</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>OLD-PC</t>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Windows, last seen 200 days ago</t>
+          <t>Last check-in 45 days ago</t>
         </is>
       </c>
     </row>
@@ -5338,17 +5343,17 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>1 domain with SPF problems</t>
+          <t>1 of 57 device records unused for 90+ days</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>parked.example</t>
+          <t>OLD-PC</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Doesn't receive mail but has no "v=spf1 -all" record to stop spoofing</t>
+          <t>Windows, last seen 200 days ago</t>
         </is>
       </c>
     </row>
@@ -5360,17 +5365,17 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
+          <t>1 domain with SPF problems</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>parked.example</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>No MTA-STS policy, so mail sent to this domain can be forced onto an unencrypted connection</t>
+          <t>Doesn't receive mail but has no "v=spf1 -all" record to stop spoofing</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5387,17 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is on for the organisation</t>
+          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is allowed</t>
+          <t>No MTA-STS policy, so mail sent to this domain can be forced onto an unencrypted connection</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5409,7 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including guests, can invite guests</t>
+          <t>SMTP AUTH is on for the organisation</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5414,7 +5419,7 @@
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Guests can invite other guests</t>
+          <t>SMTP AUTH is allowed</t>
         </is>
       </c>
     </row>
@@ -5426,17 +5431,17 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>Anyone, including guests, can invite guests</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>george.baker@fabrikam.example</t>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>Guests can invite other guests</t>
         </is>
       </c>
     </row>
@@ -5453,17 +5458,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>owen.robinson@fabrikam.example</t>
+          <t>george.baker@fabrikam.example</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
           <t>Second factor is only Mobile phone (SMS or call)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5480,12 +5480,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>owen.turner@fabrikam.example</t>
+          <t>owen.robinson@fabrikam.example</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
           <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5507,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>thomas.allen@fabrikam.example</t>
+          <t>owen.turner@fabrikam.example</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
@@ -5519,17 +5524,17 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions with spare licences</t>
+          <t>4 people can only use a text or call as a second factor</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Microsoft 365 Business Basic</t>
+          <t>thomas.allen@fabrikam.example</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>2 of 13 unassigned, 9.80 GBP/month</t>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
         </is>
       </c>
     </row>
@@ -5546,12 +5551,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Microsoft 365 Business Premium</t>
+          <t>Microsoft 365 Business Basic</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>3 of 46 unassigned, 54.30 GBP/month</t>
+          <t>2 of 13 unassigned, 9.80 GBP/month</t>
         </is>
       </c>
     </row>
@@ -5563,22 +5568,44 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
+          <t>2 subscriptions with spare licences</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Microsoft 365 Business Premium</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>3 of 46 unassigned, 54.30 GBP/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
           <t>Any user can register an app</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Whole organisation</t>
         </is>
       </c>
-      <c r="D138" s="7" t="inlineStr">
+      <c r="D139" s="7" t="inlineStr">
         <is>
           <t>Users can register apps that nobody reviews</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E138"/>
+  <autoFilter ref="A1:E139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -5752,7 +5779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -5784,7 +5811,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5799,7 +5826,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5814,7 +5841,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5829,7 +5856,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5844,7 +5871,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5859,7 +5886,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5874,7 +5901,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5889,7 +5916,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5904,7 +5931,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5919,7 +5946,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5934,7 +5961,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -5949,7 +5976,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -5964,7 +5991,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5979,7 +6006,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87167824074</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5994,7 +6021,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6009,7 +6036,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6024,7 +6051,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6039,7 +6066,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>46304.99449074074</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6054,7 +6081,7 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>46304.99450231482</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6065,11 +6092,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Risky users</t>
+          <t>Mobile devices</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>46304.99450231482</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6080,11 +6107,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Email domains</t>
+          <t>Automatic replies</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>46304.99450231482</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6095,11 +6122,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Distribution lists</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>46304.99450231482</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6110,11 +6137,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Directory sync</t>
+          <t>Risky users</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>46304.99450231482</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6125,11 +6152,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SharePoint and OneDrive usage</t>
+          <t>Email domains</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>46304.99450231482</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6140,11 +6167,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Shared files</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>46304.99450231482</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6155,11 +6182,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SharePoint storage</t>
+          <t>Directory sync</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>46304.99450231482</v>
+        <v>46305.87168981481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6170,20 +6197,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>SharePoint and OneDrive usage</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>46305.87168981481</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Shared files</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>46305.87168981481</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SharePoint storage</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n">
+        <v>46305.87168981481</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Microsoft 365 usage</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
-        <v>46304.99450231482</v>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B31" s="12" t="n">
+        <v>46305.87168981481</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Up to date</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>App sign-ins</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n">
+        <v>46305.87168981481</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Group nesting</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>46305.87168981481</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Departments and managers</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>46305.87168981481</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C28"/>
+  <autoFilter ref="A1:C34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -15,13 +15,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$F$62</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checks'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$151</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Findings'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Licences'!$A$1:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Licences'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Data freshness'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,7 +512,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 10 Oct 2026, 20:56 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 11 Oct 2026, 19:13 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>33% on 12 Sep 2026</t>
+          <t>31% on 13 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>46.9% on 12 Sep 2026</t>
+          <t>47.8% on 13 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>4 on 12 Sep 2026</t>
+          <t>4 on 13 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>52 on 12 Sep 2026</t>
+          <t>50 on 13 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -630,11 +630,11 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>1 critical, 26 high, 53 medium, 58 low findings</t>
+          <t>1 critical, 28 high, 59 medium, 62 low findings</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C14" s="7" t="n"/>
     </row>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>1 guest admin assignment</t>
+          <t>1 guest with admin roles</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Outbound policies block automatic external forwarding</t>
+          <t>The default outbound policy blocks automatic external forwarding</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Turn on DKIM for each domain in the Defender portal (Email authentication settings &gt; DKIM), publishing the two selector CNAME records it shows.</t>
+          <t>Turn on DKIM for each domain in the Defender portal (Email authentication settings &gt; DKIM), publishing the two selector CNAME records it shows. This applies to domains behind a mail gateway too when Microsoft 365 still sends for them (their SPF includes spf.protection.outlook.com); a gateway signs only the mail that goes out through it.</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>3 teams and groups without an owner</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -1848,12 +1848,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Only chosen people can create teams and groups</t>
+          <t>No guest owns a team or group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Only admins and members of Group creators can create teams and groups</t>
+          <t>No guest owns any of 9 teams and groups</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Limit who can create teams and Microsoft 365 groups to a security group of people who will look after them (the Group.Unified directory setting, changed with Microsoft Graph PowerShell; needs Entra ID P1). Otherwise anyone can create a team, add guests to it and leave it behind.</t>
+          <t>Make a member of the organisation the owner of each listed team or group and remove the guest as owner (Teams admin center, or Microsoft 365 admin center &gt; Teams &amp; groups). An owner from outside can add members and guests, change settings and see everything in it, and nobody here is accountable for that.</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Unused groups and teams expire</t>
+          <t>Only chosen people can create teams and groups</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1890,44 +1890,39 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Unused teams and groups expire after 365 days</t>
+          <t>Only admins and members of Group creators can create teams and groups</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Set a Microsoft 365 group expiration policy for all groups (Entra admin center &gt; Groups &gt; Expiration), for example 365 days. Groups in use renew automatically, owners are asked to renew the rest, and an expired group can be restored for 30 days. Needs Entra ID P1.</t>
+          <t>Limit who can create teams and Microsoft 365 groups to a security group of people who will look after them (the Group.Unified directory setting, changed with Microsoft Graph PowerShell; needs Entra ID P1). Otherwise anyone can create a team, add guests to it and leave it behind.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Managed devices meet compliance policies</t>
+          <t>Unused groups and teams expire</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>Unused teams and groups expire after 365 days</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Open each non-compliant device in Intune (Devices &gt; Monitor &gt; Noncompliant devices) to see which setting fails, fix it or retire the device, and block non-compliant devices with a Conditional Access policy that requires a compliant device.</t>
+          <t>Set a Microsoft 365 group expiration policy for all groups (Entra admin center &gt; Groups &gt; Expiration), for example 365 days. Groups in use renew automatically, owners are asked to renew the rest, and an expired group can be restored for 30 days. Needs Entra ID P1.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1934,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Company computers are encrypted</t>
+          <t>Managed devices meet compliance policies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1949,17 +1944,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>6 of 54 computers not encrypted</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Turn on BitLocker (Windows) and FileVault (macOS) with an Intune disk encryption policy, with recovery keys escrowed to Entra ID, so a lost or stolen laptop doesn't expose the client's data.</t>
+          <t>Open each non-compliant device in Intune (Devices &gt; Monitor &gt; Noncompliant devices) to see which setting fails, fix it or retire the device, and block non-compliant devices with a Conditional Access policy that requires a compliant device.</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1966,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Windows computers still get security updates</t>
+          <t>Company computers are encrypted</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1986,12 +1981,12 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
+          <t>6 of 54 computers not encrypted</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Upgrade computers on Windows 10 or an old Windows 11 release to the current Windows 11 release (Intune: Windows feature updates policy). Replace hardware that can't run Windows 11, or buy Extended Security Updates as a stopgap.</t>
+          <t>Turn on BitLocker (Windows) and FileVault (macOS) with an Intune disk encryption policy, with recovery keys escrowed to Entra ID, so a lost or stolen laptop doesn't expose the client's data.</t>
         </is>
       </c>
     </row>
@@ -2003,7 +1998,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Joined computers are managed by Intune</t>
+          <t>Windows computers still get security updates</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2013,17 +2008,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>1 of 55 joined computers not in Intune</t>
+          <t>7 of 54 Windows computers past end of support</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Enrol Entra-joined and hybrid-joined computers in Intune (automatic enrolment under Devices &gt; Enrollment &gt; Windows) so compliance, encryption and updates can be enforced on them.</t>
+          <t>Upgrade computers on Windows 10 or an old Windows 11 release to the current Windows 11 release (Intune: Windows feature updates policy). Replace hardware that can't run Windows 11, or buy Extended Security Updates as a stopgap.</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2030,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Managed devices check in with Intune</t>
+          <t>Joined computers are managed by Intune</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2050,12 +2045,12 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>1 of 55 joined computers not in Intune</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Find out whether each device is lost, replaced or broken. Retire devices that are gone; for devices still in use, restart the Intune Management Extension or re-enrol.</t>
+          <t>Enrol Entra-joined and hybrid-joined computers in Intune (automatic enrolment under Devices &gt; Enrollment &gt; Windows) so compliance, encryption and updates can be enforced on them.</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2062,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>No old devices left in Entra ID</t>
+          <t>Managed devices check in with Intune</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2082,39 +2077,44 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>1 of 57 device records unused for 90+ days</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Disable, then after 30 days delete, device records that haven't signed in for 90 days (Entra admin center &gt; Devices &gt; All devices, filter by activity). Old records can still hold BitLocker keys and count toward device limits.</t>
+          <t>Find out whether each device is lost, replaced or broken. Retire devices that are gone; for devices still in use, restart the Intune Management Extension or re-enrol.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Hybrid identity</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Directory sync is running</t>
+          <t>No old devices left in Entra ID</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Cloud-only tenant: directory sync isn't turned on</t>
+          <t>1 of 57 device records unused for 90+ days</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Check the Entra Connect server: that it is up, the Microsoft Azure AD Sync service is running and Synchronization Service Manager shows no errors. Until sync runs, accounts disabled or removed in Active Directory keep working in Microsoft 365. If the client has moved to cloud-only, turn directory sync off.</t>
+          <t>Disable, then after 30 days delete, device records that haven't signed in for 90 days (Entra admin center &gt; Devices &gt; All devices, filter by activity). Old records can still hold BitLocker keys and count toward device limits.</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Password hash sync is on</t>
+          <t>Directory sync is running</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Turn on password hash synchronization in Entra Connect (Optional features), even when users sign in through federation or pass-through authentication. Entra ID can then detect leaked passwords, and sign-in can be switched to the cloud if the on-premises servers are down.</t>
+          <t>Check the Entra Connect server: that it is up, the Microsoft Azure AD Sync service is running and Synchronization Service Manager shows no errors. Until sync runs, accounts disabled or removed in Active Directory keep working in Microsoft 365. If the client has moved to cloud-only, turn directory sync off.</t>
         </is>
       </c>
     </row>
@@ -2153,66 +2153,61 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Admin accounts are cloud-only</t>
+          <t>Password hash sync is on</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Cloud-only tenant: no accounts are synced from on-premises AD</t>
+          <t>Cloud-only tenant: directory sync isn't turned on</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Give each admin a separate cloud-only account (for example on the .onmicrosoft.com domain) for their admin roles, and remove the roles from accounts synced from Active Directory. Otherwise anyone who takes over on-premises AD can reset those passwords and become an admin in Microsoft 365.</t>
+          <t>Turn on password hash synchronization in Entra Connect (Optional features), even when users sign in through federation or pass-through authentication. Entra ID can then detect leaked passwords, and sign-in can be switched to the cloud if the on-premises servers are down.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Hybrid identity</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>No unexpected changes to how domains sign in</t>
+          <t>Admin accounts are cloud-only</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>1 domain had sign-in settings changed in the last 30 days</t>
+          <t>Cloud-only tenant: no accounts are synced from on-premises AD</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Confirm with the client that each change was planned (for example, setting up AD FS or another identity provider). If it wasn't, an attacker with admin rights may have federated the domain to their own identity provider so they can sign in as any user without a password or MFA: switch the domain back to managed sign-in, remove unknown federation settings, reset admin credentials and review the audit log.</t>
+          <t>Give each admin a separate cloud-only account (for example on the .onmicrosoft.com domain) for their admin roles, and remove the roles from accounts synced from Active Directory. Otherwise anyone who takes over on-premises AD can reset those passwords and become an admin in Microsoft 365.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sharing</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>No files are shared with anyone links</t>
+          <t>No unexpected changes to how domains sign in</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2227,24 +2222,24 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
+          <t>1 domain had sign-in settings changed in the last 30 days</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Remove anyone links that are no longer needed, and set the rest to view-only with an expiry date. The Shared files report lists each one.</t>
+          <t>Confirm with the client that each change was planned (for example, setting up AD FS or another identity provider). If it wasn't, an attacker with admin rights may have federated the domain to their own identity provider so they can sign in as any user without a password or MFA: switch the domain back to managed sign-in, remove unknown federation settings, reset admin credentials and review the audit log.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>SharePoint storage isn't nearly full</t>
+          <t>No files are shared with anyone links</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2259,24 +2254,24 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>2 files and folders shared with anyone</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Free up space before the tenant runs out, when people can no longer save files. The SharePoint storage report shows where the space goes and what to clear first; otherwise buy Office 365 Extra File Storage.</t>
+          <t>Remove anyone links that are no longer needed, and set the rest to view-only with an expiry date. The Shared files report lists each one.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Admins</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Admins use phishing-resistant sign-in methods</t>
+          <t>SharePoint storage isn't nearly full</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2291,24 +2286,24 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Have each listed admin register a passkey (in Microsoft Authenticator or on a security key) or Windows Hello for Business, then require the Phishing-resistant MFA authentication strength for admin roles in Conditional Access. Codes and push approvals can be relayed by a fake sign-in page; these can't.</t>
+          <t>Free up space before the tenant runs out, when people can no longer save files. The SharePoint storage report shows where the space goes and what to clear first; otherwise buy Office 365 Extra File Storage.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Nobody relies on a text or call as their only second factor</t>
+          <t>Every site has at least two owners</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2318,98 +2313,113 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Ask these people to set up the Microsoft Authenticator app (the registration campaign in the authentication methods policy prompts them at sign-in), then turn off text message and voice call sign-in, or keep them only as a backup. Texts and calls can be intercepted or moved to an attacker's SIM.</t>
+          <t>Give each site a second owner (in the Microsoft 365 group, or as a site administrator) so access requests and content questions have someone to go to when one person leaves. The Site access report lists each site's owners.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Licences</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Every licence assignment works</t>
+          <t>Guests don't have full control of sites</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Every licence assignment worked</t>
+          <t>1 guest with full control of 1 site</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Fix each failed licence from the group's Licenses page in the Entra admin center: buy more licences when there aren't enough, remove licences that conflict, and correct usage locations. The Licences and subscriptions report explains each error.</t>
+          <t>Take guests out of each site's owners group and away from Full Control; give them Edit or Read through the site's members or visitors group instead. Full Control lets someone outside the organisation change who can open the site and delete anything on it. The Site permissions report lists them.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Licences</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>No subscriptions are about to lapse</t>
+          <t>People outside can only view shared files</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions checked; none is lapsing</t>
+          <t>2 files and folders outside people can edit</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Renew subscriptions in their grace period, buy or cancel trials people use before they end, and move people off suspended subscriptions. Billing &gt; Your products in the Microsoft 365 admin center (or Partner Center for subscriptions you sell) shows each one.</t>
+          <t>Change sharing with people outside the organisation to view-only unless they need to edit, and remove sharing that's no longer needed. The File and folder permissions report lists each person outside and what they can edit.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Admins</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>No risky sign-ins succeeded</t>
+          <t>Admins use phishing-resistant sign-in methods</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Sign-in risk needs Entra ID P2</t>
+          <t>2 admins without a phishing-resistant method</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Check each sign-in with the person. If they don't recognise it, reset their password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised in Entra ID Protection. Add a Conditional Access policy that asks for MFA on medium and high sign-in risk. The Sign-in activity report lists every risky sign-in.</t>
+          <t>Have each listed admin register a passkey (in Microsoft Authenticator or on a security key) or Windows Hello for Business, then require the Phishing-resistant MFA authentication strength for admin roles in Conditional Access. Codes and push approvals can be relayed by a fake sign-in page; these can't.</t>
         </is>
       </c>
     </row>
@@ -2421,27 +2431,231 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
+          <t>Nobody relies on a text or call as their only second factor</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Ask these people to set up the Microsoft Authenticator app (the registration campaign in the authentication methods policy prompts them at sign-in), then turn off text message and voice call sign-in, or keep them only as a backup. Texts and calls can be intercepted or moved to an attacker's SIM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Licences</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Every licence assignment works</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Every licence assignment worked</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Fix each failed licence from the group's Licenses page in the Entra admin center: buy more licences when there aren't enough, remove licences that conflict, and correct usage locations. The Licences and subscriptions report explains each error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Licences</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>No subscriptions are about to lapse</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>2 subscriptions checked; none is lapsing</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Renew subscriptions in their grace period, buy or cancel trials people use before they end, and move people off suspended subscriptions. Billing &gt; Your products in the Microsoft 365 admin center (or Partner Center for subscriptions you sell) shows each one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>No risky sign-ins succeeded</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Sign-in risk needs Entra ID P2</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Check each sign-in with the person. If they don't recognise it, reset their password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised in Entra ID Protection. Add a Conditional Access policy that asks for MFA on medium and high sign-in risk. The Sign-in activity report lists every risky sign-in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
           <t>No accounts are at risk in Entra ID Protection</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Not checked</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>Risky users need Entra ID P2</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>Check each account with the person. If they don't recognise recent sign-ins, reset the password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised or dismiss the risk in Entra ID Protection. Add a Conditional Access policy that asks for a secure password change on high user risk. The Risky users report lists each account.</t>
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>No account reports to a blocked manager</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>1 account reports to a blocked manager</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Set a current manager on each listed account (Entra admin center &gt; Users &gt; Properties &gt; Manager, or in on-premises AD for synced accounts). The manager is where approvals, leaver notices and access reviews go; when they've left, those go nowhere, and their blocked account is usually waiting to be deleted too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>No mailbox is nearly full</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>3 mailboxes at or over 90% of quota</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Turn on the online archive for each listed mailbox (Exchange admin center &gt; Mailboxes &gt; Manage mailbox archive) with a retention policy that moves old mail into it, or clear large old items. A mailbox at its quota can't send, and soon after can't receive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>No OneDrive is nearly full</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>None of 54 OneDrives is over 90% of its quota</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Ask each listed person to clear or archive old files, or raise their OneDrive quota (SharePoint admin center &gt; Settings &gt; OneDrive Storage limit, up to 5 TB with a qualifying licence). A full OneDrive stops syncing and saving.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F55"/>
+  <autoFilter ref="A1:F62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -2461,7 +2675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2572,7 +2786,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>1 guest admin assignment</t>
+          <t>1 guest with admin roles</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4323,7 +4537,7 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Set domain authentication by mallory.quinn@fabrikam.example on 8 Oct 2026</t>
+          <t>Set domain authentication by mallory.quinn@fabrikam.example on 9 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4335,105 +4549,105 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Clients (Finance / Documents)</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Anyone can edit, link never expires</t>
+          <t>No enabled owner (Microsoft 365 group)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>holiday.jpg (OneDrive of anna.kowalski@fabrikam.example)</t>
+          <t>Old Projects</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Anyone can view</t>
+          <t>No enabled owner (site administrators)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>aaron.smith@fabrikam.example</t>
+          <t>Practice Management</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 21 Apr 2026</t>
+          <t>One owner (Microsoft 365 group)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>aisha.brown@fabrikam.example</t>
+          <t>Staff Intranet</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 5 Mar 2026</t>
+          <t>One owner (site administrators)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>1 guest with full control of 1 site</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jack.lee@fabrikam.example</t>
+          <t>accounts@hollis-partners.example on Finance</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 2 Jun 2026</t>
+          <t>Full Control, given Full Control directly</t>
         </is>
       </c>
     </row>
@@ -4450,12 +4664,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>noah.wood@fabrikam.example</t>
+          <t>aaron.smith@fabrikam.example</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 5 Feb 2026</t>
+          <t>Licensed member, last signed in 22 Apr 2026</t>
         </is>
       </c>
     </row>
@@ -4472,12 +4686,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>rhys.walker@fabrikam.example</t>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 3 Jun 2026</t>
+          <t>Licensed member, last signed in 6 Mar 2026</t>
         </is>
       </c>
     </row>
@@ -4494,19 +4708,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>zara.edwards@fabrikam.example</t>
+          <t>jack.lee@fabrikam.example</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 7 Jul 2026</t>
+          <t>Licensed member, last signed in 3 Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -4516,12 +4730,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>g#EXT#@fabrikam.example</t>
+          <t>noah.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Guest, never signed in, created ?</t>
+          <t>Licensed member, last signed in 6 Feb 2026</t>
         </is>
       </c>
     </row>
@@ -4533,17 +4747,17 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
+          <t>7 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator; signs in with Authenticator app</t>
+          <t>Licensed member, last signed in 4 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -4555,39 +4769,39 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
+          <t>7 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>zara.edwards@fabrikam.example</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator; signs in with no MFA method at all</t>
+          <t>Licensed member, last signed in 8 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>1 app with privileged roles</t>
+          <t>7 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Some app</t>
+          <t>g#EXT#@fabrikam.example</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>App holding Exchange Administrator</t>
+          <t>Guest, never signed in, created ?</t>
         </is>
       </c>
     </row>
@@ -4599,17 +4813,17 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>Users can consent to any app</t>
+          <t>2 admins without a phishing-resistant method</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Any user can grant any app access to their mail and files</t>
+          <t>Global Administrator; signs in with Authenticator app</t>
         </is>
       </c>
     </row>
@@ -4621,17 +4835,17 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>2 admins without a phishing-resistant method</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
+          <t>Global Administrator; signs in with no MFA method at all</t>
         </is>
       </c>
     </row>
@@ -4643,17 +4857,17 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>1 app with privileged roles</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
+          <t>Some app</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
+          <t>App holding Exchange Administrator</t>
         </is>
       </c>
     </row>
@@ -4665,22 +4879,17 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>Users can consent to any app</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Any user can grant any app access to their mail and files</t>
         </is>
       </c>
     </row>
@@ -4697,7 +4906,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -4719,7 +4928,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -4741,12 +4950,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
           <t>Not compliant</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4977,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -4785,7 +4999,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -4807,7 +5021,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -4824,17 +5038,17 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>1 mail domain without DKIM</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 DKIM isn't set up (selector2 CNAME missing)</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
@@ -4846,39 +5060,39 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>DMARC is monitor-only (p=none); spoofed mail is still delivered</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>parked.example</t>
+          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>Doesn't receive mail but has no DMARC p=reject record</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
@@ -4890,39 +5104,39 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>3 teams and groups without an owner</t>
+          <t>1 mail domain without DKIM</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Project Phoenix</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Team, only owner is disabled (Ben Okafor)</t>
+          <t>Microsoft 365 DKIM isn't set up (selector2 CNAME missing)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>3 teams and groups without an owner</t>
+          <t>2 domains without DMARC enforcement</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, no owner</t>
+          <t>DMARC is monitor-only (p=none); spoofed mail is still delivered</t>
         </is>
       </c>
     </row>
@@ -4934,17 +5148,17 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>3 teams and groups without an owner</t>
+          <t>2 domains without DMARC enforcement</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Provisioned</t>
+          <t>parked.example</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, owned only by an app (Provisioning app)</t>
+          <t>Doesn't receive mail but has no DMARC p=reject record</t>
         </is>
       </c>
     </row>
@@ -4956,311 +5170,286 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>Enforced by Require MFA for all users, with 1 exclusion to review</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>Project Phoenix</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Excluded from "Require MFA for all users"</t>
+          <t>Team, only owner is disabled (Ben Okafor)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>1 disabled account still licensed</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ben.okafor@fabrikam.example</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Disabled, holding 1 licence</t>
+          <t>Microsoft 365 group, only owner is disabled (Ben Okafor)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including anonymous links</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SharePoint and OneDrive</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Anyone links are allowed</t>
+          <t>Microsoft 365 group, no owner</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tenant SharePoint storage</t>
+          <t>Provisioned</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Microsoft 365 group, owned only by an app (Provisioning app)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>Enforced by Require MFA for all users, with 1 exclusion to review</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/finance</t>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Excluded from "Require MFA for all users"</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>1 disabled account still licensed</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/imaging</t>
+          <t>ben.okafor@fabrikam.example</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Disabled, holding 1 licence</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>Anyone, including anonymous links</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/marketing</t>
+          <t>SharePoint and OneDrive</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Anyone links are allowed</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>2 files and folders shared with anyone</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/patient-records</t>
+          <t>holiday.jpg (OneDrive of anna.kowalski@fabrikam.example)</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Anyone can view</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>2 files and folders shared with anyone</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/practice</t>
+          <t>Open day flyer.pdf (Marketing / Documents)</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Anyone can view, link never expires</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>1 app registration with expiring or expired credentials</t>
+          <t>2 files and folders outside people can edit</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Old connector</t>
+          <t>Budget.xlsx (Finance / Documents)</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>The 1 credential expired, last on 1 Jan 2025</t>
+          <t>Can be edited by accountant@hargreaves-partners.example</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>1 of 55 joined computers not in Intune</t>
+          <t>2 files and folders outside people can edit</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DESK-RECEPTION</t>
+          <t>Lab dockets (Patient Records / Documents)</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Hybrid joined, not managed by Intune</t>
+          <t>Can be edited by orders@dentallab.example</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>3 mailboxes at or over 90% of quota</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
+          <t>accounts@fabrikam.example</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>44.8 GB of 49.5 GB (91%), no archive</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>3 mailboxes at or over 90% of quota</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>47.2 GB of 49.5 GB (95%), no archive</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5272,44 +5461,54 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>3 mailboxes at or over 90% of quota</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+          <t>thomas.robinson@fabrikam.example</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>45.6 GB of 49.5 GB (92%), no archive</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+          <t>Tenant SharePoint storage</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5321,17 +5520,22 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>https://fabrikam.sharepoint.com/sites/finance</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 45 days ago</t>
+          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5343,17 +5547,22 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>1 of 57 device records unused for 90+ days</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>OLD-PC</t>
+          <t>https://fabrikam.sharepoint.com/sites/imaging</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Windows, last seen 200 days ago</t>
+          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5365,17 +5574,22 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>1 domain with SPF problems</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>parked.example</t>
+          <t>https://fabrikam.sharepoint.com/sites/marketing</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Doesn't receive mail but has no "v=spf1 -all" record to stop spoofing</t>
+          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5387,17 +5601,22 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>https://fabrikam.sharepoint.com/sites/patient-records</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>No MTA-STS policy, so mail sent to this domain can be forced onto an unencrypted connection</t>
+          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5409,17 +5628,22 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is on for the organisation</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>https://fabrikam.sharepoint.com/sites/practice</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is allowed</t>
+          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5431,17 +5655,17 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including guests, can invite guests</t>
+          <t>1 account reports to a blocked manager</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Guests can invite other guests</t>
+          <t>Reports to Ben Okafor, whose sign-in is blocked</t>
         </is>
       </c>
     </row>
@@ -5453,17 +5677,17 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>1 app registration with expiring or expired credentials</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>george.baker@fabrikam.example</t>
+          <t>Old connector</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>The 1 credential expired, last on 1 Jan 2025</t>
         </is>
       </c>
     </row>
@@ -5475,22 +5699,17 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>1 of 55 joined computers not in Intune</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>owen.robinson@fabrikam.example</t>
+          <t>DESK-RECEPTION</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Hybrid joined, not managed by Intune</t>
         </is>
       </c>
     </row>
@@ -5502,17 +5721,17 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>owen.turner@fabrikam.example</t>
+          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>Last check-in 38 days ago</t>
         </is>
       </c>
     </row>
@@ -5524,17 +5743,22 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>thomas.allen@fabrikam.example</t>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>Last check-in 38 days ago</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5546,17 +5770,17 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions with spare licences</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Microsoft 365 Business Basic</t>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>2 of 13 unassigned, 9.80 GBP/month</t>
+          <t>Last check-in 38 days ago</t>
         </is>
       </c>
     </row>
@@ -5568,17 +5792,17 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions with spare licences</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Microsoft 365 Business Premium</t>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>3 of 46 unassigned, 54.30 GBP/month</t>
+          <t>Last check-in 38 days ago</t>
         </is>
       </c>
     </row>
@@ -5590,22 +5814,291 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
+          <t>5 devices haven't checked in for 30+ days</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>Last check-in 45 days ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>1 of 57 device records unused for 90+ days</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>OLD-PC</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>Windows, last seen 200 days ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>1 domain with SPF problems</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>parked.example</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>Doesn't receive mail but has no "v=spf1 -all" record to stop spoofing</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>No MTA-STS policy, so mail sent to this domain can be forced onto an unencrypted connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>SMTP AUTH is on for the organisation</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Whole organisation</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>SMTP AUTH is allowed</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>Anyone, including guests, can invite guests</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Whole organisation</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>Guests can invite other guests</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>george.baker@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>owen.robinson@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>owen.turner@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>thomas.allen@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>2 subscriptions with spare licences</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Microsoft 365 Business Basic</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>2 of 13 unassigned, 9.80 GBP/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>2 subscriptions with spare licences</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Microsoft 365 Business Premium</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>3 of 46 unassigned, 54.30 GBP/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
           <t>Any user can register an app</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>Whole organisation</t>
         </is>
       </c>
-      <c r="D139" s="7" t="inlineStr">
+      <c r="D151" s="7" t="inlineStr">
         <is>
           <t>Users can register apps that nobody reviews</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E139"/>
+  <autoFilter ref="A1:E151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -5779,7 +6272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -5811,7 +6304,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5826,7 +6319,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5841,7 +6334,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5856,7 +6349,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5871,7 +6364,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5886,7 +6379,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -5901,7 +6394,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5916,7 +6409,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -5931,7 +6424,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -5946,7 +6439,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -5961,7 +6454,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -5976,7 +6469,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -5991,7 +6484,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6006,7 +6499,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>46305.87167824074</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -6021,7 +6514,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6036,7 +6529,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6051,7 +6544,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6066,7 +6559,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6081,7 +6574,7 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.80025462963</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6096,7 +6589,7 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6111,7 +6604,7 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6126,7 +6619,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6141,7 +6634,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6156,7 +6649,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6171,7 +6664,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6186,7 +6679,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6201,7 +6694,7 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -6216,7 +6709,7 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -6231,7 +6724,7 @@
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6242,11 +6735,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Microsoft 365 usage</t>
+          <t>Site access</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -6257,11 +6750,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>App sign-ins</t>
+          <t>Site permissions</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -6272,11 +6765,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Group nesting</t>
+          <t>Microsoft 365 usage</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>46305.87168981481</v>
+        <v>46306.8002662037</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -6287,20 +6780,95 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Teams</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n">
+        <v>46306.8002662037</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Mail flow</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n">
+        <v>46306.8002662037</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>App sign-ins</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>46306.8002662037</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Group nesting</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n">
+        <v>46306.8002662037</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Departments and managers</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
-        <v>46305.87168981481</v>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B38" s="12" t="n">
+        <v>46306.8002662037</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>Up to date</t>
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Administrative units</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n">
+        <v>46306.8002662037</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C34"/>
+  <autoFilter ref="A1:C39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -15,13 +15,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$F$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$F$69</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checks'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$164</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Findings'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Licences'!$A$1:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Licences'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Data freshness'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,11 +107,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -512,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 11 Oct 2026, 19:13 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 12 Oct 2026, 04:02 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -552,7 +555,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>31% on 13 Sep 2026</t>
+          <t>31% on 14 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -562,12 +565,12 @@
           <t>Users with MFA</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="8" t="n">
         <v>0.509</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>47.8% on 13 Sep 2026</t>
+          <t>46.2% on 14 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -577,12 +580,12 @@
           <t>Privileged accounts</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="9" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>4 on 13 Sep 2026</t>
+          <t>4 on 14 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -592,12 +595,12 @@
           <t>Licensed users</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="9" t="n">
         <v>54</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>50 on 13 Sep 2026</t>
+          <t>51 on 14 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -607,7 +610,7 @@
           <t>Inactive accounts</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="10" t="n">
         <v>7</v>
       </c>
       <c r="C11" s="7" t="n"/>
@@ -618,7 +621,7 @@
           <t>Licence waste / month (GBP)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="9" t="n">
         <v>164.4</v>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -629,12 +632,12 @@
           <t>Checks needing attention</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>40</v>
+      <c r="B13" s="10" t="n">
+        <v>46</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>1 critical, 28 high, 59 medium, 62 low findings</t>
+          <t>1 critical, 30 high, 69 medium, 63 low findings</t>
         </is>
       </c>
     </row>
@@ -644,8 +647,8 @@
           <t>Checks passed</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>14</v>
+      <c r="B14" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="C14" s="7" t="n"/>
     </row>
@@ -655,7 +658,7 @@
           <t>Not checked</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="10" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -679,13 +682,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Checks</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
-        <v>61</v>
+      <c r="B18" s="10" t="n">
+        <v>68</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -694,13 +697,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
-        <v>150</v>
+      <c r="B19" s="10" t="n">
+        <v>163</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -709,12 +712,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Licences</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="10" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -724,13 +727,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Data freshness</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
-        <v>38</v>
+      <c r="B21" s="10" t="n">
+        <v>40</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -764,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -830,7 +833,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>Enforced by Require MFA for all users, with 1 exclusion to review</t>
+          <t>Enforced by CA002 — All users: Require MFA, with 1 exclusion to review</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -1334,44 +1337,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Third-party apps hold only the access they need</t>
+          <t>No mail flow rule lets mail skip spam filtering</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>1 app with access to mail, files or the directory</t>
+          <t>No mail flow rule skips spam filtering (3 rules checked)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Review each app with the client. Remove apps nobody recognises (Enterprise applications &gt; Delete), and for the rest confirm the vendor and that it still needs mailbox or file access.</t>
+          <t>Remove mail flow rules that skip spam filtering (set the spam confidence level to -1) for senders picked by their address, domain or a header, which anyone can fake. For mail arriving through another filtering service use enhanced filtering on its inbound connector instead, and for a partner limit the rule to the addresses of their sending servers.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Users can't consent to apps on their own</t>
+          <t>No mail flow rule sends mail outside the organisation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1381,29 +1379,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Users can consent to any app</t>
+          <t>1 mail flow rule sends mail outside the organisation</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Set user consent to "Allow user consent for apps from verified publishers, for selected permissions" or turn it off and use the admin consent workflow. Consent phishing relies on this setting.</t>
+          <t>Check each rule that redirects mail or sends copies to an outside address with the client, and remove it unless there's a documented reason (a journaling or archiving service). Attackers with admin access add these rules to read a whole organisation's mail.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>App secrets and certificates are current</t>
+          <t>No sender domains are allowed past the spam filter</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1413,56 +1411,61 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>1 app registration with expiring or expired credentials</t>
+          <t>2 sender domains skip the spam filter</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Renew credentials before they expire to avoid an outage, and delete app registrations whose credentials have all expired if nothing uses them any more.</t>
+          <t>Remove the allowed sender domains from the anti-spam policies: anyone can send mail claiming to be from a domain, so it skips spam and spoofing checks. Where a partner's mail is wrongly caught, report it to Microsoft or add an allow entry for their spoofed sender in the Tenant Allow/Block List instead.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tenant settings</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Users can't create new tenants</t>
+          <t>Spoof protection is on</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Microsoft didn't return this setting</t>
+          <t>1 anti-phishing policy weakens spoof protection</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Set "Restrict non-admin users from creating tenants" to Yes (Entra admin center &gt; Users &gt; User settings). A tenant a user creates sits outside the client's policies, with that user as its Global Administrator.</t>
+          <t>Turn spoof intelligence and “Honour DMARC policy” back on in the anti-phishing policies (both are on by default). Without them, mail pretending to be from other organisations' domains is delivered.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tenant settings</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Users can't register apps</t>
+          <t>Risky attachment types are blocked</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1472,142 +1475,152 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Any user can register an app</t>
+          <t>1 anti-malware policy lets risky attachment types through</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Set "Users can register applications" to No (Entra admin center &gt; Users &gt; User settings) and give the Application Developer role to the people who need it.</t>
+          <t>Turn on the common attachments filter in the anti-malware policies (it's on by default), so program files, disk images and scripts (.exe, .iso, .js and the like) are quarantined rather than delivered.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tenant settings</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Guests have limited directory access</t>
+          <t>Third-party apps hold only the access they need</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Guests have limited access to directory objects (the default)</t>
+          <t>1 app with access to mail, files or the directory</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Set guest user access to "Guest users have limited access to properties and memberships of directory objects", or to the most restrictive option (Entra admin center &gt; External Identities &gt; External collaboration settings).</t>
+          <t>Review each app with the client. Remove apps nobody recognises (Enterprise applications &gt; Delete), and for the rest confirm the vendor and that it still needs mailbox or file access.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tenant settings</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>People can't join the tenant just by verifying an email address</t>
+          <t>Users can't consent to apps on their own</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Microsoft didn't return this setting</t>
+          <t>Users can consent to any app</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Turn off email-verified sign-up with Microsoft Graph PowerShell (Update-MgPolicyAuthorizationPolicy -AllowEmailVerifiedUsersToJoinOrganization:$false), so accounts are only created by admins or invitation.</t>
+          <t>Set user consent to "Allow user consent for apps from verified publishers, for selected permissions" or turn it off and use the admin consent workflow. Consent phishing relies on this setting.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tenant settings</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Users have a way to get apps approved</t>
+          <t>App secrets and certificates are current</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Users can consent to most apps themselves, so admin consent requests are off (see the user consent check)</t>
+          <t>1 app registration with expiring or expired credentials</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Turn on admin consent requests (Entra admin center &gt; Enterprise apps &gt; Consent and permissions &gt; Admin consent settings) and choose reviewers, so users blocked from consenting can ask instead of looking for a workaround.</t>
+          <t>Renew credentials before they expire to avoid an outage, and delete app registrations whose credentials have all expired if nothing uses them any more.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sharing</t>
+          <t>Tenant settings</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Files can't be shared with anonymous links</t>
+          <t>Users can't create new tenants</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including anonymous links</t>
+          <t>Microsoft didn't return this setting</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Change SharePoint external sharing to "New and existing guests" so every external person signs in. If the client relies on Anyone links, set them to expire and to view-only.</t>
+          <t>Set "Restrict non-admin users from creating tenants" to Yes (Entra admin center &gt; Users &gt; User settings). A tenant a user creates sits outside the client's policies, with that user as its Global Administrator.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Tenant settings</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Only admins and members can invite guests</t>
+          <t>Users can't register apps</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1622,24 +1635,24 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including guests, can invite guests</t>
+          <t>Any user can register an app</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Restrict guest invitations to admins and the Guest Inviter role, or at least to members, under External collaboration settings.</t>
+          <t>Set "Users can register applications" to No (Entra admin center &gt; Users &gt; User settings) and give the Application Developer role to the people who need it.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Tenant settings</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>No old, unaccepted guest invitations</t>
+          <t>Guests have limited directory access</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1649,83 +1662,78 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>No stale guest invitations</t>
+          <t>Guests have limited access to directory objects (the default)</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Delete guest accounts whose invitation has gone unaccepted for 30 days; re-invite if still needed.</t>
+          <t>Set guest user access to "Guest users have limited access to properties and memberships of directory objects", or to the most restrictive option (Entra admin center &gt; External Identities &gt; External collaboration settings).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Tenant settings</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Mail domains require encrypted delivery (MTA-STS)</t>
+          <t>People can't join the tenant just by verifying an email address</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
+          <t>Microsoft didn't return this setting</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Publish an MTA-STS policy so other mail servers only deliver to the domain over a verified, encrypted connection: a TXT record at _mta-sts.&lt;domain&gt; ("v=STSv1; id=20260101") and a policy file at https://mta-sts.&lt;domain&gt;/.well-known/mta-sts.txt listing the domain's MX hosts (for Microsoft 365, "mx: *.mail.protection.outlook.com"). Start with "mode: testing" and TLS-RPT reports, then switch to "mode: enforce" and change the id.</t>
+          <t>Turn off email-verified sign-up with Microsoft Graph PowerShell (Update-MgPolicyAuthorizationPolicy -AllowEmailVerifiedUsersToJoinOrganization:$false), so accounts are only created by admins or invitation.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Tenant settings</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Encrypted delivery failures are reported (TLS-RPT)</t>
+          <t>Users have a way to get apps approved</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>TLS-RPT is checked on mail domains that use MTA-STS, and none do yet</t>
+          <t>Users can consent to most apps themselves, so admin consent requests are off (see the user consent check)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Publish a TXT record at _smtp._tls.&lt;domain&gt; such as "v=TLSRPTv1; rua=mailto:tls-reports@&lt;domain&gt;" (or a reporting service's address), so someone hears when other servers can't deliver mail encrypted, before and after MTA-STS is enforced.</t>
+          <t>Turn on admin consent requests (Entra admin center &gt; Enterprise apps &gt; Consent and permissions &gt; Admin consent settings) and choose reviewers, so users blocked from consenting can ask instead of looking for a workaround.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Every domain has a working SPF record</t>
+          <t>Files can't be shared with anonymous links</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1735,29 +1743,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>1 domain with SPF problems</t>
+          <t>Anyone, including anonymous links</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Publish one SPF record per domain ending in -all (or ~all while testing), e.g. "v=spf1 include:spf.protection.outlook.com -all". Domains that never send mail should publish "v=spf1 -all".</t>
+          <t>Change SharePoint external sharing to "New and existing guests" so every external person signs in. If the client relies on Anyone links, set them to expire and to view-only.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Every domain enforces DMARC</t>
+          <t>Only admins and members can invite guests</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1767,61 +1775,56 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
+          <t>Anyone, including guests, can invite guests</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Publish a DMARC record with a rua= reporting address, start at p=none to see who sends as the domain, then move to p=quarantine and p=reject. Without enforcement, spoofed mail from the domain is delivered.</t>
+          <t>Restrict guest invitations to admins and the Guest Inviter role, or at least to members, under External collaboration settings.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>DKIM signing is on for every mail domain</t>
+          <t>No old, unaccepted guest invitations</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>1 mail domain without DKIM</t>
+          <t>No stale guest invitations</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Turn on DKIM for each domain in the Defender portal (Email authentication settings &gt; DKIM), publishing the two selector CNAME records it shows. This applies to domains behind a mail gateway too when Microsoft 365 still sends for them (their SPF includes spf.protection.outlook.com); a gateway signs only the mail that goes out through it.</t>
+          <t>Delete guest accounts whose invitation has gone unaccepted for 30 days; re-invite if still needed.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Every team and Microsoft 365 group has an owner</t>
+          <t>Mail domains require encrypted delivery (MTA-STS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1831,110 +1834,120 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
+          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Make an active person, ideally two, an owner of each listed team or group (Teams admin center or Microsoft 365 admin center &gt; Teams &amp; groups). Owners approve members and guests and renew the group; without one, nobody looks after its files and conversations. The ownerless group policy (Microsoft 365 admin center &gt; Settings &gt; Org settings &gt; Microsoft 365 Groups) asks members to take over when the last owner leaves.</t>
+          <t>Publish an MTA-STS policy so other mail servers only deliver to the domain over a verified, encrypted connection: a TXT record at _mta-sts.&lt;domain&gt; ("v=STSv1; id=20260101") and a policy file at https://mta-sts.&lt;domain&gt;/.well-known/mta-sts.txt listing the domain's MX hosts (for Microsoft 365, "mx: *.mail.protection.outlook.com"). Start with "mode: testing" and TLS-RPT reports, then switch to "mode: enforce" and change the id.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>No guest owns a team or group</t>
+          <t>Encrypted delivery failures are reported (TLS-RPT)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>No guest owns any of 9 teams and groups</t>
+          <t>TLS-RPT is checked on mail domains that use MTA-STS, and none do yet</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Make a member of the organisation the owner of each listed team or group and remove the guest as owner (Teams admin center, or Microsoft 365 admin center &gt; Teams &amp; groups). An owner from outside can add members and guests, change settings and see everything in it, and nobody here is accountable for that.</t>
+          <t>Publish a TXT record at _smtp._tls.&lt;domain&gt; such as "v=TLSRPTv1; rua=mailto:tls-reports@&lt;domain&gt;" (or a reporting service's address), so someone hears when other servers can't deliver mail encrypted, before and after MTA-STS is enforced.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Only chosen people can create teams and groups</t>
+          <t>Every domain has a working SPF record</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Only admins and members of Group creators can create teams and groups</t>
+          <t>1 domain with SPF problems</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Limit who can create teams and Microsoft 365 groups to a security group of people who will look after them (the Group.Unified directory setting, changed with Microsoft Graph PowerShell; needs Entra ID P1). Otherwise anyone can create a team, add guests to it and leave it behind.</t>
+          <t>Publish one SPF record per domain ending in -all (or ~all while testing), e.g. "v=spf1 include:spf.protection.outlook.com -all". Domains that never send mail should publish "v=spf1 -all".</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Unused groups and teams expire</t>
+          <t>Every domain enforces DMARC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Unused teams and groups expire after 365 days</t>
+          <t>2 domains without DMARC enforcement</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Set a Microsoft 365 group expiration policy for all groups (Entra admin center &gt; Groups &gt; Expiration), for example 365 days. Groups in use renew automatically, owners are asked to renew the rest, and an expired group can be restored for 30 days. Needs Entra ID P1.</t>
+          <t>Publish a DMARC record with a rua= reporting address, start at p=none to see who sends as the domain, then move to p=quarantine and p=reject. Without enforcement, spoofed mail from the domain is delivered.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Managed devices meet compliance policies</t>
+          <t>DKIM signing is on for every mail domain</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1949,24 +1962,24 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>1 mail domain without DKIM</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Open each non-compliant device in Intune (Devices &gt; Monitor &gt; Noncompliant devices) to see which setting fails, fix it or retire the device, and block non-compliant devices with a Conditional Access policy that requires a compliant device.</t>
+          <t>Turn on DKIM for each domain in the Defender portal (Email authentication settings &gt; DKIM), publishing the two selector CNAME records it shows. This applies to domains behind a mail gateway too when Microsoft 365 still sends for them (their SPF includes spf.protection.outlook.com); a gateway signs only the mail that goes out through it.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Company computers are encrypted</t>
+          <t>Every team and Microsoft 365 group has an owner</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1976,113 +1989,98 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>6 of 54 computers not encrypted</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Turn on BitLocker (Windows) and FileVault (macOS) with an Intune disk encryption policy, with recovery keys escrowed to Entra ID, so a lost or stolen laptop doesn't expose the client's data.</t>
+          <t>Make an active person, ideally two, an owner of each listed team or group (Teams admin center or Microsoft 365 admin center &gt; Teams &amp; groups). Owners approve members and guests and renew the group; without one, nobody looks after its files and conversations. The ownerless group policy (Microsoft 365 admin center &gt; Settings &gt; Org settings &gt; Microsoft 365 Groups) asks members to take over when the last owner leaves.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Windows computers still get security updates</t>
+          <t>No guest owns a team or group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
+          <t>No guest owns any of 9 teams and groups</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Upgrade computers on Windows 10 or an old Windows 11 release to the current Windows 11 release (Intune: Windows feature updates policy). Replace hardware that can't run Windows 11, or buy Extended Security Updates as a stopgap.</t>
+          <t>Make a member of the organisation the owner of each listed team or group and remove the guest as owner (Teams admin center, or Microsoft 365 admin center &gt; Teams &amp; groups). An owner from outside can add members and guests, change settings and see everything in it, and nobody here is accountable for that.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Joined computers are managed by Intune</t>
+          <t>Only chosen people can create teams and groups</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>1 of 55 joined computers not in Intune</t>
+          <t>Only admins and members of Group creators can create teams and groups</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Enrol Entra-joined and hybrid-joined computers in Intune (automatic enrolment under Devices &gt; Enrollment &gt; Windows) so compliance, encryption and updates can be enforced on them.</t>
+          <t>Limit who can create teams and Microsoft 365 groups to a security group of people who will look after them (the Group.Unified directory setting, changed with Microsoft Graph PowerShell; needs Entra ID P1). Otherwise anyone can create a team, add guests to it and leave it behind.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Managed devices check in with Intune</t>
+          <t>Unused groups and teams expire</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>Unused teams and groups expire after 365 days</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Find out whether each device is lost, replaced or broken. Retire devices that are gone; for devices still in use, restart the Intune Management Extension or re-enrol.</t>
+          <t>Set a Microsoft 365 group expiration policy for all groups (Entra admin center &gt; Groups &gt; Expiration), for example 365 days. Groups in use renew automatically, owners are asked to renew the rest, and an expired group can be restored for 30 days. Needs Entra ID P1.</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2092,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>No old devices left in Entra ID</t>
+          <t>Managed devices meet compliance policies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2104,110 +2102,125 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>1 of 57 device records unused for 90+ days</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Disable, then after 30 days delete, device records that haven't signed in for 90 days (Entra admin center &gt; Devices &gt; All devices, filter by activity). Old records can still hold BitLocker keys and count toward device limits.</t>
+          <t>Open each non-compliant device in Intune (Devices &gt; Monitor &gt; Noncompliant devices) to see which setting fails, fix it or retire the device, and block non-compliant devices with a Conditional Access policy that requires a compliant device.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hybrid identity</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Directory sync is running</t>
+          <t>Company computers are encrypted</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Cloud-only tenant: directory sync isn't turned on</t>
+          <t>6 of 54 computers not encrypted</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Check the Entra Connect server: that it is up, the Microsoft Azure AD Sync service is running and Synchronization Service Manager shows no errors. Until sync runs, accounts disabled or removed in Active Directory keep working in Microsoft 365. If the client has moved to cloud-only, turn directory sync off.</t>
+          <t>Turn on BitLocker (Windows) and FileVault (macOS) with an Intune disk encryption policy, with recovery keys escrowed to Entra ID, so a lost or stolen laptop doesn't expose the client's data.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hybrid identity</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Password hash sync is on</t>
+          <t>Windows computers still get security updates</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Cloud-only tenant: directory sync isn't turned on</t>
+          <t>7 of 54 Windows computers past end of support</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Turn on password hash synchronization in Entra Connect (Optional features), even when users sign in through federation or pass-through authentication. Entra ID can then detect leaked passwords, and sign-in can be switched to the cloud if the on-premises servers are down.</t>
+          <t>Upgrade computers on Windows 10 or an old Windows 11 release to the current Windows 11 release (Intune: Windows feature updates policy). Replace hardware that can't run Windows 11, or buy Extended Security Updates as a stopgap.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hybrid identity</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Admin accounts are cloud-only</t>
+          <t>Joined computers are managed by Intune</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Cloud-only tenant: no accounts are synced from on-premises AD</t>
+          <t>1 of 55 joined computers not in Intune</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Give each admin a separate cloud-only account (for example on the .onmicrosoft.com domain) for their admin roles, and remove the roles from accounts synced from Active Directory. Otherwise anyone who takes over on-premises AD can reset those passwords and become an admin in Microsoft 365.</t>
+          <t>Enrol Entra-joined and hybrid-joined computers in Intune (automatic enrolment under Devices &gt; Enrollment &gt; Windows) so compliance, encryption and updates can be enforced on them.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>No unexpected changes to how domains sign in</t>
+          <t>Managed devices check in with Intune</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2217,29 +2230,29 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>1 domain had sign-in settings changed in the last 30 days</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Confirm with the client that each change was planned (for example, setting up AD FS or another identity provider). If it wasn't, an attacker with admin rights may have federated the domain to their own identity provider so they can sign in as any user without a password or MFA: switch the domain back to managed sign-in, remove unknown federation settings, reset admin credentials and review the audit log.</t>
+          <t>Find out whether each device is lost, replaced or broken. Retire devices that are gone; for devices still in use, restart the Intune Management Extension or re-enrol.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sharing</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>No files are shared with anyone links</t>
+          <t>No old devices left in Entra ID</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2249,29 +2262,29 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
+          <t>1 of 57 device records unused for 90+ days</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Remove anyone links that are no longer needed, and set the rest to view-only with an expiry date. The Shared files report lists each one.</t>
+          <t>Disable, then after 30 days delete, device records that haven't signed in for 90 days (Entra admin center &gt; Devices &gt; All devices, filter by activity). Old records can still hold BitLocker keys and count toward device limits.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>SharePoint storage isn't nearly full</t>
+          <t>Windows computers have their BitLocker recovery key saved</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2286,24 +2299,24 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>8 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Free up space before the tenant runs out, when people can no longer save files. The SharePoint storage report shows where the space goes and what to clear first; otherwise buy Office 365 Extra File Storage.</t>
+          <t>Make Intune's disk encryption policy (Endpoint security &gt; Disk encryption) require the recovery key to be saved in Entra ID before BitLocker turns on, and on computers already encrypted run BackupToAAD-BitLockerKeyProtector (or re-run the policy). Without the key, a computer that asks for it after a firmware or hardware change can't be unlocked, and its data is lost.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sharing</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Every site has at least two owners</t>
+          <t>Every platform in use has a compliance policy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2313,113 +2326,98 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>2 sites with no owner, 2 sites with one owner</t>
+          <t>No compliance policy for iOS/iPadOS</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Give each site a second owner (in the Microsoft 365 group, or as a site administrator) so access requests and content questions have someone to go to when one person leaves. The Site access report lists each site's owners.</t>
+          <t>In Intune (Devices &gt; Compliance), create and assign a compliance policy for each platform with enrolled devices, requiring at least encryption, a screen lock and a minimum OS version, and set devices with no policy to show as not compliant (Compliance settings). Until then those devices count as compliant, so Conditional Access that requires a compliant device lets them through.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sharing</t>
+          <t>Hybrid identity</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Guests don't have full control of sites</t>
+          <t>Directory sync is running</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>1 guest with full control of 1 site</t>
+          <t>Cloud-only tenant: directory sync isn't turned on</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Take guests out of each site's owners group and away from Full Control; give them Edit or Read through the site's members or visitors group instead. Full Control lets someone outside the organisation change who can open the site and delete anything on it. The Site permissions report lists them.</t>
+          <t>Check the Entra Connect server: that it is up, the Microsoft Azure AD Sync service is running and Synchronization Service Manager shows no errors. Until sync runs, accounts disabled or removed in Active Directory keep working in Microsoft 365. If the client has moved to cloud-only, turn directory sync off.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sharing</t>
+          <t>Hybrid identity</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>People outside can only view shared files</t>
+          <t>Password hash sync is on</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders outside people can edit</t>
+          <t>Cloud-only tenant: directory sync isn't turned on</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Change sharing with people outside the organisation to view-only unless they need to edit, and remove sharing that's no longer needed. The File and folder permissions report lists each person outside and what they can edit.</t>
+          <t>Turn on password hash synchronization in Entra Connect (Optional features), even when users sign in through federation or pass-through authentication. Entra ID can then detect leaked passwords, and sign-in can be switched to the cloud if the on-premises servers are down.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Admins</t>
+          <t>Hybrid identity</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Admins use phishing-resistant sign-in methods</t>
+          <t>Admin accounts are cloud-only</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
+          <t>Cloud-only tenant: no accounts are synced from on-premises AD</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Have each listed admin register a passkey (in Microsoft Authenticator or on a security key) or Windows Hello for Business, then require the Phishing-resistant MFA authentication strength for admin roles in Conditional Access. Codes and push approvals can be relayed by a fake sign-in page; these can't.</t>
+          <t>Give each admin a separate cloud-only account (for example on the .onmicrosoft.com domain) for their admin roles, and remove the roles from accounts synced from Active Directory. Otherwise anyone who takes over on-premises AD can reset those passwords and become an admin in Microsoft 365.</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2429,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Nobody relies on a text or call as their only second factor</t>
+          <t>No unexpected changes to how domains sign in</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2441,137 +2439,157 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>1 domain had sign-in settings changed in the last 30 days</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Ask these people to set up the Microsoft Authenticator app (the registration campaign in the authentication methods policy prompts them at sign-in), then turn off text message and voice call sign-in, or keep them only as a backup. Texts and calls can be intercepted or moved to an attacker's SIM.</t>
+          <t>Confirm with the client that each change was planned (for example, setting up AD FS or another identity provider). If it wasn't, an attacker with admin rights may have federated the domain to their own identity provider so they can sign in as any user without a password or MFA: switch the domain back to managed sign-in, remove unknown federation settings, reset admin credentials and review the audit log.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Licences</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Every licence assignment works</t>
+          <t>No files are shared with anyone links</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Every licence assignment worked</t>
+          <t>2 files and folders shared with anyone</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Fix each failed licence from the group's Licenses page in the Entra admin center: buy more licences when there aren't enough, remove licences that conflict, and correct usage locations. The Licences and subscriptions report explains each error.</t>
+          <t>Remove anyone links that are no longer needed, and set the rest to view-only with an expiry date. The Shared files report lists each one.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Licences</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>No subscriptions are about to lapse</t>
+          <t>SharePoint storage isn't nearly full</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions checked; none is lapsing</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Renew subscriptions in their grace period, buy or cancel trials people use before they end, and move people off suspended subscriptions. Billing &gt; Your products in the Microsoft 365 admin center (or Partner Center for subscriptions you sell) shows each one.</t>
+          <t>Free up space before the tenant runs out, when people can no longer save files. The SharePoint storage report shows where the space goes and what to clear first; otherwise buy Office 365 Extra File Storage.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>No risky sign-ins succeeded</t>
+          <t>Every site has at least two owners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>Sign-in risk needs Entra ID P2</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Check each sign-in with the person. If they don't recognise it, reset their password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised in Entra ID Protection. Add a Conditional Access policy that asks for MFA on medium and high sign-in risk. The Sign-in activity report lists every risky sign-in.</t>
+          <t>Give each site a second owner (in the Microsoft 365 group, or as a site administrator) so access requests and content questions have someone to go to when one person leaves. The Site access report lists each site's owners.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>No accounts are at risk in Entra ID Protection</t>
+          <t>Guests don't have full control of sites</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Risky users need Entra ID P2</t>
+          <t>1 guest with full control of 1 site</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Check each account with the person. If they don't recognise recent sign-ins, reset the password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised or dismiss the risk in Entra ID Protection. Add a Conditional Access policy that asks for a secure password change on high user risk. The Risky users report lists each account.</t>
+          <t>Take guests out of each site's owners group and away from Full Control; give them Edit or Read through the site's members or visitors group instead. Full Control lets someone outside the organisation change who can open the site and delete anything on it. The Site permissions report lists them.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Accounts</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>No account reports to a blocked manager</t>
+          <t>People outside can only view shared files</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2581,29 +2599,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>1 account reports to a blocked manager</t>
+          <t>2 files and folders outside people can edit</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Set a current manager on each listed account (Entra admin center &gt; Users &gt; Properties &gt; Manager, or in on-premises AD for synced accounts). The manager is where approvals, leaver notices and access reviews go; when they've left, those go nowhere, and their blocked account is usually waiting to be deleted too.</t>
+          <t>Change sharing with people outside the organisation to view-only unless they need to edit, and remove sharing that's no longer needed. The File and folder permissions report lists each person outside and what they can edit.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Admins</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>No mailbox is nearly full</t>
+          <t>Admins use phishing-resistant sign-in methods</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2618,44 +2636,248 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>3 mailboxes at or over 90% of quota</t>
+          <t>2 admins without a phishing-resistant method</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Turn on the online archive for each listed mailbox (Exchange admin center &gt; Mailboxes &gt; Manage mailbox archive) with a retention policy that moves old mail into it, or clear large old items. A mailbox at its quota can't send, and soon after can't receive.</t>
+          <t>Have each listed admin register a passkey (in Microsoft Authenticator or on a security key) or Windows Hello for Business, then require the Phishing-resistant MFA authentication strength for admin roles in Conditional Access. Codes and push approvals can be relayed by a fake sign-in page; these can't.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Nobody relies on a text or call as their only second factor</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Ask these people to set up the Microsoft Authenticator app (the registration campaign in the authentication methods policy prompts them at sign-in), then turn off text message and voice call sign-in, or keep them only as a backup. Texts and calls can be intercepted or moved to an attacker's SIM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Licences</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Every licence assignment works</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Every licence assignment worked</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Fix each failed licence from the group's Licenses page in the Entra admin center: buy more licences when there aren't enough, remove licences that conflict, and correct usage locations. The Licences and subscriptions report explains each error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Licences</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>No subscriptions are about to lapse</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>2 subscriptions checked; none is lapsing</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Renew subscriptions in their grace period, buy or cancel trials people use before they end, and move people off suspended subscriptions. Billing &gt; Your products in the Microsoft 365 admin center (or Partner Center for subscriptions you sell) shows each one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>No risky sign-ins succeeded</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Sign-in risk needs Entra ID P2</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Check each sign-in with the person. If they don't recognise it, reset their password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised in Entra ID Protection. Add a Conditional Access policy that asks for MFA on medium and high sign-in risk. The Sign-in activity report lists every risky sign-in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>No accounts are at risk in Entra ID Protection</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Risky users need Entra ID P2</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Check each account with the person. If they don't recognise recent sign-ins, reset the password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised or dismiss the risk in Entra ID Protection. Add a Conditional Access policy that asks for a secure password change on high user risk. The Risky users report lists each account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>No account reports to a blocked manager</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>1 account reports to a blocked manager</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Set a current manager on each listed account (Entra admin center &gt; Users &gt; Properties &gt; Manager, or in on-premises AD for synced accounts). The manager is where approvals, leaver notices and access reviews go; when they've left, those go nowhere, and their blocked account is usually waiting to be deleted too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>No mailbox is nearly full</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>3 mailboxes at or over 90% of quota</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Turn on the online archive for each listed mailbox (Exchange admin center &gt; Mailboxes &gt; Manage mailbox archive) with a retention policy that moves old mail into it, or clear large old items. A mailbox at its quota can't send, and soon after can't receive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>No OneDrive is nearly full</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>None of 54 OneDrives is over 90% of its quota</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>Ask each listed person to clear or archive old files, or raise their OneDrive quota (SharePoint admin center &gt; Settings &gt; OneDrive Storage limit, up to 5 TB with a qualifying licence). A full OneDrive stops syncing and saving.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F62"/>
+  <autoFilter ref="A1:F69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -2675,7 +2897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2774,7 +2996,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator: excluded from Require MFA for all users</t>
+          <t>Global Administrator: excluded from CA001 — Admins: Require phishing-resistant MFA, CA002 — All users: Require MFA, CA005 — Block sign-ins from disallowed countries, CA006 — Require MFA for Azure management, CA007 — Admins: No persistent browser, 8h sign-in frequency, CA008 — All users: 8h sign-in frequency, CA009 — Require MFA for device registration, CA010 — Insider risk: Step-up MFA, CA011 — High sign-in risk: Block</t>
         </is>
       </c>
     </row>
@@ -3791,17 +4013,17 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>5 external forwards</t>
+          <t>1 mail flow rule sends mail outside the organisation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>Copy patient letters to archive</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Mailbox forwarding to anna.kowalski@homemail.example (keeps a copy)</t>
+          <t>Sends mail or copies to records@dentalarchive.example</t>
         </is>
       </c>
     </row>
@@ -3823,7 +4045,7 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Inbox rule "Copy to home" forwards to anna.kowalski.home@homemail.example</t>
+          <t>Mailbox forwarding to anna.kowalski@homemail.example (keeps a copy)</t>
         </is>
       </c>
     </row>
@@ -3840,17 +4062,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>rhys.hall@fabrikam.example</t>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Mailbox forwarding to rhys.hall@homemail.example (doesn't keep a copy)</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Inbox rule "Copy to home" forwards to anna.kowalski.home@homemail.example</t>
         </is>
       </c>
     </row>
@@ -3867,12 +4084,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>rhys.walker@fabrikam.example</t>
+          <t>rhys.hall@fabrikam.example</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Mailbox forwarding to rhys.walker@homemail.example (doesn't keep a copy)</t>
+          <t>Mailbox forwarding to rhys.hall@homemail.example (doesn't keep a copy)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3894,12 +4111,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>thomas.robinson@fabrikam.example</t>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Inbox rule "Invoices to bookkeeper" forwards to bookkeeping@ledgerline.example</t>
+          <t>Mailbox forwarding to rhys.walker@homemail.example (doesn't keep a copy)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3911,46 +4133,46 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>5 external forwards</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>thomas.robinson@fabrikam.example</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>No MFA method registered</t>
+          <t>Inbox rule "Invoices to bookkeeper" forwards to bookkeeping@ledgerline.example</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>2 sender domains skip the spam filter</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>aaron.smith@fabrikam.example</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>No MFA method registered</t>
+          <t>Allows mail claiming to be from gmail.com, labpartners.example past the spam filter (gmail.com is free mail or the organisation's own)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -3960,7 +4182,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>aisha.brown@fabrikam.example</t>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -3982,7 +4204,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>amelia.khan@fabrikam.example</t>
+          <t>aaron.smith@fabrikam.example</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -4004,7 +4226,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>arthur.williams@fabrikam.example</t>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -4026,7 +4248,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ava.jackson@fabrikam.example</t>
+          <t>amelia.khan@fabrikam.example</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -4048,7 +4270,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ava.moore@fabrikam.example</t>
+          <t>arthur.williams@fabrikam.example</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -4070,7 +4292,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ava.thomas@fabrikam.example</t>
+          <t>ava.jackson@fabrikam.example</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -4092,7 +4314,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>carl.svensson@fabrikam.example</t>
+          <t>ava.moore@fabrikam.example</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -4114,7 +4336,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>chloe.jackson@fabrikam.example</t>
+          <t>ava.thomas@fabrikam.example</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -4136,7 +4358,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>george.williams@fabrikam.example</t>
+          <t>carl.svensson@fabrikam.example</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -4158,7 +4380,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>henry.roberts@fabrikam.example</t>
+          <t>chloe.jackson@fabrikam.example</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -4180,7 +4402,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>isla.scott@fabrikam.example</t>
+          <t>george.williams@fabrikam.example</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -4202,7 +4424,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jack.lee@fabrikam.example</t>
+          <t>henry.roberts@fabrikam.example</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -4224,7 +4446,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>jack.roberts@fabrikam.example</t>
+          <t>isla.scott@fabrikam.example</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -4246,7 +4468,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>lily.khan@fabrikam.example</t>
+          <t>jack.lee@fabrikam.example</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -4268,7 +4490,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>lily.watson@fabrikam.example</t>
+          <t>jack.roberts@fabrikam.example</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -4290,7 +4512,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>lily.white@fabrikam.example</t>
+          <t>lily.khan@fabrikam.example</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -4312,7 +4534,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>megan.king@fabrikam.example</t>
+          <t>lily.watson@fabrikam.example</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -4334,7 +4556,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>noah.wood@fabrikam.example</t>
+          <t>lily.white@fabrikam.example</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -4356,7 +4578,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>olivia.taylor@fabrikam.example</t>
+          <t>megan.king@fabrikam.example</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -4378,7 +4600,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>owen.scott@fabrikam.example</t>
+          <t>noah.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -4400,7 +4622,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>rhys.walker@fabrikam.example</t>
+          <t>olivia.taylor@fabrikam.example</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -4422,7 +4644,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ruby.davies@fabrikam.example</t>
+          <t>owen.scott@fabrikam.example</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -4444,7 +4666,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ruby.wood@fabrikam.example</t>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4466,7 +4688,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>thomas.johnson@fabrikam.example</t>
+          <t>ruby.davies@fabrikam.example</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -4488,7 +4710,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>zara.edwards@fabrikam.example</t>
+          <t>ruby.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4500,44 +4722,44 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Legacy authentication is allowed</t>
+          <t>27 users without MFA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>thomas.johnson@fabrikam.example</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>No enabled policy blocks legacy authentication for all users</t>
+          <t>No MFA method registered</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>1 domain had sign-in settings changed in the last 30 days</t>
+          <t>27 users without MFA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>zara.edwards@fabrikam.example</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Set domain authentication by mallory.quinn@fabrikam.example on 9 Oct 2026</t>
+          <t>No MFA method registered</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4771,17 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>2 sites with no owner, 2 sites with one owner</t>
+          <t>Legacy authentication is allowed</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>No enabled owner (Microsoft 365 group)</t>
+          <t>No enabled policy blocks legacy authentication for all users</t>
         </is>
       </c>
     </row>
@@ -4571,24 +4793,24 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>2 sites with no owner, 2 sites with one owner</t>
+          <t>1 domain had sign-in settings changed in the last 30 days</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Old Projects</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>No enabled owner (site administrators)</t>
+          <t>Set domain authentication by mallory.quinn@fabrikam.example on 9 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -4598,19 +4820,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Practice Management</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>One owner (Microsoft 365 group)</t>
+          <t>No enabled owner (Microsoft 365 group)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -4620,78 +4842,78 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Staff Intranet</t>
+          <t>Old Projects</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>One owner (site administrators)</t>
+          <t>No enabled owner (site administrators)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>1 guest with full control of 1 site</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>accounts@hollis-partners.example on Finance</t>
+          <t>Practice Management</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Full Control, given Full Control directly</t>
+          <t>One owner (Microsoft 365 group)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>aaron.smith@fabrikam.example</t>
+          <t>Staff Intranet</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 22 Apr 2026</t>
+          <t>One owner (site administrators)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>1 guest with full control of 1 site</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>aisha.brown@fabrikam.example</t>
+          <t>accounts@hollis-partners.example on Finance</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 6 Mar 2026</t>
+          <t>Full Control, given Full Control directly</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4930,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>jack.lee@fabrikam.example</t>
+          <t>aaron.smith@fabrikam.example</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 3 Jun 2026</t>
+          <t>Licensed member, last signed in 22 Apr 2026</t>
         </is>
       </c>
     </row>
@@ -4730,12 +4952,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>noah.wood@fabrikam.example</t>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 6 Feb 2026</t>
+          <t>Licensed member, last signed in 7 Mar 2026</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4974,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>rhys.walker@fabrikam.example</t>
+          <t>jack.lee@fabrikam.example</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 4 Jun 2026</t>
+          <t>Licensed member, last signed in 3 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -4774,19 +4996,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>zara.edwards@fabrikam.example</t>
+          <t>noah.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 8 Jul 2026</t>
+          <t>Licensed member, last signed in 7 Feb 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -4796,12 +5018,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>g#EXT#@fabrikam.example</t>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Guest, never signed in, created ?</t>
+          <t>Licensed member, last signed in 5 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -4813,39 +5035,39 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
+          <t>7 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>zara.edwards@fabrikam.example</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator; signs in with Authenticator app</t>
+          <t>Licensed member, last signed in 8 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
+          <t>7 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>g#EXT#@fabrikam.example</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator; signs in with no MFA method at all</t>
+          <t>Guest, never signed in, created ?</t>
         </is>
       </c>
     </row>
@@ -4857,17 +5079,17 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>1 app with privileged roles</t>
+          <t>2 admins without a phishing-resistant method</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Some app</t>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>App holding Exchange Administrator</t>
+          <t>Global Administrator; signs in with Authenticator app</t>
         </is>
       </c>
     </row>
@@ -4879,17 +5101,17 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Users can consent to any app</t>
+          <t>2 admins without a phishing-resistant method</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Any user can grant any app access to their mail and files</t>
+          <t>Global Administrator; signs in with no MFA method at all</t>
         </is>
       </c>
     </row>
@@ -4901,17 +5123,17 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>1 app with privileged roles</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
+          <t>Some app</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
+          <t>App holding Exchange Administrator</t>
         </is>
       </c>
     </row>
@@ -4923,17 +5145,17 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>Users can consent to any app</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
+          <t>Any user can grant any app access to their mail and files</t>
         </is>
       </c>
     </row>
@@ -4945,22 +5167,17 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>No compliance policy for iOS/iPadOS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>iOS/iPadOS</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>1 enrolled device, no compliance policy assigned</t>
         </is>
       </c>
     </row>
@@ -4977,7 +5194,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -4999,7 +5216,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -5021,12 +5238,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
           <t>Not compliant</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5265,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5065,7 +5287,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -5087,7 +5309,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5104,17 +5326,17 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>1 mail domain without DKIM</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 DKIM isn't set up (selector2 CNAME missing)</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
@@ -5126,39 +5348,39 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>DMARC is monitor-only (p=none); spoofed mail is still delivered</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>parked.example</t>
+          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Doesn't receive mail but has no DMARC p=reject record</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
@@ -5170,83 +5392,83 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
+          <t>8 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Project Phoenix</t>
+          <t>DESK-SMITH03</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Team, only owner is disabled (Ben Okafor)</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
+          <t>8 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>DESK-WHITE42</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, only owner is disabled (Ben Okafor)</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
+          <t>8 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>LAPTOP-EVANS26</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, no owner</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
+          <t>8 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Provisioned</t>
+          <t>LAPTOP-HUGHES11</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, owned only by an app (Provisioning app)</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
@@ -5258,17 +5480,17 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>Enforced by Require MFA for all users, with 1 exclusion to review</t>
+          <t>8 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>LAPTOP-JACKSON49</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>Excluded from "Require MFA for all users"</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
@@ -5280,17 +5502,17 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>1 disabled account still licensed</t>
+          <t>8 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ben.okafor@fabrikam.example</t>
+          <t>LAPTOP-JONES34</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Disabled, holding 1 licence</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
@@ -5302,39 +5524,39 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including anonymous links</t>
+          <t>8 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SharePoint and OneDrive</t>
+          <t>LAPTOP-SCOTT19</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>Anyone links are allowed</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
+          <t>8 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>holiday.jpg (OneDrive of anna.kowalski@fabrikam.example)</t>
+          <t>DESK-RECEPTION</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Anyone can view</t>
+          <t>No recovery key saved in Entra ID (encryption not known)</t>
         </is>
       </c>
     </row>
@@ -5346,17 +5568,17 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
+          <t>1 mail domain without DKIM</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Open day flyer.pdf (Marketing / Documents)</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>Anyone can view, link never expires</t>
+          <t>Microsoft 365 DKIM isn't set up (selector2 CNAME missing)</t>
         </is>
       </c>
     </row>
@@ -5368,44 +5590,39 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders outside people can edit</t>
+          <t>2 domains without DMARC enforcement</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Budget.xlsx (Finance / Documents)</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Can be edited by accountant@hargreaves-partners.example</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>DMARC is monitor-only (p=none); spoofed mail is still delivered</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders outside people can edit</t>
+          <t>2 domains without DMARC enforcement</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Lab dockets (Patient Records / Documents)</t>
+          <t>parked.example</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Can be edited by orders@dentallab.example</t>
+          <t>Doesn't receive mail but has no DMARC p=reject record</t>
         </is>
       </c>
     </row>
@@ -5417,17 +5634,17 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>3 mailboxes at or over 90% of quota</t>
+          <t>1 anti-malware policy lets risky attachment types through</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>accounts@fabrikam.example</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>44.8 GB of 49.5 GB (91%), no archive</t>
+          <t>The common attachments filter is off</t>
         </is>
       </c>
     </row>
@@ -5439,22 +5656,17 @@
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>3 mailboxes at or over 90% of quota</t>
+          <t>1 anti-phishing policy weakens spoof protection</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>aisha.brown@fabrikam.example</t>
+          <t>Office365 AntiPhish Default</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>47.2 GB of 49.5 GB (95%), no archive</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Ignores what senders' DMARC policies ask for</t>
         </is>
       </c>
     </row>
@@ -5466,49 +5678,39 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>3 mailboxes at or over 90% of quota</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>thomas.robinson@fabrikam.example</t>
+          <t>Project Phoenix</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>45.6 GB of 49.5 GB (92%), no archive</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Team, only owner is disabled (Ben Okafor)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tenant SharePoint storage</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Microsoft 365 group, only owner is disabled (Ben Okafor)</t>
         </is>
       </c>
     </row>
@@ -5520,22 +5722,17 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/finance</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Microsoft 365 group, no owner</t>
         </is>
       </c>
     </row>
@@ -5547,284 +5744,279 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/imaging</t>
+          <t>Provisioned</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Microsoft 365 group, owned only by an app (Provisioning app)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>Enforced by CA002 — All users: Require MFA, with 1 exclusion to review</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/marketing</t>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Excluded from "CA002 — All users: Require MFA"</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>1 disabled account still licensed</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/patient-records</t>
+          <t>ben.okafor@fabrikam.example</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Disabled, holding 1 licence</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>Anyone, including anonymous links</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/practice</t>
+          <t>SharePoint and OneDrive</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Anyone links are allowed</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>1 account reports to a blocked manager</t>
+          <t>2 files and folders shared with anyone</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>holiday.jpg (OneDrive of anna.kowalski@fabrikam.example)</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Reports to Ben Okafor, whose sign-in is blocked</t>
+          <t>Anyone can view</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>1 app registration with expiring or expired credentials</t>
+          <t>2 files and folders shared with anyone</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Old connector</t>
+          <t>Open day flyer.pdf (Marketing / Documents)</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>The 1 credential expired, last on 1 Jan 2025</t>
+          <t>Anyone can view, link never expires</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>1 of 55 joined computers not in Intune</t>
+          <t>2 files and folders outside people can edit</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DESK-RECEPTION</t>
+          <t>Budget.xlsx (Finance / Documents)</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Hybrid joined, not managed by Intune</t>
+          <t>Can be edited by accountant@hargreaves-partners.example</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>2 files and folders outside people can edit</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
+          <t>Lab dockets (Patient Records / Documents)</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>Can be edited by orders@dentallab.example</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>3 mailboxes at or over 90% of quota</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>accounts@fabrikam.example</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>44.8 GB of 49.5 GB (91%), no archive</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>3 mailboxes at or over 90% of quota</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>47.2 GB of 49.5 GB (95%), no archive</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>3 mailboxes at or over 90% of quota</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+          <t>thomas.robinson@fabrikam.example</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>45.6 GB of 49.5 GB (92%), no archive</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>Tenant SharePoint storage</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 45 days ago</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5836,17 +6028,22 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>1 of 57 device records unused for 90+ days</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>OLD-PC</t>
+          <t>https://fabrikam.sharepoint.com/sites/finance</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>Windows, last seen 200 days ago</t>
+          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5858,17 +6055,22 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>1 domain with SPF problems</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>parked.example</t>
+          <t>https://fabrikam.sharepoint.com/sites/imaging</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Doesn't receive mail but has no "v=spf1 -all" record to stop spoofing</t>
+          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5880,17 +6082,22 @@
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>https://fabrikam.sharepoint.com/sites/marketing</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>No MTA-STS policy, so mail sent to this domain can be forced onto an unencrypted connection</t>
+          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5902,17 +6109,22 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is on for the organisation</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>https://fabrikam.sharepoint.com/sites/patient-records</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is allowed</t>
+          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5924,17 +6136,22 @@
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including guests, can invite guests</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>https://fabrikam.sharepoint.com/sites/practice</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>Guests can invite other guests</t>
+          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5946,17 +6163,17 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>1 account reports to a blocked manager</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>george.baker@fabrikam.example</t>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>Reports to Ben Okafor, whose sign-in is blocked</t>
         </is>
       </c>
     </row>
@@ -5968,22 +6185,17 @@
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>1 app registration with expiring or expired credentials</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>owen.robinson@fabrikam.example</t>
+          <t>Old connector</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>The 1 credential expired, last on 1 Jan 2025</t>
         </is>
       </c>
     </row>
@@ -5995,17 +6207,17 @@
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>1 of 55 joined computers not in Intune</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>owen.turner@fabrikam.example</t>
+          <t>DESK-RECEPTION</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>Hybrid joined, not managed by Intune</t>
         </is>
       </c>
     </row>
@@ -6017,17 +6229,17 @@
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>thomas.allen@fabrikam.example</t>
+          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>Last check-in 38 days ago</t>
         </is>
       </c>
     </row>
@@ -6039,17 +6251,22 @@
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions with spare licences</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Microsoft 365 Business Basic</t>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>2 of 13 unassigned, 9.80 GBP/month</t>
+          <t>Last check-in 38 days ago</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6061,17 +6278,17 @@
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions with spare licences</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Microsoft 365 Business Premium</t>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>3 of 46 unassigned, 54.30 GBP/month</t>
+          <t>Last check-in 38 days ago</t>
         </is>
       </c>
     </row>
@@ -6083,22 +6300,313 @@
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
+          <t>5 devices haven't checked in for 30+ days</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>Last check-in 38 days ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>5 devices haven't checked in for 30+ days</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>Last check-in 45 days ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>1 of 57 device records unused for 90+ days</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>OLD-PC</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>Windows, last seen 200 days ago</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>1 domain with SPF problems</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>parked.example</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>Doesn't receive mail but has no "v=spf1 -all" record to stop spoofing</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>No MTA-STS policy, so mail sent to this domain can be forced onto an unencrypted connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>SMTP AUTH is on for the organisation</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Whole organisation</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>SMTP AUTH is allowed</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>Anyone, including guests, can invite guests</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Whole organisation</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>Guests can invite other guests</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>george.baker@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>owen.robinson@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>owen.turner@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>thomas.allen@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>2 subscriptions with spare licences</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Microsoft 365 Business Basic</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>2 of 13 unassigned, 9.80 GBP/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>2 subscriptions with spare licences</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Microsoft 365 Business Premium</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>3 of 46 unassigned, 54.30 GBP/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
           <t>Any user can register an app</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>Whole organisation</t>
         </is>
       </c>
-      <c r="D151" s="7" t="inlineStr">
+      <c r="D164" s="7" t="inlineStr">
         <is>
           <t>Users can register apps that nobody reviews</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E151"/>
+  <autoFilter ref="A1:E164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -6211,10 +6719,10 @@
       <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" s="11" t="n">
+      <c r="H2" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="I2" s="11" t="n">
+      <c r="I2" s="12" t="n">
         <v>144.8</v>
       </c>
     </row>
@@ -6244,10 +6752,10 @@
       <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H3" s="12" t="n">
         <v>4.9</v>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I3" s="12" t="n">
         <v>19.6</v>
       </c>
     </row>
@@ -6272,7 +6780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -6303,8 +6811,8 @@
           <t>Tenant profile and licences</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B2" s="13" t="n">
+        <v>46307.16694444444</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6318,8 +6826,8 @@
           <t>Connection and permissions</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B3" s="13" t="n">
+        <v>46307.16694444444</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6333,8 +6841,8 @@
           <t>Users</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B4" s="13" t="n">
+        <v>46307.16694444444</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -6348,8 +6856,8 @@
           <t>Admin roles</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B5" s="13" t="n">
+        <v>46307.16694444444</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6363,8 +6871,8 @@
           <t>Conditional Access</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B6" s="13" t="n">
+        <v>46307.16694444444</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6378,8 +6886,8 @@
           <t>MFA registration</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B7" s="13" t="n">
+        <v>46307.16694444444</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -6393,8 +6901,8 @@
           <t>Per-user MFA</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B8" s="13" t="n">
+        <v>46307.16694444444</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -6408,8 +6916,8 @@
           <t>Secure Score</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B9" s="13" t="n">
+        <v>46307.16694444444</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6423,8 +6931,8 @@
           <t>Sign-in methods policy</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B10" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6438,8 +6946,8 @@
           <t>Admin activity</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B11" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6453,8 +6961,8 @@
           <t>Apps and consents</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B12" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -6468,8 +6976,8 @@
           <t>Sharing and consent settings</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B13" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -6483,8 +6991,8 @@
           <t>Groups and Teams</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B14" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6498,8 +7006,8 @@
           <t>Deleted users and groups</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B15" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -6513,8 +7021,8 @@
           <t>Mailboxes</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B16" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6528,8 +7036,8 @@
           <t>Inbox rules</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B17" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6543,8 +7051,8 @@
           <t>Sign-in activity</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B18" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6558,8 +7066,8 @@
           <t>Mailbox size</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B19" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6573,8 +7081,8 @@
           <t>Legacy sign-ins</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
-        <v>46306.80025462963</v>
+      <c r="B20" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6588,8 +7096,8 @@
           <t>Mobile devices</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>46306.8002662037</v>
+      <c r="B21" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6603,8 +7111,8 @@
           <t>Automatic replies</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
-        <v>46306.8002662037</v>
+      <c r="B22" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6618,8 +7126,8 @@
           <t>Distribution lists</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n">
-        <v>46306.8002662037</v>
+      <c r="B23" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6633,8 +7141,8 @@
           <t>Risky users</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
-        <v>46306.8002662037</v>
+      <c r="B24" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6648,8 +7156,8 @@
           <t>Email domains</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
-        <v>46306.8002662037</v>
+      <c r="B25" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6663,8 +7171,8 @@
           <t>Devices</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
-        <v>46306.8002662037</v>
+      <c r="B26" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6675,11 +7183,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Directory sync</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>Intune policies</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6690,11 +7198,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SharePoint and OneDrive usage</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>Directory sync</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -6705,11 +7213,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Shared files</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>SharePoint and OneDrive usage</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -6720,11 +7228,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SharePoint storage</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>Shared files</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6735,11 +7243,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site access</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>SharePoint storage</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -6750,11 +7258,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Site permissions</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>Site access</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -6765,11 +7273,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Microsoft 365 usage</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>Site permissions</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>46307.16695601852</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -6780,11 +7288,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Teams</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>Microsoft 365 usage</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>46307.1669675926</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -6795,11 +7303,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mail flow</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>Teams</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>46307.1669675926</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -6810,11 +7318,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>App sign-ins</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>Mail flow</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>46307.1669675926</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -6825,11 +7333,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Group nesting</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>Mail rules and protection</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>46307.1669675926</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6840,11 +7348,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Departments and managers</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n">
-        <v>46306.8002662037</v>
+          <t>App sign-ins</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>46307.1669675926</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -6855,20 +7363,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Group nesting</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>46307.1669675926</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Departments and managers</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>46307.1669675926</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Administrative units</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
-        <v>46306.8002662037</v>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B41" s="13" t="n">
+        <v>46307.1669675926</v>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Up to date</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C39"/>
+  <autoFilter ref="A1:C41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 12 Oct 2026, 04:02 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 12 Oct 2026, 11:29 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Give each site a second owner (in the Microsoft 365 group, or as a site administrator) so access requests and content questions have someone to go to when one person leaves. The Site access report lists each site's owners.</t>
+          <t>Give each site a second owner (in the Microsoft 365 group, in the site's owners group, or as a site administrator) so access requests and content questions have someone to go to when one person leaves. The Site access report lists each site's owners.</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>No enabled owner (site administrators)</t>
+          <t>No enabled owner (site administrators and owners group)</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>One owner (site administrators)</t>
+          <t>One owner (site administrators and owners group)</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 22 Apr 2026</t>
+          <t>Licensed member, last signed in 23 Apr 2026</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 3 Jun 2026</t>
+          <t>Licensed member, last signed in 4 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 8 Jul 2026</t>
+          <t>Licensed member, last signed in 9 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>46307.16694444444</v>
+        <v>46307.47756944445</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>46307.16694444444</v>
+        <v>46307.47756944445</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>46307.16694444444</v>
+        <v>46307.47756944445</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>46307.16694444444</v>
+        <v>46307.47756944445</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>46307.16694444444</v>
+        <v>46307.47756944445</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>46307.16694444444</v>
+        <v>46307.47756944445</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>46307.16694444444</v>
+        <v>46307.47756944445</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>46307.16694444444</v>
+        <v>46307.47756944445</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7258,11 +7258,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Site access</t>
+          <t>Site permissions</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47758101852</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7273,11 +7273,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Site permissions</t>
+          <t>Site access</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>46307.16695601852</v>
+        <v>46307.47759259259</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>46307.1669675926</v>
+        <v>46307.47759259259</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>46307.1669675926</v>
+        <v>46307.47759259259</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>46307.1669675926</v>
+        <v>46307.47759259259</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>46307.1669675926</v>
+        <v>46307.47759259259</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>46307.1669675926</v>
+        <v>46307.47759259259</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>46307.1669675926</v>
+        <v>46307.47759259259</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>46307.1669675926</v>
+        <v>46307.47759259259</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>46307.1669675926</v>
+        <v>46307.47759259259</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -15,13 +15,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$F$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$F$72</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checks'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$172</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Findings'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Licences'!$A$1:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Licences'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$44</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Data freshness'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 12 Oct 2026, 11:29 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 16 Oct 2026, 11:17 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>31% on 14 Sep 2026</t>
+          <t>32% on 18 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>46.2% on 14 Sep 2026</t>
+          <t>45.6% on 18 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>4 on 14 Sep 2026</t>
+          <t>4 on 18 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>51 on 14 Sep 2026</t>
+          <t>51 on 18 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>1 critical, 30 high, 69 medium, 63 low findings</t>
+          <t>1 critical, 31 high, 99 medium, 40 low findings</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" s="7" t="n"/>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -897,12 +897,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>1 admin without MFA, and 1 whose registration isn't known</t>
+          <t>1 admin without MFA, and 2 whose registration isn't known</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Have each listed admin register a strong method (Authenticator or a FIDO2 key), or remove the role. Break-glass accounts should use FIDO2 keys kept offline.</t>
+          <t>Have every admin without MFA register a strong method (Authenticator or a FIDO2 key), or remove their role. Break-glass accounts should use FIDO2 keys kept offline.</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Disable accounts that haven't signed in for 90 days, or were created over 30 days ago and never used (after checking with the client), then remove their licences. Inactive accounts are a common foothold for attackers.</t>
+          <t>Disable accounts that haven't signed in for 90 days, or were created over 30 days ago and never used (after checking with their manager), then remove their licences. Inactive accounts are a common foothold for attackers.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Remove forwarding to outside addresses unless the client has a documented business reason. Forwarding is the most common way attackers keep reading a mailbox after a password reset.</t>
+          <t>Remove forwarding to outside addresses unless there's a documented business reason. Forwarding is the most common way attackers keep reading a mailbox after a password reset.</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Mailbox auditing is on</t>
+          <t>The Microsoft 365 audit log is on</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Mailbox auditing is on for the organisation</t>
+          <t>The audit log is recording user and admin activity</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Turn mailbox auditing back on for the organisation (Set-OrganizationConfig -AuditDisabled $false). Without it there's no record of who read or deleted mail during an incident.</t>
+          <t>Turn on the audit log in Microsoft Purview (Audit, then Start recording user and admin activity). Without it there's no record of who deleted, downloaded or shared files, who opened someone else's mailbox or who created an inbox rule, and Microsoft can take up to a day to start recording.</t>
         </is>
       </c>
     </row>
@@ -1310,27 +1310,22 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is turned off</t>
+          <t>Mailbox auditing is on</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is on for the organisation</t>
+          <t>Mailbox auditing is on for the organisation</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Turn off SMTP AUTH for the organisation and enable it only on the mailboxes of devices or apps that still need it, such as scanners. It accepts passwords without MFA.</t>
+          <t>Turn mailbox auditing back on for the organisation (Set-OrganizationConfig -AuditDisabled $false). Without it there's no record of who read or deleted mail during an incident.</t>
         </is>
       </c>
     </row>
@@ -1342,22 +1337,27 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>No mail flow rule lets mail skip spam filtering</t>
+          <t>SMTP AUTH is turned off</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>No mail flow rule skips spam filtering (3 rules checked)</t>
+          <t>SMTP AUTH is on for the organisation</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Remove mail flow rules that skip spam filtering (set the spam confidence level to -1) for senders picked by their address, domain or a header, which anyone can fake. For mail arriving through another filtering service use enhanced filtering on its inbound connector instead, and for a partner limit the rule to the addresses of their sending servers.</t>
+          <t>Turn off SMTP AUTH for the organisation and enable it only on the mailboxes of devices or apps that still need it, such as scanners. It accepts passwords without MFA.</t>
         </is>
       </c>
     </row>
@@ -1369,27 +1369,22 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>No mail flow rule sends mail outside the organisation</t>
+          <t>No mail flow rule lets mail skip spam filtering</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>1 mail flow rule sends mail outside the organisation</t>
+          <t>No mail flow rule skips spam filtering (3 rules checked)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Check each rule that redirects mail or sends copies to an outside address with the client, and remove it unless there's a documented reason (a journaling or archiving service). Attackers with admin access add these rules to read a whole organisation's mail.</t>
+          <t>Remove mail flow rules that skip spam filtering (set the spam confidence level to -1) for senders picked by their address, domain or a header, which anyone can fake. For mail arriving through another filtering service use enhanced filtering on its inbound connector instead, and for a partner limit the rule to the addresses of their sending servers.</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1396,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>No sender domains are allowed past the spam filter</t>
+          <t>No mail flow rule sends mail outside the organisation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1416,12 +1411,12 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>2 sender domains skip the spam filter</t>
+          <t>1 mail flow rule sends mail outside the organisation</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Remove the allowed sender domains from the anti-spam policies: anyone can send mail claiming to be from a domain, so it skips spam and spoofing checks. Where a partner's mail is wrongly caught, report it to Microsoft or add an allow entry for their spoofed sender in the Tenant Allow/Block List instead.</t>
+          <t>Check each rule that redirects mail or sends copies to an outside address, and remove it unless there's a documented reason (a journaling or archiving service). Attackers with admin access add these rules to read a whole organisation's mail.</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1428,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Spoof protection is on</t>
+          <t>No sender domains are allowed past the spam filter</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1443,17 +1438,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>1 anti-phishing policy weakens spoof protection</t>
+          <t>2 sender domains skip the spam filter</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Turn spoof intelligence and “Honour DMARC policy” back on in the anti-phishing policies (both are on by default). Without them, mail pretending to be from other organisations' domains is delivered.</t>
+          <t>Remove the allowed sender domains from the anti-spam policies: anyone can send mail claiming to be from a domain, so it skips spam and spoofing checks. Where a partner's mail is wrongly caught, report it to Microsoft or add an allow entry for their spoofed sender in the Tenant Allow/Block List instead.</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Risky attachment types are blocked</t>
+          <t>Spoof protection is on</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1480,24 +1475,24 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>1 anti-malware policy lets risky attachment types through</t>
+          <t>1 anti-phishing policy weakens spoof protection</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Turn on the common attachments filter in the anti-malware policies (it's on by default), so program files, disk images and scripts (.exe, .iso, .js and the like) are quarantined rather than delivered.</t>
+          <t>Turn spoof intelligence and “Honour DMARC policy” back on in the anti-phishing policies (both are on by default). Without them, mail pretending to be from other organisations' domains is delivered.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Third-party apps hold only the access they need</t>
+          <t>Risky attachment types are blocked</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1507,17 +1502,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>1 app with access to mail, files or the directory</t>
+          <t>1 anti-malware policy lets risky attachment types through</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Review each app with the client. Remove apps nobody recognises (Enterprise applications &gt; Delete), and for the rest confirm the vendor and that it still needs mailbox or file access.</t>
+          <t>Turn on the common attachments filter in the anti-malware policies (it's on by default), so program files, disk images and scripts (.exe, .iso, .js and the like) are quarantined rather than delivered.</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1524,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Users can't consent to apps on their own</t>
+          <t>Third-party apps hold only the access they need</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1539,17 +1534,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Users can consent to any app</t>
+          <t>1 app with access to mail, files or the directory</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Set user consent to "Allow user consent for apps from verified publishers, for selected permissions" or turn it off and use the admin consent workflow. Consent phishing relies on this setting.</t>
+          <t>Review each app with the people who use it. Remove apps nobody recognises (Enterprise applications &gt; Delete), and for the rest confirm the vendor and that it still needs mailbox or file access.</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1556,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>App secrets and certificates are current</t>
+          <t>Users can't consent to apps on their own</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1571,44 +1566,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>1 app registration with expiring or expired credentials</t>
+          <t>Users can consent to any app</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Renew credentials before they expire to avoid an outage, and delete app registrations whose credentials have all expired if nothing uses them any more.</t>
+          <t>Set user consent to "Allow user consent for apps from verified publishers, for selected permissions" or turn it off and use the admin consent workflow. Consent phishing relies on this setting.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tenant settings</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Users can't create new tenants</t>
+          <t>App secrets and certificates are current</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Microsoft didn't return this setting</t>
+          <t>1 app registration with expiring or expired credentials</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Set "Restrict non-admin users from creating tenants" to Yes (Entra admin center &gt; Users &gt; User settings). A tenant a user creates sits outside the client's policies, with that user as its Global Administrator.</t>
+          <t>Renew credentials before they expire to avoid an outage, and delete app registrations whose credentials have all expired if nothing uses them any more.</t>
         </is>
       </c>
     </row>
@@ -1620,27 +1620,22 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Users can't register apps</t>
+          <t>Users can't create new tenants</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Any user can register an app</t>
+          <t>Microsoft didn't return this setting</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Set "Users can register applications" to No (Entra admin center &gt; Users &gt; User settings) and give the Application Developer role to the people who need it.</t>
+          <t>Set "Restrict non-admin users from creating tenants" to Yes (Entra admin center &gt; Users &gt; User settings). A tenant a user creates sits outside the organisation's policies, with that user as its Global Administrator.</t>
         </is>
       </c>
     </row>
@@ -1652,22 +1647,27 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Guests have limited directory access</t>
+          <t>Users can't register apps</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Guests have limited access to directory objects (the default)</t>
+          <t>Any user can register an app</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Set guest user access to "Guest users have limited access to properties and memberships of directory objects", or to the most restrictive option (Entra admin center &gt; External Identities &gt; External collaboration settings).</t>
+          <t>Set "Users can register applications" to No (Entra admin center &gt; Users &gt; User settings) and give the Application Developer role to the people who need it.</t>
         </is>
       </c>
     </row>
@@ -1679,22 +1679,22 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>People can't join the tenant just by verifying an email address</t>
+          <t>Guests have limited directory access</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Microsoft didn't return this setting</t>
+          <t>Guests have limited access to directory objects (the default)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Turn off email-verified sign-up with Microsoft Graph PowerShell (Update-MgPolicyAuthorizationPolicy -AllowEmailVerifiedUsersToJoinOrganization:$false), so accounts are only created by admins or invitation.</t>
+          <t>Set guest user access to "Guest users have limited access to properties and memberships of directory objects", or to the most restrictive option (Entra admin center &gt; External Identities &gt; External collaboration settings).</t>
         </is>
       </c>
     </row>
@@ -1706,66 +1706,61 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Users have a way to get apps approved</t>
+          <t>People can't join the tenant just by verifying an email address</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Users can consent to most apps themselves, so admin consent requests are off (see the user consent check)</t>
+          <t>Microsoft didn't return this setting</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Turn on admin consent requests (Entra admin center &gt; Enterprise apps &gt; Consent and permissions &gt; Admin consent settings) and choose reviewers, so users blocked from consenting can ask instead of looking for a workaround.</t>
+          <t>Turn off email-verified sign-up with Microsoft Graph PowerShell (Update-MgPolicyAuthorizationPolicy -AllowEmailVerifiedUsersToJoinOrganization:$false), so accounts are only created by admins or invitation.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sharing</t>
+          <t>Tenant settings</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Files can't be shared with anonymous links</t>
+          <t>Users have a way to get apps approved</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including anonymous links</t>
+          <t>Users can consent to most apps themselves, so admin consent requests are off (see the user consent check)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Change SharePoint external sharing to "New and existing guests" so every external person signs in. If the client relies on Anyone links, set them to expire and to view-only.</t>
+          <t>Turn on admin consent requests (Entra admin center &gt; Enterprise apps &gt; Consent and permissions &gt; Admin consent settings) and choose reviewers, so users blocked from consenting can ask instead of looking for a workaround.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Only admins and members can invite guests</t>
+          <t>Files can't be shared with anonymous links</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1775,17 +1770,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including guests, can invite guests</t>
+          <t>Anyone, including anonymous links</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Restrict guest invitations to admins and the Guest Inviter role, or at least to members, under External collaboration settings.</t>
+          <t>Change SharePoint external sharing to "New and existing guests" so every external person signs in. Where Anyone links are needed, set them to expire and to view-only.</t>
         </is>
       </c>
     </row>
@@ -1797,54 +1792,54 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>No old, unaccepted guest invitations</t>
+          <t>Only admins and members can invite guests</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>No stale guest invitations</t>
+          <t>Anyone, including guests, can invite guests</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Delete guest accounts whose invitation has gone unaccepted for 30 days; re-invite if still needed.</t>
+          <t>Restrict guest invitations to admins and the Guest Inviter role, or at least to members, under External collaboration settings.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Mail domains require encrypted delivery (MTA-STS)</t>
+          <t>No old, unaccepted guest invitations</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
+          <t>No stale guest invitations</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Publish an MTA-STS policy so other mail servers only deliver to the domain over a verified, encrypted connection: a TXT record at _mta-sts.&lt;domain&gt; ("v=STSv1; id=20260101") and a policy file at https://mta-sts.&lt;domain&gt;/.well-known/mta-sts.txt listing the domain's MX hosts (for Microsoft 365, "mx: *.mail.protection.outlook.com"). Start with "mode: testing" and TLS-RPT reports, then switch to "mode: enforce" and change the id.</t>
+          <t>Delete guest accounts whose invitation has gone unaccepted for 30 days; re-invite if still needed.</t>
         </is>
       </c>
     </row>
@@ -1856,22 +1851,27 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Encrypted delivery failures are reported (TLS-RPT)</t>
+          <t>Mail domains require encrypted delivery (MTA-STS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>TLS-RPT is checked on mail domains that use MTA-STS, and none do yet</t>
+          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Publish a TXT record at _smtp._tls.&lt;domain&gt; such as "v=TLSRPTv1; rua=mailto:tls-reports@&lt;domain&gt;" (or a reporting service's address), so someone hears when other servers can't deliver mail encrypted, before and after MTA-STS is enforced.</t>
+          <t>Publish an MTA-STS policy so other mail servers only deliver to the domain over a verified, encrypted connection: a TXT record at _mta-sts.&lt;domain&gt; ("v=STSv1; id=20260101") and a policy file at https://mta-sts.&lt;domain&gt;/.well-known/mta-sts.txt listing the domain's MX hosts (for Microsoft 365, "mx: *.mail.protection.outlook.com"). Start with "mode: testing" and TLS-RPT reports, then switch to "mode: enforce" and change the id.</t>
         </is>
       </c>
     </row>
@@ -1883,27 +1883,22 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Every domain has a working SPF record</t>
+          <t>Encrypted delivery failures are reported (TLS-RPT)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>1 domain with SPF problems</t>
+          <t>TLS-RPT is checked on mail domains that use MTA-STS, and none do yet</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Publish one SPF record per domain ending in -all (or ~all while testing), e.g. "v=spf1 include:spf.protection.outlook.com -all". Domains that never send mail should publish "v=spf1 -all".</t>
+          <t>Publish a TXT record at _smtp._tls.&lt;domain&gt; such as "v=TLSRPTv1; rua=mailto:tls-reports@&lt;domain&gt;" (or a reporting service's address), so someone hears when other servers can't deliver mail encrypted, before and after MTA-STS is enforced.</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1910,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Every domain enforces DMARC</t>
+          <t>Every domain has a working SPF record</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1925,17 +1920,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
+          <t>1 domain with SPF problems</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Publish a DMARC record with a rua= reporting address, start at p=none to see who sends as the domain, then move to p=quarantine and p=reject. Without enforcement, spoofed mail from the domain is delivered.</t>
+          <t>Publish one SPF record per domain ending in -all (or ~all while testing), e.g. "v=spf1 include:spf.protection.outlook.com -all". Domains that never send mail should publish "v=spf1 -all".</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1942,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>DKIM signing is on for every mail domain</t>
+          <t>Every domain enforces DMARC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1962,24 +1957,24 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>1 mail domain without DKIM</t>
+          <t>2 domains without DMARC enforcement</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Turn on DKIM for each domain in the Defender portal (Email authentication settings &gt; DKIM), publishing the two selector CNAME records it shows. This applies to domains behind a mail gateway too when Microsoft 365 still sends for them (their SPF includes spf.protection.outlook.com); a gateway signs only the mail that goes out through it.</t>
+          <t>Publish a DMARC record with a rua= reporting address, start at p=none to see who sends as the domain, then move to p=quarantine and p=reject. Without enforcement, spoofed mail from the domain is delivered.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Every team and Microsoft 365 group has an owner</t>
+          <t>DKIM signing is on for every mail domain</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1994,51 +1989,56 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
+          <t>1 mail domain without DKIM</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Make an active person, ideally two, an owner of each listed team or group (Teams admin center or Microsoft 365 admin center &gt; Teams &amp; groups). Owners approve members and guests and renew the group; without one, nobody looks after its files and conversations. The ownerless group policy (Microsoft 365 admin center &gt; Settings &gt; Org settings &gt; Microsoft 365 Groups) asks members to take over when the last owner leaves.</t>
+          <t>Turn on DKIM for each domain in the Defender portal (Email authentication settings &gt; DKIM), publishing the two selector CNAME records it shows. This applies to domains behind a mail gateway too when Microsoft 365 still sends for them (their SPF includes spf.protection.outlook.com); a gateway signs only the mail that goes out through it.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Guests</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>No guest owns a team or group</t>
+          <t>Every team and Microsoft 365 group has an owner</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>No guest owns any of 9 teams and groups</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Make a member of the organisation the owner of each listed team or group and remove the guest as owner (Teams admin center, or Microsoft 365 admin center &gt; Teams &amp; groups). An owner from outside can add members and guests, change settings and see everything in it, and nobody here is accountable for that.</t>
+          <t>Make an active person, ideally two, an owner of each listed team or group (Teams admin center or Microsoft 365 admin center &gt; Teams &amp; groups). Owners approve members and guests and renew the group; without one, nobody looks after its files and conversations. The ownerless group policy (Microsoft 365 admin center &gt; Settings &gt; Org settings &gt; Microsoft 365 Groups) asks members to take over when the last owner leaves.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Guests</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Only chosen people can create teams and groups</t>
+          <t>No guest owns a team or group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Only admins and members of Group creators can create teams and groups</t>
+          <t>No guest owns any of 9 teams and groups</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Limit who can create teams and Microsoft 365 groups to a security group of people who will look after them (the Group.Unified directory setting, changed with Microsoft Graph PowerShell; needs Entra ID P1). Otherwise anyone can create a team, add guests to it and leave it behind.</t>
+          <t>Make a member of the organisation the owner of each listed team or group and remove the guest as owner (Teams admin center, or Microsoft 365 admin center &gt; Teams &amp; groups). An owner from outside can add members and guests, change settings and see everything in it, and nobody here is accountable for that.</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Unused groups and teams expire</t>
+          <t>Only chosen people can create teams and groups</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2075,44 +2075,39 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Unused teams and groups expire after 365 days</t>
+          <t>Only admins and members of Group creators can create teams and groups</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Set a Microsoft 365 group expiration policy for all groups (Entra admin center &gt; Groups &gt; Expiration), for example 365 days. Groups in use renew automatically, owners are asked to renew the rest, and an expired group can be restored for 30 days. Needs Entra ID P1.</t>
+          <t>Limit who can create teams and Microsoft 365 groups to a security group of people who will look after them (the Group.Unified directory setting, changed with Microsoft Graph PowerShell; needs Entra ID P1). Otherwise anyone can create a team, add guests to it and leave it behind.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Managed devices meet compliance policies</t>
+          <t>Unused groups and teams expire</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>Unused teams and groups expire after 365 days</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Open each non-compliant device in Intune (Devices &gt; Monitor &gt; Noncompliant devices) to see which setting fails, fix it or retire the device, and block non-compliant devices with a Conditional Access policy that requires a compliant device.</t>
+          <t>Set a Microsoft 365 group expiration policy for all groups (Entra admin center &gt; Groups &gt; Expiration), for example 365 days. Groups in use renew automatically, owners are asked to renew the rest, and an expired group can be restored for 30 days. Needs Entra ID P1.</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2119,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Company computers are encrypted</t>
+          <t>Managed devices meet compliance policies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2134,17 +2129,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>6 of 54 computers not encrypted</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Turn on BitLocker (Windows) and FileVault (macOS) with an Intune disk encryption policy, with recovery keys escrowed to Entra ID, so a lost or stolen laptop doesn't expose the client's data.</t>
+          <t>Open each non-compliant device in Intune (Devices &gt; Monitor &gt; Noncompliant devices) to see which setting fails, fix it or retire the device, and block non-compliant devices with a Conditional Access policy that requires a compliant device.</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2151,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Windows computers still get security updates</t>
+          <t>Company computers are encrypted</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2171,12 +2166,12 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
+          <t>6 of 54 computers not encrypted</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Upgrade computers on Windows 10 or an old Windows 11 release to the current Windows 11 release (Intune: Windows feature updates policy). Replace hardware that can't run Windows 11, or buy Extended Security Updates as a stopgap.</t>
+          <t>Turn on BitLocker (Windows) and FileVault (macOS) with an Intune disk encryption policy, with recovery keys escrowed to Entra ID, so a lost or stolen laptop doesn't expose the organisation's data.</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2183,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Joined computers are managed by Intune</t>
+          <t>Windows computers still get security updates</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2198,17 +2193,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>1 of 55 joined computers not in Intune</t>
+          <t>36 of 54 Windows computers past end of support</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Enrol Entra-joined and hybrid-joined computers in Intune (automatic enrolment under Devices &gt; Enrollment &gt; Windows) so compliance, encryption and updates can be enforced on them.</t>
+          <t>Upgrade computers on Windows 10 or an old Windows 11 release to the current Windows 11 release (Intune: Windows feature updates policy). Replace hardware that can't run Windows 11, or buy Extended Security Updates as a stopgap.</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2215,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Managed devices check in with Intune</t>
+          <t>Joined computers are managed by Intune</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2235,12 +2230,12 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>1 of 55 joined computers not in Intune</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Find out whether each device is lost, replaced or broken. Retire devices that are gone; for devices still in use, restart the Intune Management Extension or re-enrol.</t>
+          <t>Enrol Entra-joined and hybrid-joined computers in Intune (automatic enrolment under Devices &gt; Enrollment &gt; Windows) so compliance, encryption and updates can be enforced on them.</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2247,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>No old devices left in Entra ID</t>
+          <t>Managed devices check in with Intune</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2267,12 +2262,12 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>1 of 57 device records unused for 90+ days</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Disable, then after 30 days delete, device records that haven't signed in for 90 days (Entra admin center &gt; Devices &gt; All devices, filter by activity). Old records can still hold BitLocker keys and count toward device limits.</t>
+          <t>Find out whether each device is lost, replaced or broken. Retire devices that are gone; for devices still in use, restart the Intune Management Extension or re-enrol.</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2279,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Windows computers have their BitLocker recovery key saved</t>
+          <t>No old devices left in Entra ID</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2294,17 +2289,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>8 of 55 joined Windows computers without a saved recovery key</t>
+          <t>1 of 57 device records unused for 90+ days</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Make Intune's disk encryption policy (Endpoint security &gt; Disk encryption) require the recovery key to be saved in Entra ID before BitLocker turns on, and on computers already encrypted run BackupToAAD-BitLockerKeyProtector (or re-run the policy). Without the key, a computer that asks for it after a firmware or hardware change can't be unlocked, and its data is lost.</t>
+          <t>Disable, then after 30 days delete, device records that haven't signed in for 90 days (Entra admin center &gt; Devices &gt; All devices, filter by activity). Old records can still hold BitLocker keys and count toward device limits.</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2311,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Every platform in use has a compliance policy</t>
+          <t>Windows computers have their BitLocker recovery key saved</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2331,66 +2326,76 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>No compliance policy for iOS/iPadOS</t>
+          <t>7 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>In Intune (Devices &gt; Compliance), create and assign a compliance policy for each platform with enrolled devices, requiring at least encryption, a screen lock and a minimum OS version, and set devices with no policy to show as not compliant (Compliance settings). Until then those devices count as compliant, so Conditional Access that requires a compliant device lets them through.</t>
+          <t>Make Intune's disk encryption policy (Endpoint security &gt; Disk encryption) require the recovery key to be saved in Entra ID before BitLocker turns on, and on computers already encrypted run BackupToAAD-BitLockerKeyProtector (or re-run the policy). Without the key, a computer that asks for it after a firmware or hardware change can't be unlocked, and its data is lost.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hybrid identity</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Directory sync is running</t>
+          <t>Windows computers back up their local admin password with LAPS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Cloud-only tenant: directory sync isn't turned on</t>
+          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Check the Entra Connect server: that it is up, the Microsoft Azure AD Sync service is running and Synchronization Service Manager shows no errors. Until sync runs, accounts disabled or removed in Active Directory keep working in Microsoft 365. If the client has moved to cloud-only, turn directory sync off.</t>
+          <t>In Entra ID (Devices &gt; Device settings), turn on Microsoft Entra Local Administrator Password Solution (LAPS), then in Intune (Endpoint security &gt; Account protection) create a Local admin password solution policy that backs the password up to Entra ID and assign it to every Windows computer. Each computer then gets its own local admin password, changed regularly, so one leaked password doesn't open every computer.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Hybrid identity</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Password hash sync is on</t>
+          <t>Every platform in use has a compliance policy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Cloud-only tenant: directory sync isn't turned on</t>
+          <t>No compliance policy for iOS/iPadOS</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Turn on password hash synchronization in Entra Connect (Optional features), even when users sign in through federation or pass-through authentication. Entra ID can then detect leaked passwords, and sign-in can be switched to the cloud if the on-premises servers are down.</t>
+          <t>In Intune (Devices &gt; Compliance), create and assign a compliance policy for each platform with enrolled devices, requiring at least encryption, a screen lock and a minimum OS version, and set devices with no policy to show as not compliant (Compliance settings). Until then those devices count as compliant, so Conditional Access that requires a compliant device lets them through.</t>
         </is>
       </c>
     </row>
@@ -2402,98 +2407,88 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Admin accounts are cloud-only</t>
+          <t>Directory sync is running</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Cloud-only tenant: no accounts are synced from on-premises AD</t>
+          <t>Cloud-only tenant: directory sync isn't turned on</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Give each admin a separate cloud-only account (for example on the .onmicrosoft.com domain) for their admin roles, and remove the roles from accounts synced from Active Directory. Otherwise anyone who takes over on-premises AD can reset those passwords and become an admin in Microsoft 365.</t>
+          <t>Check the Entra Connect server: that it is up, the Microsoft Azure AD Sync service is running and Synchronization Service Manager shows no errors. Until sync runs, accounts disabled or removed in Active Directory keep working in Microsoft 365. If the organisation has moved to cloud-only, turn directory sync off.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Hybrid identity</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>No unexpected changes to how domains sign in</t>
+          <t>Password hash sync is on</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>1 domain had sign-in settings changed in the last 30 days</t>
+          <t>Cloud-only tenant: directory sync isn't turned on</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Confirm with the client that each change was planned (for example, setting up AD FS or another identity provider). If it wasn't, an attacker with admin rights may have federated the domain to their own identity provider so they can sign in as any user without a password or MFA: switch the domain back to managed sign-in, remove unknown federation settings, reset admin credentials and review the audit log.</t>
+          <t>Turn on password hash synchronization in Entra Connect (Optional features), even when users sign in through federation or pass-through authentication. Entra ID can then detect leaked passwords, and sign-in can be switched to the cloud if the on-premises servers are down.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sharing</t>
+          <t>Hybrid identity</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>No files are shared with anyone links</t>
+          <t>Admin accounts are cloud-only</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
+          <t>Cloud-only tenant: no accounts are synced from on-premises AD</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Remove anyone links that are no longer needed, and set the rest to view-only with an expiry date. The Shared files report lists each one.</t>
+          <t>Give each admin a separate cloud-only account (for example on the .onmicrosoft.com domain) for their admin roles, and remove the roles from accounts synced from Active Directory. Otherwise anyone who takes over on-premises AD can reset those passwords and become an admin in Microsoft 365.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>SharePoint storage isn't nearly full</t>
+          <t>No unexpected changes to how domains sign in</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2503,17 +2498,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>1 domain had sign-in settings changed in the last 30 days</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Free up space before the tenant runs out, when people can no longer save files. The SharePoint storage report shows where the space goes and what to clear first; otherwise buy Office 365 Extra File Storage.</t>
+          <t>Confirm that each change was planned (for example, setting up AD FS or another identity provider). If it wasn't, an attacker with admin rights may have federated the domain to their own identity provider so they can sign in as any user without a password or MFA: switch the domain back to managed sign-in, remove unknown federation settings, reset admin credentials and review the audit log.</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2520,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Every site has at least two owners</t>
+          <t>No files are shared with anyone links</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2535,29 +2530,29 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>2 sites with no owner, 2 sites with one owner</t>
+          <t>2 files and folders shared with anyone</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Give each site a second owner (in the Microsoft 365 group, in the site's owners group, or as a site administrator) so access requests and content questions have someone to go to when one person leaves. The Site access report lists each site's owners.</t>
+          <t>Remove anyone links that are no longer needed, and set the rest to view-only with an expiry date. The Shared files report lists each one.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sharing</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Guests don't have full control of sites</t>
+          <t>SharePoint storage isn't nearly full</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2567,17 +2562,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>1 guest with full control of 1 site</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Take guests out of each site's owners group and away from Full Control; give them Edit or Read through the site's members or visitors group instead. Full Control lets someone outside the organisation change who can open the site and delete anything on it. The Site permissions report lists them.</t>
+          <t>Free up space before the tenant runs out, when people can no longer save files. The SharePoint storage report shows where the space goes and what to clear first; otherwise buy Office 365 Extra File Storage.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2584,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>People outside can only view shared files</t>
+          <t>Every site has at least two owners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2599,29 +2594,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders outside people can edit</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Change sharing with people outside the organisation to view-only unless they need to edit, and remove sharing that's no longer needed. The File and folder permissions report lists each person outside and what they can edit.</t>
+          <t>Give each site a second owner (in the Microsoft 365 group, in the site's owners group, or as a site administrator) so access requests and content questions have someone to go to when one person leaves. The Site access report lists each site's owners.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Admins</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Admins use phishing-resistant sign-in methods</t>
+          <t>Guests don't have full control of sites</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2631,29 +2626,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
+          <t>1 guest with full control of 1 site</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Have each listed admin register a passkey (in Microsoft Authenticator or on a security key) or Windows Hello for Business, then require the Phishing-resistant MFA authentication strength for admin roles in Conditional Access. Codes and push approvals can be relayed by a fake sign-in page; these can't.</t>
+          <t>Take guests out of each site's owners group and away from Full Control; give them Edit or Read through the site's members or visitors group instead. Full Control lets someone outside the organisation change who can open the site and delete anything on it. The Site permissions report lists them.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Sharing</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Nobody relies on a text or call as their only second factor</t>
+          <t>People outside can only view shared files</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2663,221 +2658,317 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>2 files and folders outside people can edit</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Ask these people to set up the Microsoft Authenticator app (the registration campaign in the authentication methods policy prompts them at sign-in), then turn off text message and voice call sign-in, or keep them only as a backup. Texts and calls can be intercepted or moved to an attacker's SIM.</t>
+          <t>Change sharing with people outside the organisation to view-only unless they need to edit, and remove sharing that's no longer needed. The File and folder permissions report lists each person outside and what they can edit.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Licences</t>
+          <t>Admins</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Every licence assignment works</t>
+          <t>Admins use phishing-resistant sign-in methods</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Every licence assignment worked</t>
+          <t>2 admins without a phishing-resistant method</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Fix each failed licence from the group's Licenses page in the Entra admin center: buy more licences when there aren't enough, remove licences that conflict, and correct usage locations. The Licences and subscriptions report explains each error.</t>
+          <t>Have every admin register a passkey (in Microsoft Authenticator or on a security key) or Windows Hello for Business, then require the Phishing-resistant MFA authentication strength for admin roles in Conditional Access. Codes and push approvals can be relayed by a fake sign-in page; these can't.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Licences</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>No subscriptions are about to lapse</t>
+          <t>Nobody relies on a text or call as their only second factor</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions checked; none is lapsing</t>
+          <t>4 people can only use a text or call as a second factor</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Renew subscriptions in their grace period, buy or cancel trials people use before they end, and move people off suspended subscriptions. Billing &gt; Your products in the Microsoft 365 admin center (or Partner Center for subscriptions you sell) shows each one.</t>
+          <t>Ask these people to set up the Microsoft Authenticator app (the registration campaign in the authentication methods policy prompts them at sign-in), then turn off text message and voice call sign-in, or keep them only as a backup. Texts and calls can be intercepted or moved to an attacker's SIM.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Licences</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>No risky sign-ins succeeded</t>
+          <t>Every licence assignment works</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>Sign-in risk needs Entra ID P2</t>
+          <t>Every licence assignment worked</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Check each sign-in with the person. If they don't recognise it, reset their password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised in Entra ID Protection. Add a Conditional Access policy that asks for MFA on medium and high sign-in risk. The Sign-in activity report lists every risky sign-in.</t>
+          <t>Fix each failed licence from the group's Licenses page in the Entra admin center: buy more licences when there aren't enough, remove licences that conflict, and correct usage locations. The Licences and subscriptions report explains each error.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Licences</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>No accounts are at risk in Entra ID Protection</t>
+          <t>No subscriptions are about to lapse</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Not checked</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>Risky users need Entra ID P2</t>
+          <t>2 subscriptions checked; none is lapsing</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>Check each account with the person. If they don't recognise recent sign-ins, reset the password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised or dismiss the risk in Entra ID Protection. Add a Conditional Access policy that asks for a secure password change on high user risk. The Risky users report lists each account.</t>
+          <t>Renew subscriptions in their grace period, buy or cancel trials people use before they end, and move people off suspended subscriptions. Billing &gt; Your products in the Microsoft 365 admin center (or Partner Center for subscriptions you sell) shows each one.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Accounts</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>No account reports to a blocked manager</t>
+          <t>No risky sign-ins succeeded</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>1 account reports to a blocked manager</t>
+          <t>Sign-in risk needs Entra ID P2</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Set a current manager on each listed account (Entra admin center &gt; Users &gt; Properties &gt; Manager, or in on-premises AD for synced accounts). The manager is where approvals, leaver notices and access reviews go; when they've left, those go nowhere, and their blocked account is usually waiting to be deleted too.</t>
+          <t>Check each sign-in with the person. If they don't recognise it, reset their password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised in Entra ID Protection. Add a Conditional Access policy that asks for MFA on medium and high sign-in risk. The Sign-in activity report lists every risky sign-in.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Identity</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>No mailbox is nearly full</t>
+          <t>No accounts are at risk in Entra ID Protection</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Needs attention</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Not checked</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>3 mailboxes at or over 90% of quota</t>
+          <t>Risky users need Entra ID P2</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Turn on the online archive for each listed mailbox (Exchange admin center &gt; Mailboxes &gt; Manage mailbox archive) with a retention policy that moves old mail into it, or clear large old items. A mailbox at its quota can't send, and soon after can't receive.</t>
+          <t>Check each account with the person. If they don't recognise recent sign-ins, reset the password, sign them out everywhere (revoke sessions), and check their MFA methods, inbox rules and app consents; then confirm the account compromised or dismiss the risk in Entra ID Protection. Add a Conditional Access policy that asks for a secure password change on high user risk. The Risky users report lists each account.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>No account reports to a blocked manager</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>1 account reports to a blocked manager</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Set a current manager on each listed account (Entra admin center &gt; Users &gt; Properties &gt; Manager, or in on-premises AD for synced accounts). The manager is where approvals, leaver notices and access reviews go; when they've left, those go nowhere, and their blocked account is usually waiting to be deleted too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>No mailbox is nearly full</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>3 mailboxes at or over 90% of quota</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Turn on the online archive for each listed mailbox (Exchange admin center &gt; Mailboxes &gt; Manage mailbox archive) with a retention policy that moves old mail into it, or clear large old items. A mailbox at its quota can't send, and soon after can't receive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>No OneDrive is nearly full</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>None of 54 OneDrives is over 90% of its quota</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>Ask each listed person to clear or archive old files, or raise their OneDrive quota (SharePoint admin center &gt; Settings &gt; OneDrive Storage limit, up to 5 TB with a qualifying licence). A full OneDrive stops syncing and saving.</t>
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Threats</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>No high or medium severity Defender alerts are left open</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>2 high or medium severity alerts open in Defender, 1 not picked up</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>In the Microsoft Defender portal (Incidents &amp; alerts), assign each open alert to someone, check what it names (for an account: recent sign-ins, inbox rules and MFA methods; for a device: what Defender found on it), then resolve it saying whether it was a real threat. Set up email notifications for new incidents (Settings &gt; Microsoft Defender XDR &gt; Email notifications) so they're seen the day they happen. The Security alerts report lists each alert.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F69"/>
+  <autoFilter ref="A1:F72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -2897,12 +2988,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E164"/>
+  <dimension ref="A1:E172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
@@ -2942,10 +3033,10 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>1 admin without MFA, and 1 whose registration isn't known</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>1 admin without MFA, and 2 whose registration isn't known</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>breakglass@fabrikam.example</t>
         </is>
@@ -2964,39 +3055,39 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>1 admin without MFA, and 1 whose registration isn't known</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>g#EXT#@fabrikam.example</t>
+          <t>1 admin without MFA, and 2 whose registration isn't known</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>evelyn.shaw@fabrikam.example</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Exchange Administrator: MFA registration unknown</t>
+          <t>Global Administrator (eligible): MFA registration unknown</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>1 admin not covered by MFA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>1 admin without MFA, and 2 whose registration isn't known</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>g#EXT#@fabrikam.example</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator: excluded from CA001 — Admins: Require phishing-resistant MFA, CA002 — All users: Require MFA, CA005 — Block sign-ins from disallowed countries, CA006 — Require MFA for Azure management, CA007 — Admins: No persistent browser, 8h sign-in frequency, CA008 — All users: 8h sign-in frequency, CA009 — Require MFA for device registration, CA010 — Insider risk: Step-up MFA, CA011 — High sign-in risk: Block</t>
+          <t>Exchange Administrator: MFA registration unknown</t>
         </is>
       </c>
     </row>
@@ -3008,17 +3099,17 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>1 guest with admin roles</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>g#EXT#@fabrikam.example</t>
+          <t>1 admin not covered by MFA</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Guest holding Exchange Administrator</t>
+          <t>Global Administrator: excluded from CA001 — Admins: Require phishing-resistant MFA, CA002 — All users: Require MFA and 7 more policies</t>
         </is>
       </c>
     </row>
@@ -3030,17 +3121,17 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>1 app with access to mail, files or the directory</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Mail Sync Pro</t>
+          <t>1 guest with admin roles</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>g#EXT#@fabrikam.example</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Mail.Read (application permission; unverified publisher)</t>
+          <t>Guest holding Exchange Administrator</t>
         </is>
       </c>
     </row>
@@ -3052,17 +3143,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>6 of 54 computers not encrypted</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
+          <t>1 app with access to mail, files or the directory</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Mail Sync Pro</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Windows disk isn't encrypted</t>
+          <t>Mail.Read (application permission; unverified publisher)</t>
         </is>
       </c>
     </row>
@@ -3077,19 +3168,14 @@
           <t>6 of 54 computers not encrypted</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Windows disk isn't encrypted</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3104,14 +3190,19 @@
           <t>6 of 54 computers not encrypted</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Windows disk isn't encrypted</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3126,9 +3217,9 @@
           <t>6 of 54 computers not encrypted</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3148,9 +3239,9 @@
           <t>6 of 54 computers not encrypted</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3170,9 +3261,9 @@
           <t>6 of 54 computers not encrypted</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3189,17 +3280,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LAPTOP-HARRIS31 (noah.harris@fabrikam.example)</t>
+          <t>6 of 54 computers not encrypted</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Windows 10 stopped getting security updates on 14 Oct 2025. Extended Security Updates or LTSC can cover it; otherwise upgrade.</t>
+          <t>Windows disk isn't encrypted</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3302,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LAPTOP-JACKSON49 (chloe.jackson@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-HARRIS31 (noah.harris@fabrikam.example)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -3233,12 +3324,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-JACKSON49 (chloe.jackson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -3255,12 +3346,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LAPTOP-SMITH13 (owen.smith@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -3277,12 +3368,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LAPTOP-WALKER04 (rhys.walker@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-SMITH13 (owen.smith@fabrikam.example)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -3299,12 +3390,12 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WALKER04 (rhys.walker@fabrikam.example)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -3321,12 +3412,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LAPTOP-WOOD22 (william.wood@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -3338,670 +3429,670 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DESK-ALLEN09 (thomas.allen@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WOOD22 (william.wood@fabrikam.example)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 10 stopped getting security updates on 14 Oct 2025. Extended Security Updates or LTSC can cover it; otherwise upgrade.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DESK-CLARK06 (ruby.clark@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>DESK-ALLEN09 (thomas.allen@fabrikam.example)</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DESK-HARRISON21 (leo.harrison@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>DESK-CLARK06 (ruby.clark@fabrikam.example)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DESK-KHAN30 (owen.khan@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>DESK-HARRISON21 (leo.harrison@fabrikam.example)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DESK-KING24 (megan.king@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>DESK-KHAN30 (owen.khan@fabrikam.example)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>DESK-KING24 (megan.king@fabrikam.example)</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DESK-ROBERTS45 (jack.roberts@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>DESK-ROBERTS45 (jack.roberts@fabrikam.example)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DESK-WHITE42 (lily.white@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DESK-WILLIAMS27 (arthur.williams@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>DESK-WHITE42 (lily.white@fabrikam.example)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DESK-WOOD39 (ruby.wood@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>DESK-WILLIAMS27 (arthur.williams@fabrikam.example)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>LAPTOP-BROWN01 (aisha.brown@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>DESK-WOOD39 (ruby.wood@fabrikam.example)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-BROWN01 (aisha.brown@fabrikam.example)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>LAPTOP-GREEN32 (megan.green@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>LAPTOP-JOHNSON47 (thomas.johnson@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-GREEN32 (megan.green@fabrikam.example)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>LAPTOP-JONES34 (ethan.jones@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-JOHNSON47 (thomas.johnson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>LAPTOP-KHAN35 (lily.khan@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-JONES34 (ethan.jones@fabrikam.example)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>LAPTOP-LEE02 (jack.lee@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-KHAN35 (lily.khan@fabrikam.example)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-LEE02 (jack.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>LAPTOP-ROBERTS41 (henry.roberts@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>LAPTOP-SCOTT17 (owen.scott@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-ROBERTS41 (henry.roberts@fabrikam.example)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>LAPTOP-SCOTT19 (isla.scott@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-SCOTT17 (owen.scott@fabrikam.example)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>LAPTOP-SMITH50 (oscar.smith@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-SCOTT19 (isla.scott@fabrikam.example)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>LAPTOP-TAYLOR43 (olivia.taylor@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-SMITH50 (oscar.smith@fabrikam.example)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>LAPTOP-THOMAS08 (ava.thomas@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-TAYLOR43 (olivia.taylor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>LAPTOP-TURNER37 (callum.turner@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-THOMAS08 (ava.thomas@fabrikam.example)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>LAPTOP-WALKER10 (george.walker@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-TURNER37 (callum.turner@fabrikam.example)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WALKER10 (george.walker@fabrikam.example)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>7 of 54 Windows computers past end of support</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>LAPTOP-WILLIAMS20 (priya.williams@fabrikam.example)</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Windows 11 24H2: updates for Home and Pro end 13 Oct 2026.</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>1 suspicious inbox rule</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>36 of 54 Windows computers past end of support</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WILLIAMS20 (priya.williams@fabrikam.example)</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>".": Moves to RSS Feeds mail mentioning invoice, payment; Rule name '.' looks deliberately blank</t>
+          <t>Windows 11 24H2: updates for Home and Pro ended 13 Oct 2026 (Enterprise and Education: 12 Oct 2027).</t>
         </is>
       </c>
     </row>
@@ -4013,17 +4104,17 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>1 mail flow rule sends mail outside the organisation</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Copy patient letters to archive</t>
+          <t>1 suspicious inbox rule</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Sends mail or copies to records@dentalarchive.example</t>
+          <t>".": Moves to RSS Feeds mail mentioning invoice, payment; Rule name '.' looks deliberately blank</t>
         </is>
       </c>
     </row>
@@ -4035,17 +4126,17 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>5 external forwards</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>1 mail flow rule sends mail outside the organisation</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Copy patient letters to archive</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Mailbox forwarding to anna.kowalski@homemail.example (keeps a copy)</t>
+          <t>Sends mail or copies to records@dentalarchive.example</t>
         </is>
       </c>
     </row>
@@ -4060,14 +4151,14 @@
           <t>5 external forwards</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Inbox rule "Copy to home" forwards to anna.kowalski.home@homemail.example</t>
+          <t>Mailbox forwarding to anna.kowalski@homemail.example (keeps a copy)</t>
         </is>
       </c>
     </row>
@@ -4082,19 +4173,14 @@
           <t>5 external forwards</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>rhys.hall@fabrikam.example</t>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Mailbox forwarding to rhys.hall@homemail.example (doesn't keep a copy)</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Inbox rule "Copy to home" forwards to anna.kowalski.home@homemail.example</t>
         </is>
       </c>
     </row>
@@ -4109,14 +4195,14 @@
           <t>5 external forwards</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>rhys.walker@fabrikam.example</t>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>rhys.hall@fabrikam.example</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Mailbox forwarding to rhys.walker@homemail.example (doesn't keep a copy)</t>
+          <t>Mailbox forwarding to rhys.hall@homemail.example (doesn't keep a copy)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4136,14 +4222,19 @@
           <t>5 external forwards</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>thomas.robinson@fabrikam.example</t>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Inbox rule "Invoices to bookkeeper" forwards to bookkeeping@ledgerline.example</t>
+          <t>Mailbox forwarding to rhys.walker@homemail.example (doesn't keep a copy)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4155,17 +4246,17 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>2 sender domains skip the spam filter</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Default</t>
+          <t>5 external forwards</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>thomas.robinson@fabrikam.example</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Allows mail claiming to be from gmail.com, labpartners.example past the spam filter (gmail.com is free mail or the organisation's own)</t>
+          <t>Inbox rule "Invoices to bookkeeper" forwards to bookkeeping@ledgerline.example</t>
         </is>
       </c>
     </row>
@@ -4177,24 +4268,24 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>2 sender domains skip the spam filter</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Default</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>No MFA method registered</t>
+          <t>Allows mail claiming to be from gmail.com, labpartners.example past the spam filter (gmail.com is free mail or the organisation's own)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -4202,9 +4293,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>aaron.smith@fabrikam.example</t>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -4224,9 +4315,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>aisha.brown@fabrikam.example</t>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>aaron.smith@fabrikam.example</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -4246,9 +4337,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>amelia.khan@fabrikam.example</t>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -4268,9 +4359,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>arthur.williams@fabrikam.example</t>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>amelia.khan@fabrikam.example</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -4290,9 +4381,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>ava.jackson@fabrikam.example</t>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>arthur.williams@fabrikam.example</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -4312,9 +4403,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>ava.moore@fabrikam.example</t>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>ava.jackson@fabrikam.example</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -4334,9 +4425,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>ava.thomas@fabrikam.example</t>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>ava.moore@fabrikam.example</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -4356,9 +4447,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>carl.svensson@fabrikam.example</t>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>ava.thomas@fabrikam.example</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -4378,9 +4469,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>chloe.jackson@fabrikam.example</t>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>carl.svensson@fabrikam.example</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -4400,9 +4491,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>george.williams@fabrikam.example</t>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>chloe.jackson@fabrikam.example</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -4422,9 +4513,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>henry.roberts@fabrikam.example</t>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>george.williams@fabrikam.example</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -4444,9 +4535,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>isla.scott@fabrikam.example</t>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>henry.roberts@fabrikam.example</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -4466,9 +4557,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>jack.lee@fabrikam.example</t>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>isla.scott@fabrikam.example</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -4488,9 +4579,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>jack.roberts@fabrikam.example</t>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>jack.lee@fabrikam.example</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -4510,9 +4601,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>lily.khan@fabrikam.example</t>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>jack.roberts@fabrikam.example</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -4532,9 +4623,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>lily.watson@fabrikam.example</t>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>lily.khan@fabrikam.example</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -4554,9 +4645,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>lily.white@fabrikam.example</t>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>lily.watson@fabrikam.example</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -4576,9 +4667,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>megan.king@fabrikam.example</t>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>lily.white@fabrikam.example</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -4598,9 +4689,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>noah.wood@fabrikam.example</t>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>megan.king@fabrikam.example</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -4620,9 +4711,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>olivia.taylor@fabrikam.example</t>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>noah.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -4642,9 +4733,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>owen.scott@fabrikam.example</t>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>olivia.taylor@fabrikam.example</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -4664,9 +4755,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>rhys.walker@fabrikam.example</t>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>owen.scott@fabrikam.example</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4686,9 +4777,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>ruby.davies@fabrikam.example</t>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -4708,9 +4799,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>ruby.wood@fabrikam.example</t>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>ruby.davies@fabrikam.example</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4730,9 +4821,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>thomas.johnson@fabrikam.example</t>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>ruby.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -4752,9 +4843,9 @@
           <t>27 users without MFA</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>zara.edwards@fabrikam.example</t>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>thomas.johnson@fabrikam.example</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4766,22 +4857,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Legacy authentication is allowed</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Whole organisation</t>
+          <t>27 users without MFA</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>zara.edwards@fabrikam.example</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>No enabled policy blocks legacy authentication for all users</t>
+          <t>No MFA method registered</t>
         </is>
       </c>
     </row>
@@ -4793,17 +4884,17 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>1 domain had sign-in settings changed in the last 30 days</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>fabrikam.example</t>
+          <t>Legacy authentication is allowed</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Set domain authentication by mallory.quinn@fabrikam.example on 9 Oct 2026</t>
+          <t>No enabled policy blocks legacy authentication for all users</t>
         </is>
       </c>
     </row>
@@ -4815,17 +4906,17 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>2 sites with no owner, 2 sites with one owner</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Marketing</t>
+          <t>1 domain had sign-in settings changed in the last 30 days</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>No enabled owner (Microsoft 365 group)</t>
+          <t>Set domain authentication by mallory.quinn@fabrikam.example on 13 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4840,21 +4931,21 @@
           <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Old Projects</t>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>No enabled owner (site administrators and owners group)</t>
+          <t>No enabled owner (Microsoft 365 group)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -4862,14 +4953,14 @@
           <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Practice Management</t>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Old Projects</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>One owner (Microsoft 365 group)</t>
+          <t>No enabled owner (site administrators and owners group)</t>
         </is>
       </c>
     </row>
@@ -4884,80 +4975,80 @@
           <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Staff Intranet</t>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Practice Management</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>One owner (site administrators and owners group)</t>
+          <t>One owner (Microsoft 365 group)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>1 guest with full control of 1 site</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>accounts@hollis-partners.example on Finance</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Staff Intranet</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Full Control, given Full Control directly</t>
+          <t>One owner (site administrators and owners group)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>aaron.smith@fabrikam.example</t>
+          <t>1 guest with full control of 1 site</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>accounts@hollis-partners.example on Finance</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 23 Apr 2026</t>
+          <t>Full Control, given Full Control directly</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>aisha.brown@fabrikam.example</t>
+          <t>2 high or medium severity alerts open in Defender, 1 not picked up</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Email messages containing malicious URL removed after delivery</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 7 Mar 2026</t>
+          <t>Defender for Office 365, nobody has picked it up, since 14 Oct 2026; names anna.kowalski@fabrikam.example</t>
         </is>
       </c>
     </row>
@@ -4969,17 +5060,17 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>jack.lee@fabrikam.example</t>
+          <t>2 high or medium severity alerts open in Defender, 1 not picked up</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Suspicious PowerShell command line</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 4 Jun 2026</t>
+          <t>Defender for Endpoint, in progress with helpdesk@msp.example, since 12 Oct 2026; names LAPTOP-OKAFOR\bob, LAPTOP-OKAFOR</t>
         </is>
       </c>
     </row>
@@ -4994,14 +5085,14 @@
           <t>7 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>noah.wood@fabrikam.example</t>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>aaron.smith@fabrikam.example</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 7 Feb 2026</t>
+          <t>Licensed member, last signed in 27 Apr 2026</t>
         </is>
       </c>
     </row>
@@ -5016,14 +5107,14 @@
           <t>7 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>rhys.walker@fabrikam.example</t>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 5 Jun 2026</t>
+          <t>Licensed member, last signed in 11 Mar 2026</t>
         </is>
       </c>
     </row>
@@ -5038,21 +5129,21 @@
           <t>7 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>zara.edwards@fabrikam.example</t>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>jack.lee@fabrikam.example</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 9 Jul 2026</t>
+          <t>Licensed member, last signed in 8 Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
@@ -5060,14 +5151,14 @@
           <t>7 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>g#EXT#@fabrikam.example</t>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>noah.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Guest, never signed in, created ?</t>
+          <t>Licensed member, last signed in 11 Feb 2026</t>
         </is>
       </c>
     </row>
@@ -5079,17 +5170,17 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>7 accounts inactive for 90+ days or never used</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator; signs in with Authenticator app</t>
+          <t>Licensed member, last signed in 9 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -5101,39 +5192,39 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>7 accounts inactive for 90+ days or never used</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>zara.edwards@fabrikam.example</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator; signs in with no MFA method at all</t>
+          <t>Licensed member, last signed in 13 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>1 app with privileged roles</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Some app</t>
+          <t>7 accounts inactive for 90+ days or never used</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>g#EXT#@fabrikam.example</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>App holding Exchange Administrator</t>
+          <t>Guest, never signed in, created ?</t>
         </is>
       </c>
     </row>
@@ -5145,17 +5236,17 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Users can consent to any app</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Whole organisation</t>
+          <t>2 admins without a phishing-resistant method</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Any user can grant any app access to their mail and files</t>
+          <t>Global Administrator; signs in with Authenticator app</t>
         </is>
       </c>
     </row>
@@ -5167,17 +5258,17 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>No compliance policy for iOS/iPadOS</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>iOS/iPadOS</t>
+          <t>2 admins without a phishing-resistant method</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>1 enrolled device, no compliance policy assigned</t>
+          <t>Global Administrator; signs in with no MFA method at all</t>
         </is>
       </c>
     </row>
@@ -5189,17 +5280,17 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
+          <t>1 app with privileged roles</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Some app</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
+          <t>App holding Exchange Administrator</t>
         </is>
       </c>
     </row>
@@ -5211,17 +5302,17 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
+          <t>Users can consent to any app</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
+          <t>Any user can grant any app access to their mail and files</t>
         </is>
       </c>
     </row>
@@ -5233,22 +5324,17 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>No compliance policy for iOS/iPadOS</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>iOS/iPadOS</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>1 enrolled device, no compliance policy assigned</t>
         </is>
       </c>
     </row>
@@ -5263,9 +5349,9 @@
           <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5285,9 +5371,9 @@
           <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -5307,14 +5393,19 @@
           <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
           <t>Not compliant</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5329,9 +5420,9 @@
           <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -5351,9 +5442,9 @@
           <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -5373,9 +5464,9 @@
           <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -5392,17 +5483,17 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>8 of 55 joined Windows computers without a saved recovery key</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>DESK-SMITH03</t>
+          <t>9 of 55 managed devices not compliant</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Encrypted, but no recovery key saved in Entra ID</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
@@ -5414,17 +5505,17 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>8 of 55 joined Windows computers without a saved recovery key</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>DESK-WHITE42</t>
+          <t>9 of 55 managed devices not compliant</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Encrypted, but no recovery key saved in Entra ID</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
@@ -5436,17 +5527,17 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>8 of 55 joined Windows computers without a saved recovery key</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>LAPTOP-EVANS26</t>
+          <t>9 of 55 managed devices not compliant</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Encrypted, but no recovery key saved in Entra ID</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
@@ -5458,12 +5549,12 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>8 of 55 joined Windows computers without a saved recovery key</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>LAPTOP-HUGHES11</t>
+          <t>7 of 55 joined Windows computers without a saved recovery key</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>DESK-SMITH03</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -5480,12 +5571,12 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>8 of 55 joined Windows computers without a saved recovery key</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>LAPTOP-JACKSON49</t>
+          <t>7 of 55 joined Windows computers without a saved recovery key</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>DESK-WHITE42</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -5502,12 +5593,12 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>8 of 55 joined Windows computers without a saved recovery key</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>LAPTOP-JONES34</t>
+          <t>7 of 55 joined Windows computers without a saved recovery key</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-EVANS26</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -5524,12 +5615,12 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>8 of 55 joined Windows computers without a saved recovery key</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>LAPTOP-SCOTT19</t>
+          <t>7 of 55 joined Windows computers without a saved recovery key</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-HUGHES11</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
@@ -5541,22 +5632,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>8 of 55 joined Windows computers without a saved recovery key</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>DESK-RECEPTION</t>
+          <t>7 of 55 joined Windows computers without a saved recovery key</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-JACKSON49</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>No recovery key saved in Entra ID (encryption not known)</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
@@ -5568,17 +5659,17 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>1 mail domain without DKIM</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>fabrikam.example</t>
+          <t>7 of 55 joined Windows computers without a saved recovery key</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-JONES34</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 DKIM isn't set up (selector2 CNAME missing)</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
@@ -5590,39 +5681,39 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>fabrikam.example</t>
+          <t>7 of 55 joined Windows computers without a saved recovery key</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-SCOTT19</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>DMARC is monitor-only (p=none); spoofed mail is still delivered</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>parked.example</t>
+          <t>1 mail domain without DKIM</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Doesn't receive mail but has no DMARC p=reject record</t>
+          <t>Microsoft 365 DKIM isn't set up (selector2 CNAME missing)</t>
         </is>
       </c>
     </row>
@@ -5634,39 +5725,39 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>1 anti-malware policy lets risky attachment types through</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Default</t>
+          <t>2 domains without DMARC enforcement</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>The common attachments filter is off</t>
+          <t>DMARC is monitor-only (p=none); spoofed mail is still delivered</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>1 anti-phishing policy weakens spoof protection</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Office365 AntiPhish Default</t>
+          <t>2 domains without DMARC enforcement</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>parked.example</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Ignores what senders' DMARC policies ask for</t>
+          <t>Doesn't receive mail but has no DMARC p=reject record</t>
         </is>
       </c>
     </row>
@@ -5678,46 +5769,46 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Project Phoenix</t>
+          <t>1 anti-malware policy lets risky attachment types through</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Default</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Team, only owner is disabled (Ben Okafor)</t>
+          <t>The common attachments filter is off</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Marketing</t>
+          <t>1 anti-phishing policy weakens spoof protection</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Office365 AntiPhish Default</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, only owner is disabled (Ben Okafor)</t>
+          <t>Ignores what senders' DMARC policies ask for</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
@@ -5725,14 +5816,14 @@
           <t>4 teams and groups without an owner</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Marketing</t>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Project Phoenix</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, no owner</t>
+          <t>Team, only owner is disabled (Ben Okafor)</t>
         </is>
       </c>
     </row>
@@ -5747,58 +5838,58 @@
           <t>4 teams and groups without an owner</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Provisioned</t>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, owned only by an app (Provisioning app)</t>
+          <t>Microsoft 365 group, only owner is disabled (Ben Okafor)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>Enforced by CA002 — All users: Require MFA, with 1 exclusion to review</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>4 teams and groups without an owner</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Excluded from "CA002 — All users: Require MFA"</t>
+          <t>Microsoft 365 group, no owner</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>1 disabled account still licensed</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>ben.okafor@fabrikam.example</t>
+          <t>4 teams and groups without an owner</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>Provisioned</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Disabled, holding 1 licence</t>
+          <t>Microsoft 365 group, owned only by an app (Provisioning app)</t>
         </is>
       </c>
     </row>
@@ -5810,17 +5901,17 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including anonymous links</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>SharePoint and OneDrive</t>
+          <t>Enforced by CA002 — All users: Require MFA, with 1 exclusion to review</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Anyone links are allowed</t>
+          <t>Excluded from "CA002 — All users: Require MFA"</t>
         </is>
       </c>
     </row>
@@ -5832,17 +5923,17 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>holiday.jpg (OneDrive of anna.kowalski@fabrikam.example)</t>
+          <t>1 disabled account still licensed</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>ben.okafor@fabrikam.example</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Anyone can view</t>
+          <t>Disabled, holding 1 licence</t>
         </is>
       </c>
     </row>
@@ -5854,17 +5945,17 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Open day flyer.pdf (Marketing / Documents)</t>
+          <t>Anyone, including anonymous links</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>SharePoint and OneDrive</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Anyone can view, link never expires</t>
+          <t>Anyone links are allowed</t>
         </is>
       </c>
     </row>
@@ -5876,22 +5967,17 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders outside people can edit</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Budget.xlsx (Finance / Documents)</t>
+          <t>2 files and folders shared with anyone</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>holiday.jpg (OneDrive of anna.kowalski@fabrikam.example)</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Can be edited by accountant@hargreaves-partners.example</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Anyone can view</t>
         </is>
       </c>
     </row>
@@ -5903,17 +5989,17 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders outside people can edit</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Lab dockets (Patient Records / Documents)</t>
+          <t>2 files and folders shared with anyone</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Open day flyer.pdf (Marketing / Documents)</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Can be edited by orders@dentallab.example</t>
+          <t>Anyone can view, link never expires</t>
         </is>
       </c>
     </row>
@@ -5925,17 +6011,22 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>3 mailboxes at or over 90% of quota</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>accounts@fabrikam.example</t>
+          <t>2 files and folders outside people can edit</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Budget.xlsx (Finance / Documents)</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>44.8 GB of 49.5 GB (91%), no archive</t>
+          <t>Can be edited by accountant@hargreaves-partners.example</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5947,22 +6038,17 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>3 mailboxes at or over 90% of quota</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>aisha.brown@fabrikam.example</t>
+          <t>2 files and folders outside people can edit</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>Lab dockets (Patient Records / Documents)</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>47.2 GB of 49.5 GB (95%), no archive</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Can be edited by orders@dentallab.example</t>
         </is>
       </c>
     </row>
@@ -5977,19 +6063,14 @@
           <t>3 mailboxes at or over 90% of quota</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>thomas.robinson@fabrikam.example</t>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>accounts@fabrikam.example</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>45.6 GB of 49.5 GB (92%), no archive</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>44.8 GB of 49.5 GB (91%), no archive</t>
         </is>
       </c>
     </row>
@@ -6001,17 +6082,17 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Tenant SharePoint storage</t>
+          <t>3 mailboxes at or over 90% of quota</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>47.2 GB of 49.5 GB (95%), no archive</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6023,22 +6104,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>https://fabrikam.sharepoint.com/sites/finance</t>
+          <t>3 mailboxes at or over 90% of quota</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>thomas.robinson@fabrikam.example</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
+          <t>45.6 GB of 49.5 GB (92%), no archive</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6050,7 +6131,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
@@ -6058,14 +6139,14 @@
           <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>https://fabrikam.sharepoint.com/sites/imaging</t>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>Tenant SharePoint storage</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6085,14 +6166,14 @@
           <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>https://fabrikam.sharepoint.com/sites/marketing</t>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>https://fabrikam.sharepoint.com/sites/finance</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
+          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -6112,14 +6193,14 @@
           <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>https://fabrikam.sharepoint.com/sites/patient-records</t>
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>https://fabrikam.sharepoint.com/sites/imaging</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
+          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -6139,14 +6220,14 @@
           <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>https://fabrikam.sharepoint.com/sites/practice</t>
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>https://fabrikam.sharepoint.com/sites/marketing</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
+          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6163,17 +6244,22 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>1 account reports to a blocked manager</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="inlineStr">
+        <is>
+          <t>https://fabrikam.sharepoint.com/sites/patient-records</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Reports to Ben Okafor, whose sign-in is blocked</t>
+          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6185,17 +6271,22 @@
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>1 app registration with expiring or expired credentials</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Old connector</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>https://fabrikam.sharepoint.com/sites/practice</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>The 1 credential expired, last on 1 Jan 2025</t>
+          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6207,17 +6298,17 @@
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>1 of 55 joined computers not in Intune</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>DESK-RECEPTION</t>
+          <t>1 account reports to a blocked manager</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Hybrid joined, not managed by Intune</t>
+          <t>Reports to Ben Okafor, whose sign-in is blocked</t>
         </is>
       </c>
     </row>
@@ -6229,17 +6320,17 @@
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
+          <t>1 app registration with expiring or expired credentials</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>Old connector</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>The 1 credential expired, last on 1 Jan 2025</t>
         </is>
       </c>
     </row>
@@ -6251,22 +6342,17 @@
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>1 of 55 joined computers not in Intune</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>DESK-RECEPTION</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Hybrid joined, not managed by Intune</t>
         </is>
       </c>
     </row>
@@ -6281,9 +6367,9 @@
           <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
@@ -6303,14 +6389,19 @@
           <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
           <t>Last check-in 38 days ago</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6325,14 +6416,14 @@
           <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 45 days ago</t>
+          <t>Last check-in 38 days ago</t>
         </is>
       </c>
     </row>
@@ -6344,17 +6435,17 @@
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>1 of 57 device records unused for 90+ days</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>OLD-PC</t>
+          <t>5 devices haven't checked in for 30+ days</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Windows, last seen 200 days ago</t>
+          <t>Last check-in 38 days ago</t>
         </is>
       </c>
     </row>
@@ -6366,17 +6457,17 @@
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>1 domain with SPF problems</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>parked.example</t>
+          <t>5 devices haven't checked in for 30+ days</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>Doesn't receive mail but has no "v=spf1 -all" record to stop spoofing</t>
+          <t>Last check-in 45 days ago</t>
         </is>
       </c>
     </row>
@@ -6388,17 +6479,17 @@
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>fabrikam.example</t>
+          <t>1 of 57 device records unused for 90+ days</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>OLD-PC</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>No MTA-STS policy, so mail sent to this domain can be forced onto an unencrypted connection</t>
+          <t>Windows, last seen 200 days ago</t>
         </is>
       </c>
     </row>
@@ -6410,17 +6501,17 @@
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is on for the organisation</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Whole organisation</t>
+          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>DESK-HARRISON21</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is allowed</t>
+          <t>No local admin password backed up in Entra ID</t>
         </is>
       </c>
     </row>
@@ -6432,17 +6523,17 @@
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including guests, can invite guests</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Whole organisation</t>
+          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="inlineStr">
+        <is>
+          <t>DESK-ROBERTS45</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Guests can invite other guests</t>
+          <t>No local admin password backed up in Entra ID</t>
         </is>
       </c>
     </row>
@@ -6454,17 +6545,17 @@
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>george.baker@fabrikam.example</t>
+          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-SMITH13</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>No local admin password backed up in Entra ID</t>
         </is>
       </c>
     </row>
@@ -6476,22 +6567,17 @@
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>owen.robinson@fabrikam.example</t>
+          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-TURNER37</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>No local admin password backed up in Entra ID</t>
         </is>
       </c>
     </row>
@@ -6503,17 +6589,17 @@
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>owen.turner@fabrikam.example</t>
+          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WARD29</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>No local admin password backed up in Entra ID</t>
         </is>
       </c>
     </row>
@@ -6525,17 +6611,17 @@
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>thomas.allen@fabrikam.example</t>
+          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>LAPTOP-WOOD05</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>No local admin password backed up in Entra ID</t>
         </is>
       </c>
     </row>
@@ -6547,17 +6633,17 @@
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions with spare licences</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Microsoft 365 Business Basic</t>
+          <t>1 domain with SPF problems</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>parked.example</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>2 of 13 unassigned, 9.80 GBP/month</t>
+          <t>Doesn't receive mail but has no "v=spf1 -all" record to stop spoofing</t>
         </is>
       </c>
     </row>
@@ -6569,17 +6655,17 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions with spare licences</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Microsoft 365 Business Premium</t>
+          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>3 of 46 unassigned, 54.30 GBP/month</t>
+          <t>No MTA-STS policy, so mail sent to this domain can be forced onto an unencrypted connection</t>
         </is>
       </c>
     </row>
@@ -6591,22 +6677,203 @@
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
+          <t>SMTP AUTH is on for the organisation</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="inlineStr">
+        <is>
+          <t>Whole organisation</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>SMTP AUTH is allowed</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>Anyone, including guests, can invite guests</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
+        <is>
+          <t>Whole organisation</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>Guests can invite other guests</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="inlineStr">
+        <is>
+          <t>george.baker@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>owen.robinson@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>owen.turner@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>thomas.allen@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>2 subscriptions with spare licences</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft 365 Business Basic</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>2 of 13 unassigned, 9.80 GBP/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>2 subscriptions with spare licences</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft 365 Business Premium</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>3 of 46 unassigned, 54.30 GBP/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
           <t>Any user can register an app</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C172" s="7" t="inlineStr">
         <is>
           <t>Whole organisation</t>
         </is>
       </c>
-      <c r="D164" s="7" t="inlineStr">
+      <c r="D172" s="7" t="inlineStr">
         <is>
           <t>Users can register apps that nobody reviews</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E164"/>
+  <autoFilter ref="A1:E172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -6780,7 +7047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -6812,7 +7079,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>46307.47756944445</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6827,7 +7094,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>46307.47756944445</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6842,7 +7109,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>46307.47756944445</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -6857,7 +7124,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>46307.47756944445</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6872,7 +7139,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>46307.47756944445</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6887,7 +7154,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>46307.47756944445</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -6902,7 +7169,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>46307.47756944445</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -6917,7 +7184,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>46307.47756944445</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6932,7 +7199,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6947,7 +7214,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6962,7 +7229,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -6977,7 +7244,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -6992,7 +7259,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -7007,7 +7274,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.46931712963</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -7022,7 +7289,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -7037,7 +7304,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -7052,7 +7319,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -7067,7 +7334,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -7082,7 +7349,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -7097,7 +7364,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7112,7 +7379,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7127,7 +7394,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7142,7 +7409,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7153,11 +7420,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Email domains</t>
+          <t>Security alerts</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -7168,11 +7435,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Email domains</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -7183,11 +7450,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Intune policies</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -7198,11 +7465,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Directory sync</t>
+          <t>Intune policies</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -7213,11 +7480,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SharePoint and OneDrive usage</t>
+          <t>Installed apps</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7228,11 +7495,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shared files</t>
+          <t>Directory sync</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -7243,11 +7510,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SharePoint storage</t>
+          <t>SharePoint and OneDrive usage</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.4693287037</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7258,11 +7525,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Site permissions</t>
+          <t>Shared files</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>46307.47758101852</v>
+        <v>46311.46934027778</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7273,11 +7540,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Site access</t>
+          <t>SharePoint storage</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>46307.47759259259</v>
+        <v>46311.46934027778</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7288,11 +7555,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Microsoft 365 usage</t>
+          <t>Site permissions</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>46307.47759259259</v>
+        <v>46311.46934027778</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7303,11 +7570,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Site access</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>46307.47759259259</v>
+        <v>46311.46934027778</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7318,11 +7585,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mail flow</t>
+          <t>Microsoft 365 usage</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>46307.47759259259</v>
+        <v>46311.46934027778</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -7333,11 +7600,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mail rules and protection</t>
+          <t>Teams</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>46307.47759259259</v>
+        <v>46311.46934027778</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -7348,11 +7615,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>App sign-ins</t>
+          <t>Mail flow</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>46307.47759259259</v>
+        <v>46311.46934027778</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -7363,11 +7630,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Group nesting</t>
+          <t>Mail rules and protection</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>46307.47759259259</v>
+        <v>46311.46934027778</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -7378,11 +7645,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Departments and managers</t>
+          <t>App sign-ins</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>46307.47759259259</v>
+        <v>46311.46934027778</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7393,20 +7660,65 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Group nesting</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>46311.46934027778</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Departments and managers</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>46311.46934027778</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Administrative units</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n">
-        <v>46307.47759259259</v>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B43" s="13" t="n">
+        <v>46311.46934027778</v>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Up to date</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Service health</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="n">
+        <v>46311.46934027778</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C41"/>
+  <autoFilter ref="A1:C44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -49,7 +49,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000D7A5F"/>
+      <color rgb="002B4A6B"/>
       <sz val="16"/>
     </font>
     <font>
@@ -77,7 +77,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D7A5F"/>
+        <fgColor rgb="002B4A6B"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +91,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="000D7A5F"/>
+        <color rgb="002B4A6B"/>
       </bottom>
     </border>
   </borders>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 16 Oct 2026, 11:17 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 16 Oct 2026, 12:33 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Set domain authentication by mallory.quinn@fabrikam.example on 13 Oct 2026</t>
+          <t>Set domain authentication by mallory.quinn@fabrikam.example on 14 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>46311.46931712963</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52193287037</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>46311.4693287037</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52194444444</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52195601852</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52195601852</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52195601852</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52195601852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52195601852</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52195601852</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52195601852</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>46311.46934027778</v>
+        <v>46311.52195601852</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 16 Oct 2026, 12:33 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 16 Oct 2026, 13:36 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>46311.52193287037</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.5654050926</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>46311.52194444444</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>46311.52195601852</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>46311.52195601852</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>46311.52195601852</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>46311.52195601852</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>46311.52195601852</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>46311.52195601852</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>46311.52195601852</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>46311.52195601852</v>
+        <v>46311.56541666666</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Summary'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checks'!$A$1:$F$72</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Checks'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings'!$A$1:$E$175</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Findings'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Licences'!$A$1:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Licences'!$1:$1</definedName>
@@ -30,10 +30,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="d mmm yyyy hh:mm"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -98,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,9 +111,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -515,7 +511,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 16 Oct 2026, 13:36 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 17 Oct 2026, 10:10 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -555,7 +551,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>32% on 18 Sep 2026</t>
+          <t>32% on 19 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -565,12 +561,12 @@
           <t>Users with MFA</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>0.509</v>
+      <c r="B8" s="6" t="n">
+        <v>0.5</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>45.6% on 18 Sep 2026</t>
+          <t>44.7% on 19 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -580,12 +576,12 @@
           <t>Privileged accounts</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>4 on 18 Sep 2026</t>
+          <t>4 on 19 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -595,12 +591,12 @@
           <t>Licensed users</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="8" t="n">
         <v>54</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>51 on 18 Sep 2026</t>
+          <t>51 on 19 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -610,8 +606,8 @@
           <t>Inactive accounts</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>7</v>
+      <c r="B11" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="C11" s="7" t="n"/>
     </row>
@@ -621,7 +617,7 @@
           <t>Licence waste / month (GBP)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="8" t="n">
         <v>164.4</v>
       </c>
       <c r="C12" s="7" t="n"/>
@@ -632,12 +628,12 @@
           <t>Checks needing attention</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>48</v>
+      <c r="B13" s="9" t="n">
+        <v>49</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>1 critical, 31 high, 99 medium, 40 low findings</t>
+          <t>1 critical, 31 high, 101 medium, 41 low findings</t>
         </is>
       </c>
     </row>
@@ -647,8 +643,8 @@
           <t>Checks passed</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
-        <v>16</v>
+      <c r="B14" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="C14" s="7" t="n"/>
     </row>
@@ -658,7 +654,7 @@
           <t>Not checked</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="9" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="7" t="n"/>
@@ -682,12 +678,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Checks</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="9" t="n">
         <v>71</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -697,13 +693,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v>171</v>
+      <c r="B19" s="9" t="n">
+        <v>174</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -712,12 +708,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Licences</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -727,12 +723,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Data freshness</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="9" t="n">
         <v>43</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1020,7 +1016,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1052,7 +1048,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>8 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1084,7 +1080,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>1 disabled account still licensed</t>
+          <t>1 disabled account still licensed (not counting 1 shared mailbox that needs one)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1261,12 +1257,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Needs attention</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>All 3 shared mailboxes block sign-in</t>
+          <t>1 of 3 shared mailboxes allows sign-in</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -2988,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E172"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3082,7 +3083,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>g#EXT#@fabrikam.example</t>
+          <t>sam.carter_consultants.example#EXT#@fabrikam.onmicrosoft.com</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -3126,7 +3127,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>g#EXT#@fabrikam.example</t>
+          <t>sam.carter_consultants.example#EXT#@fabrikam.onmicrosoft.com</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -4290,7 +4291,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -4312,7 +4313,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -4334,7 +4335,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -4356,7 +4357,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -4378,7 +4379,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -4400,7 +4401,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -4422,7 +4423,7 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
@@ -4444,7 +4445,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -4466,7 +4467,7 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
@@ -4488,7 +4489,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -4510,7 +4511,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
@@ -4532,7 +4533,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
@@ -4554,7 +4555,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
@@ -4576,7 +4577,7 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
@@ -4598,7 +4599,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
@@ -4620,7 +4621,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
@@ -4642,7 +4643,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -4664,7 +4665,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
@@ -4686,7 +4687,7 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
@@ -4708,7 +4709,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
@@ -4730,7 +4731,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
@@ -4752,7 +4753,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -4774,12 +4775,12 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>rhys.walker@fabrikam.example</t>
+          <t>reception@fabrikam.example</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -4796,12 +4797,12 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>ruby.davies@fabrikam.example</t>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4818,12 +4819,12 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>ruby.wood@fabrikam.example</t>
+          <t>ruby.davies@fabrikam.example</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -4840,12 +4841,12 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>thomas.johnson@fabrikam.example</t>
+          <t>ruby.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4862,12 +4863,12 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>27 users without MFA</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>zara.edwards@fabrikam.example</t>
+          <t>thomas.johnson@fabrikam.example</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -4879,22 +4880,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Legacy authentication is allowed</t>
+          <t>28 users without MFA</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>zara.edwards@fabrikam.example</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>No enabled policy blocks legacy authentication for all users</t>
+          <t>No MFA method registered</t>
         </is>
       </c>
     </row>
@@ -4906,17 +4907,17 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>1 domain had sign-in settings changed in the last 30 days</t>
+          <t>Legacy authentication is allowed</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Set domain authentication by mallory.quinn@fabrikam.example on 14 Oct 2026</t>
+          <t>No enabled policy blocks legacy authentication for all users</t>
         </is>
       </c>
     </row>
@@ -4928,17 +4929,17 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>2 sites with no owner, 2 sites with one owner</t>
+          <t>1 domain had sign-in settings changed in the last 30 days</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>No enabled owner (Microsoft 365 group)</t>
+          <t>Set domain authentication by mallory.quinn@fabrikam.example on 14 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -4955,19 +4956,19 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Old Projects</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>No enabled owner (site administrators and owners group)</t>
+          <t>No enabled owner (Microsoft 365 group)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -4977,12 +4978,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Practice Management</t>
+          <t>Old Projects</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>One owner (Microsoft 365 group)</t>
+          <t>No enabled owner (site administrators and owners group)</t>
         </is>
       </c>
     </row>
@@ -4999,34 +5000,34 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Staff Intranet</t>
+          <t>Practice Management</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>One owner (site administrators and owners group)</t>
+          <t>One owner (Microsoft 365 group)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>1 guest with full control of 1 site</t>
+          <t>2 sites with no owner, 2 sites with one owner</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>accounts@hollis-partners.example on Finance</t>
+          <t>Staff Intranet</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Full Control, given Full Control directly</t>
+          <t>One owner (site administrators and owners group)</t>
         </is>
       </c>
     </row>
@@ -5038,24 +5039,24 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>2 high or medium severity alerts open in Defender, 1 not picked up</t>
+          <t>1 guest with full control of 1 site</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Email messages containing malicious URL removed after delivery</t>
+          <t>accounts@hollis-partners.example on Finance</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Defender for Office 365, nobody has picked it up, since 14 Oct 2026; names anna.kowalski@fabrikam.example</t>
+          <t>Full Control, given Full Control directly</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -5065,12 +5066,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Suspicious PowerShell command line</t>
+          <t>Email messages containing malicious URL removed after delivery</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Defender for Endpoint, in progress with helpdesk@msp.example, since 12 Oct 2026; names LAPTOP-OKAFOR\bob, LAPTOP-OKAFOR</t>
+          <t>Defender for Office 365, nobody has picked it up, since 15 Oct 2026; names anna.kowalski@fabrikam.example</t>
         </is>
       </c>
     </row>
@@ -5082,17 +5083,17 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>2 high or medium severity alerts open in Defender, 1 not picked up</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>aaron.smith@fabrikam.example</t>
+          <t>Suspicious PowerShell command line</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 27 Apr 2026</t>
+          <t>Defender for Endpoint, in progress with helpdesk@msp.example, since 13 Oct 2026; names LAPTOP-OKAFOR\bob, LAPTOP-OKAFOR</t>
         </is>
       </c>
     </row>
@@ -5104,17 +5105,17 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>8 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>aisha.brown@fabrikam.example</t>
+          <t>aaron.smith@fabrikam.example</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 11 Mar 2026</t>
+          <t>Licensed member, last signed in 28 Apr 2026</t>
         </is>
       </c>
     </row>
@@ -5126,17 +5127,17 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>8 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>jack.lee@fabrikam.example</t>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 8 Jun 2026</t>
+          <t>Licensed member, last signed in 12 Mar 2026</t>
         </is>
       </c>
     </row>
@@ -5148,17 +5149,17 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>8 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>noah.wood@fabrikam.example</t>
+          <t>jack.lee@fabrikam.example</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 11 Feb 2026</t>
+          <t>Licensed member, last signed in 9 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -5170,17 +5171,17 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>8 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>rhys.walker@fabrikam.example</t>
+          <t>noah.wood@fabrikam.example</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 9 Jun 2026</t>
+          <t>Licensed member, last signed in 12 Feb 2026</t>
         </is>
       </c>
     </row>
@@ -5192,83 +5193,83 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>8 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>zara.edwards@fabrikam.example</t>
+          <t>rhys.walker@fabrikam.example</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 13 Jul 2026</t>
+          <t>Licensed member, last signed in 10 Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>7 accounts inactive for 90+ days or never used</t>
+          <t>8 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>g#EXT#@fabrikam.example</t>
+          <t>zara.edwards@fabrikam.example</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Guest, never signed in, created ?</t>
+          <t>Licensed member, last signed in 14 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
+          <t>8 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>reception@fabrikam.example</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator; signs in with Authenticator app</t>
+          <t>Member, never signed in, created 4 Mar 2024</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>2 admins without a phishing-resistant method</t>
+          <t>8 accounts inactive for 90+ days or never used</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>sam.carter_consultants.example#EXT#@fabrikam.onmicrosoft.com</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Global Administrator; signs in with no MFA method at all</t>
+          <t>Guest, never signed in, created 2 Sep 2025</t>
         </is>
       </c>
     </row>
@@ -5280,17 +5281,17 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>1 app with privileged roles</t>
+          <t>2 admins without a phishing-resistant method</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Some app</t>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>App holding Exchange Administrator</t>
+          <t>Global Administrator; signs in with Authenticator app</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5303,17 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Users can consent to any app</t>
+          <t>2 admins without a phishing-resistant method</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Any user can grant any app access to their mail and files</t>
+          <t>Global Administrator; signs in with no MFA method at all</t>
         </is>
       </c>
     </row>
@@ -5324,17 +5325,17 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>No compliance policy for iOS/iPadOS</t>
+          <t>1 app with privileged roles</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>iOS/iPadOS</t>
+          <t>Backup connector</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>1 enrolled device, no compliance policy assigned</t>
+          <t>App holding Exchange Administrator</t>
         </is>
       </c>
     </row>
@@ -5346,17 +5347,17 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>Users can consent to any app</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
+          <t>Any user can grant any app access to their mail and files</t>
         </is>
       </c>
     </row>
@@ -5368,17 +5369,17 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>9 of 55 managed devices not compliant</t>
+          <t>No compliance policy for iOS/iPadOS</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
+          <t>iOS/iPadOS</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Not compliant</t>
+          <t>1 enrolled device, no compliance policy assigned</t>
         </is>
       </c>
     </row>
@@ -5395,17 +5396,12 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
           <t>Not compliant</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5418,7 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+          <t>DESK-MOORE18 (ava.moore@fabrikam.example)</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -5444,12 +5440,17 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
           <t>Not compliant</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5467,7 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -5488,7 +5489,7 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -5510,7 +5511,7 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
@@ -5532,7 +5533,7 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
+          <t>LAPTOP-ROBINSON07 (thomas.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -5549,17 +5550,17 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>7 of 55 joined Windows computers without a saved recovery key</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>DESK-SMITH03</t>
+          <t>LAPTOP-WARD29 (jack.ward@fabrikam.example)</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Encrypted, but no recovery key saved in Entra ID</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
@@ -5571,17 +5572,17 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>7 of 55 joined Windows computers without a saved recovery key</t>
+          <t>9 of 55 managed devices not compliant</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>DESK-WHITE42</t>
+          <t>LAPTOP-WATSON40 (lily.watson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>Encrypted, but no recovery key saved in Entra ID</t>
+          <t>Not compliant</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5599,7 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-EVANS26</t>
+          <t>DESK-SMITH03</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -5620,7 +5621,7 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-HUGHES11</t>
+          <t>DESK-WHITE42</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
@@ -5642,7 +5643,7 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-JACKSON49</t>
+          <t>LAPTOP-EVANS26</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
@@ -5664,7 +5665,7 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-JONES34</t>
+          <t>LAPTOP-HUGHES11</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
@@ -5686,7 +5687,7 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-SCOTT19</t>
+          <t>LAPTOP-JACKSON49</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
@@ -5703,17 +5704,17 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>1 mail domain without DKIM</t>
+          <t>7 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>LAPTOP-JONES34</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 DKIM isn't set up (selector2 CNAME missing)</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
@@ -5725,39 +5726,39 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
+          <t>7 of 55 joined Windows computers without a saved recovery key</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>LAPTOP-SCOTT19</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>DMARC is monitor-only (p=none); spoofed mail is still delivered</t>
+          <t>Encrypted, but no recovery key saved in Entra ID</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>2 domains without DMARC enforcement</t>
+          <t>1 mail domain without DKIM</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>parked.example</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Doesn't receive mail but has no DMARC p=reject record</t>
+          <t>Microsoft 365 DKIM isn't set up (selector2 CNAME missing)</t>
         </is>
       </c>
     </row>
@@ -5769,39 +5770,39 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>1 anti-malware policy lets risky attachment types through</t>
+          <t>2 domains without DMARC enforcement</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>The common attachments filter is off</t>
+          <t>DMARC is monitor-only (p=none); spoofed mail is still delivered</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>1 anti-phishing policy weakens spoof protection</t>
+          <t>2 domains without DMARC enforcement</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Office365 AntiPhish Default</t>
+          <t>parked.example</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Ignores what senders' DMARC policies ask for</t>
+          <t>Needs a DMARC p=reject record, or spoofed mail from it is still delivered</t>
         </is>
       </c>
     </row>
@@ -5813,68 +5814,68 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
+          <t>1 anti-malware policy lets risky attachment types through</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>Project Phoenix</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Team, only owner is disabled (Ben Okafor)</t>
+          <t>The common attachments filter is off</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
+          <t>1 of 3 shared mailboxes allows sign-in</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>reception@fabrikam.example</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, only owner is disabled (Ben Okafor)</t>
+          <t>Shared mailbox account allows sign-in</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>4 teams and groups without an owner</t>
+          <t>1 anti-phishing policy weakens spoof protection</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Office365 AntiPhish Default</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, no owner</t>
+          <t>Ignores what senders' DMARC policies ask for</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
@@ -5884,78 +5885,78 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>Provisioned</t>
+          <t>Project Phoenix</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 group, owned only by an app (Provisioning app)</t>
+          <t>Team, only owner is disabled (Ben Okafor)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>Enforced by CA002 — All users: Require MFA, with 1 exclusion to review</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>breakglass@fabrikam.example</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Excluded from "CA002 — All users: Require MFA"</t>
+          <t>Microsoft 365 group, only owner is disabled (Ben Okafor)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>1 disabled account still licensed</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>ben.okafor@fabrikam.example</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Disabled, holding 1 licence</t>
+          <t>Microsoft 365 group, no owner</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including anonymous links</t>
+          <t>4 teams and groups without an owner</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>SharePoint and OneDrive</t>
+          <t>Provisioned</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Anyone links are allowed</t>
+          <t>Microsoft 365 group, owned only by an app (Provisioning app)</t>
         </is>
       </c>
     </row>
@@ -5967,17 +5968,17 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
+          <t>Enforced by CA002 — All users: Require MFA, with 1 exclusion to review</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>holiday.jpg (OneDrive of anna.kowalski@fabrikam.example)</t>
+          <t>breakglass@fabrikam.example</t>
         </is>
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Anyone can view</t>
+          <t>Excluded from "CA002 — All users: Require MFA"</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5990,17 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders shared with anyone</t>
+          <t>1 disabled account still licensed (not counting 1 shared mailbox that needs one)</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>Open day flyer.pdf (Marketing / Documents)</t>
+          <t>ben.okafor@fabrikam.example</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Anyone can view, link never expires</t>
+          <t>Disabled, holding 1 licence</t>
         </is>
       </c>
     </row>
@@ -6011,22 +6012,17 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders outside people can edit</t>
+          <t>Anyone, including anonymous links</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>Budget.xlsx (Finance / Documents)</t>
+          <t>SharePoint and OneDrive</t>
         </is>
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Can be edited by accountant@hargreaves-partners.example</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Anyone links are allowed</t>
         </is>
       </c>
     </row>
@@ -6038,17 +6034,17 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>2 files and folders outside people can edit</t>
+          <t>2 files and folders shared with anyone</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>Lab dockets (Patient Records / Documents)</t>
+          <t>holiday.jpg (OneDrive of anna.kowalski@fabrikam.example)</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Can be edited by orders@dentallab.example</t>
+          <t>Anyone can view</t>
         </is>
       </c>
     </row>
@@ -6060,17 +6056,17 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>3 mailboxes at or over 90% of quota</t>
+          <t>2 files and folders shared with anyone</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>accounts@fabrikam.example</t>
+          <t>Open day flyer.pdf (Marketing / Documents)</t>
         </is>
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>44.8 GB of 49.5 GB (91%), no archive</t>
+          <t>Anyone can view, link never expires</t>
         </is>
       </c>
     </row>
@@ -6082,17 +6078,17 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>3 mailboxes at or over 90% of quota</t>
+          <t>2 files and folders outside people can edit</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>aisha.brown@fabrikam.example</t>
+          <t>Budget.xlsx (Finance / Documents)</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>47.2 GB of 49.5 GB (95%), no archive</t>
+          <t>Can be edited by accountant@hargreaves-partners.example</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6109,22 +6105,17 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>3 mailboxes at or over 90% of quota</t>
+          <t>2 files and folders outside people can edit</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>thomas.robinson@fabrikam.example</t>
+          <t>Lab dockets (Patient Records / Documents)</t>
         </is>
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>45.6 GB of 49.5 GB (92%), no archive</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Can be edited by orders@dentallab.example</t>
         </is>
       </c>
     </row>
@@ -6136,44 +6127,39 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>3 mailboxes at or over 90% of quota</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>Tenant SharePoint storage</t>
+          <t>accounts@fabrikam.example</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>44.8 GB of 49.5 GB (91%), no archive</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>3 mailboxes at or over 90% of quota</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/finance</t>
+          <t>aisha.brown@fabrikam.example</t>
         </is>
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
+          <t>47.2 GB of 49.5 GB (95%), no archive</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -6185,22 +6171,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
+          <t>3 mailboxes at or over 90% of quota</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/imaging</t>
+          <t>thomas.robinson@fabrikam.example</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
+          <t>45.6 GB of 49.5 GB (92%), no archive</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -6212,7 +6198,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
@@ -6222,12 +6208,12 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/marketing</t>
+          <t>Tenant SharePoint storage</t>
         </is>
       </c>
       <c r="D144" s="7" t="inlineStr">
         <is>
-          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -6249,12 +6235,12 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/patient-records</t>
+          <t>https://fabrikam.sharepoint.com/sites/finance</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
+          <t>117.5 GB, of which 3.0 GB in the recycle bin and 7.6 GB older versions</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -6276,12 +6262,12 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>https://fabrikam.sharepoint.com/sites/practice</t>
+          <t>https://fabrikam.sharepoint.com/sites/imaging</t>
         </is>
       </c>
       <c r="D146" s="7" t="inlineStr">
         <is>
-          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
+          <t>483.2 GB, of which 46.0 GB in the recycle bin and 33.3 GB older versions</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -6298,17 +6284,22 @@
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>1 account reports to a blocked manager</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>anna.kowalski@fabrikam.example</t>
+          <t>https://fabrikam.sharepoint.com/sites/marketing</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Reports to Ben Okafor, whose sign-in is blocked</t>
+          <t>65.3 GB, of which 1.0 GB in the recycle bin and 4.9 GB older versions</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6320,17 +6311,22 @@
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>1 app registration with expiring or expired credentials</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>Old connector</t>
+          <t>https://fabrikam.sharepoint.com/sites/patient-records</t>
         </is>
       </c>
       <c r="D148" s="7" t="inlineStr">
         <is>
-          <t>The 1 credential expired, last on 1 Jan 2025</t>
+          <t>352.6 GB, of which 12.0 GB in the recycle bin and 25.2 GB older versions</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6342,17 +6338,22 @@
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>1 of 55 joined computers not in Intune</t>
+          <t>88% of about 1.45 TB used (1 TB + 10 GB × 46 licences)</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>DESK-RECEPTION</t>
+          <t>https://fabrikam.sharepoint.com/sites/practice</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Hybrid joined, not managed by Intune</t>
+          <t>182.8 GB, of which 6.0 GB in the recycle bin and 21.1 GB older versions</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6364,17 +6365,17 @@
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>1 account reports to a blocked manager</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
+          <t>anna.kowalski@fabrikam.example</t>
         </is>
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>Reports to Ben Okafor, whose sign-in is blocked</t>
         </is>
       </c>
     </row>
@@ -6386,22 +6387,17 @@
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>1 app registration with expiring or expired credentials</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
+          <t>Old connector</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>The 1 credential expired, last on 1 Jan 2025</t>
         </is>
       </c>
     </row>
@@ -6413,17 +6409,17 @@
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
-          <t>5 devices haven't checked in for 30+ days</t>
+          <t>1 of 55 joined computers not in Intune</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
+          <t>DESK-RECEPTION</t>
         </is>
       </c>
       <c r="D152" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 38 days ago</t>
+          <t>Hybrid joined, not managed by Intune</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6436,7 @@
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
+          <t>DESK-LEWIS12 (william.lewis@fabrikam.example)</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
@@ -6462,12 +6458,17 @@
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
+          <t>DESK-ROBINSON51 (owen.robinson@fabrikam.example)</t>
         </is>
       </c>
       <c r="D154" s="7" t="inlineStr">
         <is>
-          <t>Last check-in 45 days ago</t>
+          <t>Last check-in 38 days ago</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6479,17 +6480,17 @@
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>1 of 57 device records unused for 90+ days</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>OLD-PC</t>
+          <t>LAPTOP-DAVIES38 (ruby.davies@fabrikam.example)</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Windows, last seen 200 days ago</t>
+          <t>Last check-in 38 days ago</t>
         </is>
       </c>
     </row>
@@ -6501,17 +6502,17 @@
       </c>
       <c r="B156" s="7" t="inlineStr">
         <is>
-          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>DESK-HARRISON21</t>
+          <t>LAPTOP-LEE25 (arthur.lee@fabrikam.example)</t>
         </is>
       </c>
       <c r="D156" s="7" t="inlineStr">
         <is>
-          <t>No local admin password backed up in Entra ID</t>
+          <t>Last check-in 38 days ago</t>
         </is>
       </c>
     </row>
@@ -6523,17 +6524,17 @@
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
+          <t>5 devices haven't checked in for 30+ days</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>DESK-ROBERTS45</t>
+          <t>LAPTOP-OKAFOR (ben.okafor@fabrikam.example)</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>No local admin password backed up in Entra ID</t>
+          <t>Last check-in 45 days ago</t>
         </is>
       </c>
     </row>
@@ -6545,17 +6546,17 @@
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
+          <t>1 of 57 device records unused for 90+ days</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-SMITH13</t>
+          <t>OLD-PC</t>
         </is>
       </c>
       <c r="D158" s="7" t="inlineStr">
         <is>
-          <t>No local admin password backed up in Entra ID</t>
+          <t>Windows, last seen 200 days ago</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6573,7 @@
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-TURNER37</t>
+          <t>DESK-HARRISON21</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
@@ -6594,7 +6595,7 @@
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-WARD29</t>
+          <t>DESK-ROBERTS45</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
@@ -6616,7 +6617,7 @@
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>LAPTOP-WOOD05</t>
+          <t>LAPTOP-SMITH13</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
@@ -6633,17 +6634,17 @@
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>1 domain with SPF problems</t>
+          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>parked.example</t>
+          <t>LAPTOP-TURNER37</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>Doesn't receive mail but has no "v=spf1 -all" record to stop spoofing</t>
+          <t>No local admin password backed up in Entra ID</t>
         </is>
       </c>
     </row>
@@ -6655,17 +6656,17 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
+          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>fabrikam.example</t>
+          <t>LAPTOP-WARD29</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>No MTA-STS policy, so mail sent to this domain can be forced onto an unencrypted connection</t>
+          <t>No local admin password backed up in Entra ID</t>
         </is>
       </c>
     </row>
@@ -6677,17 +6678,17 @@
       </c>
       <c r="B164" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is on for the organisation</t>
+          <t>6 of 54 Entra joined Windows computers without a LAPS backup</t>
         </is>
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>LAPTOP-WOOD05</t>
         </is>
       </c>
       <c r="D164" s="7" t="inlineStr">
         <is>
-          <t>SMTP AUTH is allowed</t>
+          <t>No local admin password backed up in Entra ID</t>
         </is>
       </c>
     </row>
@@ -6699,17 +6700,17 @@
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>Anyone, including guests, can invite guests</t>
+          <t>1 domain with SPF problems</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>Whole organisation</t>
+          <t>parked.example</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Guests can invite other guests</t>
+          <t>Needs a "v=spf1 -all" record saying it sends no mail, or anyone can send as it</t>
         </is>
       </c>
     </row>
@@ -6721,17 +6722,17 @@
       </c>
       <c r="B166" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>1 of 1 mail domain doesn't fully enforce MTA-STS</t>
         </is>
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>george.baker@fabrikam.example</t>
+          <t>fabrikam.example</t>
         </is>
       </c>
       <c r="D166" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>No MTA-STS policy, so mail sent to this domain can be forced onto an unencrypted connection</t>
         </is>
       </c>
     </row>
@@ -6743,22 +6744,17 @@
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>SMTP AUTH is on for the organisation</t>
         </is>
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>owen.robinson@fabrikam.example</t>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>SMTP AUTH is allowed</t>
         </is>
       </c>
     </row>
@@ -6770,17 +6766,17 @@
       </c>
       <c r="B168" s="7" t="inlineStr">
         <is>
-          <t>4 people can only use a text or call as a second factor</t>
+          <t>Anyone, including guests, can invite guests</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>owen.turner@fabrikam.example</t>
+          <t>Whole organisation</t>
         </is>
       </c>
       <c r="D168" s="7" t="inlineStr">
         <is>
-          <t>Second factor is only Mobile phone (SMS or call)</t>
+          <t>Guests can invite other guests</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6793,7 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>thomas.allen@fabrikam.example</t>
+          <t>george.baker@fabrikam.example</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
@@ -6814,17 +6810,22 @@
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions with spare licences</t>
+          <t>4 people can only use a text or call as a second factor</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 Business Basic</t>
+          <t>owen.robinson@fabrikam.example</t>
         </is>
       </c>
       <c r="D170" s="7" t="inlineStr">
         <is>
-          <t>2 of 13 unassigned, 9.80 GBP/month</t>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6836,17 +6837,17 @@
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>2 subscriptions with spare licences</t>
+          <t>4 people can only use a text or call as a second factor</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>Microsoft 365 Business Premium</t>
+          <t>owen.turner@fabrikam.example</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>3 of 46 unassigned, 54.30 GBP/month</t>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
         </is>
       </c>
     </row>
@@ -6858,22 +6859,88 @@
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
+          <t>4 people can only use a text or call as a second factor</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>thomas.allen@fabrikam.example</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>Second factor is only Mobile phone (SMS or call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>2 subscriptions with spare licences</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft 365 Business Basic</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>2 of 13 unassigned, 9.80 GBP/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>2 subscriptions with spare licences</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t>Microsoft 365 Business Premium</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>3 of 46 unassigned, 54.30 GBP/month</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
           <t>Any user can register an app</t>
         </is>
       </c>
-      <c r="C172" s="7" t="inlineStr">
+      <c r="C175" s="7" t="inlineStr">
         <is>
           <t>Whole organisation</t>
         </is>
       </c>
-      <c r="D172" s="7" t="inlineStr">
+      <c r="D175" s="7" t="inlineStr">
         <is>
           <t>Users can register apps that nobody reviews</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E172"/>
+  <autoFilter ref="A1:E175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -6986,10 +7053,10 @@
       <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="H2" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="11" t="n">
         <v>144.8</v>
       </c>
     </row>
@@ -7019,10 +7086,10 @@
       <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="12" t="n">
+      <c r="H3" s="11" t="n">
         <v>4.9</v>
       </c>
-      <c r="I3" s="12" t="n">
+      <c r="I3" s="11" t="n">
         <v>19.6</v>
       </c>
     </row>
@@ -7078,8 +7145,8 @@
           <t>Tenant profile and licences</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B2" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7093,8 +7160,8 @@
           <t>Connection and permissions</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B3" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -7108,8 +7175,8 @@
           <t>Users</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B4" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -7123,8 +7190,8 @@
           <t>Admin roles</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B5" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7138,8 +7205,8 @@
           <t>Conditional Access</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B6" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -7153,8 +7220,8 @@
           <t>MFA registration</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B7" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7168,8 +7235,8 @@
           <t>Per-user MFA</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B8" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -7183,8 +7250,8 @@
           <t>Secure Score</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B9" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -7198,8 +7265,8 @@
           <t>Sign-in methods policy</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B10" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -7213,8 +7280,8 @@
           <t>Admin activity</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B11" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -7228,8 +7295,8 @@
           <t>Apps and consents</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B12" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -7243,8 +7310,8 @@
           <t>Sharing and consent settings</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B13" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -7258,8 +7325,8 @@
           <t>Groups and Teams</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B14" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -7273,8 +7340,8 @@
           <t>Deleted users and groups</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B15" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -7288,8 +7355,8 @@
           <t>Mailboxes</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B16" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -7303,8 +7370,8 @@
           <t>Inbox rules</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B17" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -7318,8 +7385,8 @@
           <t>Sign-in activity</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B18" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -7333,8 +7400,8 @@
           <t>Mailbox size</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B19" s="12" t="n">
+        <v>46312.42236111111</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -7348,8 +7415,8 @@
           <t>Legacy sign-ins</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B20" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -7363,8 +7430,8 @@
           <t>Mobile devices</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n">
-        <v>46311.5654050926</v>
+      <c r="B21" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7378,8 +7445,8 @@
           <t>Automatic replies</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B22" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7393,8 +7460,8 @@
           <t>Distribution lists</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B23" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7408,8 +7475,8 @@
           <t>Risky users</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B24" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7423,8 +7490,8 @@
           <t>Security alerts</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B25" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -7438,8 +7505,8 @@
           <t>Email domains</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B26" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -7453,8 +7520,8 @@
           <t>Devices</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B27" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -7468,8 +7535,8 @@
           <t>Intune policies</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B28" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -7483,8 +7550,8 @@
           <t>Installed apps</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B29" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7498,8 +7565,8 @@
           <t>Directory sync</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B30" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -7513,8 +7580,8 @@
           <t>SharePoint and OneDrive usage</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B31" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7528,8 +7595,8 @@
           <t>Shared files</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B32" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7543,8 +7610,8 @@
           <t>SharePoint storage</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B33" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7558,8 +7625,8 @@
           <t>Site permissions</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B34" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7573,8 +7640,8 @@
           <t>Site access</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B35" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7588,8 +7655,8 @@
           <t>Microsoft 365 usage</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B36" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -7603,8 +7670,8 @@
           <t>Teams</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B37" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -7618,8 +7685,8 @@
           <t>Mail flow</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B38" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -7633,8 +7700,8 @@
           <t>Mail rules and protection</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B39" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -7648,8 +7715,8 @@
           <t>App sign-ins</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B40" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7663,8 +7730,8 @@
           <t>Group nesting</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B41" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -7678,8 +7745,8 @@
           <t>Departments and managers</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B42" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7693,8 +7760,8 @@
           <t>Administrative units</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B43" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7708,8 +7775,8 @@
           <t>Service health</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
-        <v>46311.56541666666</v>
+      <c r="B44" s="12" t="n">
+        <v>46312.42237268519</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 17 Oct 2026, 10:10 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 17 Oct 2026, 14:14 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Set domain authentication by mallory.quinn@fabrikam.example on 14 Oct 2026</t>
+          <t>Set domain authentication by mallory.quinn@fabrikam.example on 15 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>46312.42236111111</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59164351852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>46312.42237268519</v>
+        <v>46312.59165509259</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>

--- a/examples/monthly-security-licensing-review.xlsx
+++ b/examples/monthly-security-licensing-review.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Findings'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Licences'!$A$1:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Licences'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Data freshness'!$A$1:$C$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Data freshness'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by Harbour IT · 17 Oct 2026, 14:14 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
+          <t>Prepared by Harbour IT · 24 Oct 2026, 11:17 UTC · Microsoft 365 tenant fabrikam.onmicrosoft.com</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>32% on 19 Sep 2026</t>
+          <t>33% on 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>44.7% on 19 Sep 2026</t>
+          <t>46.1% on 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>4 on 19 Sep 2026</t>
+          <t>4 on 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>51 on 19 Sep 2026</t>
+          <t>51 on 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Set domain authentication by mallory.quinn@fabrikam.example on 15 Oct 2026</t>
+          <t>Set domain authentication by mallory.quinn@fabrikam.example on 21 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Defender for Office 365, nobody has picked it up, since 15 Oct 2026; names anna.kowalski@fabrikam.example</t>
+          <t>Defender for Office 365, nobody has picked it up, since 22 Oct 2026; names anna.kowalski@fabrikam.example</t>
         </is>
       </c>
     </row>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Defender for Endpoint, in progress with helpdesk@msp.example, since 13 Oct 2026; names LAPTOP-OKAFOR\bob, LAPTOP-OKAFOR</t>
+          <t>Defender for Endpoint, in progress with helpdesk@msp.example, since 20 Oct 2026; names LAPTOP-OKAFOR\bob, LAPTOP-OKAFOR</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 28 Apr 2026</t>
+          <t>Licensed member, last signed in 5 May 2026</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 12 Mar 2026</t>
+          <t>Licensed member, last signed in 19 Mar 2026</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 9 Jun 2026</t>
+          <t>Licensed member, last signed in 16 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 12 Feb 2026</t>
+          <t>Licensed member, last signed in 19 Feb 2026</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 10 Jun 2026</t>
+          <t>Licensed member, last signed in 17 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Licensed member, last signed in 14 Jul 2026</t>
+          <t>Licensed member, last signed in 21 Jul 2026</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Guest, never signed in, created 2 Sep 2025</t>
+          <t>Guest, never signed in, created 9 Sep 2025</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46934027778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46934027778</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46934027778</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46934027778</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46934027778</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46934027778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46934027778</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46934027778</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46934027778</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46934027778</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>46312.59164351852</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46935185185</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>46312.59165509259</v>
+        <v>46319.46936342592</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -7784,8 +7784,23 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI agents</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="n">
+        <v>46319.46936342592</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Up to date</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C44"/>
+  <autoFilter ref="A1:C45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
